--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/20260617/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FAA89F1-03EA-4BE9-8D6E-67BDF424414B}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7FD4372-6CF4-4BD7-BE5E-62711F9400BD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="4" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -888,7 +888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -908,6 +908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5382,7 +5383,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6112,7 +6113,7 @@
         <v>9</v>
       </c>
       <c r="N3" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -6213,7 +6214,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -6259,7 +6260,7 @@
         <v>18</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -6544,7 +6545,7 @@
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14" t="s">
         <v>136</v>
       </c>
     </row>
@@ -6555,7 +6556,7 @@
       <c r="B31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14" t="s">
         <v>148</v>
       </c>
     </row>
@@ -7476,7 +7477,7 @@
       </c>
       <c r="CD3">
         <f>IFERROR(VLOOKUP(BT3,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE3">
         <f>IF(BR3='Resultats Reals'!$K$2,5,0)</f>
@@ -7484,7 +7485,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" ref="CF3:CF49" si="0">SUM(BU3:CE3)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.25">
@@ -8002,7 +8003,7 @@
       </c>
       <c r="CD5">
         <f>IFERROR(VLOOKUP(BT5,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE5">
         <f>IF(BR5='Resultats Reals'!$K$2,5,0)</f>
@@ -8010,7 +8011,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.25">
@@ -8265,7 +8266,7 @@
       </c>
       <c r="CD6">
         <f>IFERROR(VLOOKUP(BT6,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE6">
         <f>IF(BR6='Resultats Reals'!$K$2,5,0)</f>
@@ -8273,7 +8274,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.25">
@@ -8528,7 +8529,7 @@
       </c>
       <c r="CD7">
         <f>IFERROR(VLOOKUP(BT7,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE7">
         <f>IF(BR7='Resultats Reals'!$K$2,5,0)</f>
@@ -8536,7 +8537,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.25">
@@ -9057,7 +9058,7 @@
       </c>
       <c r="CD9">
         <f>IFERROR(VLOOKUP(BT9,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE9">
         <f>IF(BR9='Resultats Reals'!$K$2,5,0)</f>
@@ -9065,7 +9066,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.25">
@@ -9320,7 +9321,7 @@
       </c>
       <c r="CD10">
         <f>IFERROR(VLOOKUP(BT10,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE10">
         <f>IF(BR10='Resultats Reals'!$K$2,5,0)</f>
@@ -9328,7 +9329,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.25">
@@ -9583,7 +9584,7 @@
       </c>
       <c r="CD11">
         <f>IFERROR(VLOOKUP(BT11,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE11">
         <f>IF(BR11='Resultats Reals'!$K$2,5,0)</f>
@@ -9591,7 +9592,7 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.25">
@@ -9846,7 +9847,7 @@
       </c>
       <c r="CD12">
         <f>IFERROR(VLOOKUP(BT12,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE12">
         <f>IF(BR12='Resultats Reals'!$K$2,5,0)</f>
@@ -9854,7 +9855,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.25">
@@ -10109,7 +10110,7 @@
       </c>
       <c r="CD13">
         <f>IFERROR(VLOOKUP(BT13,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE13">
         <f>IF(BR13='Resultats Reals'!$K$2,5,0)</f>
@@ -10117,7 +10118,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.25">
@@ -11161,7 +11162,7 @@
       </c>
       <c r="CD17">
         <f>IFERROR(VLOOKUP(BT17,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE17">
         <f>IF(BR17='Resultats Reals'!$K$2,5,0)</f>
@@ -11169,7 +11170,7 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.25">
@@ -11427,7 +11428,7 @@
       </c>
       <c r="CD18">
         <f>IFERROR(VLOOKUP(BT18,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE18">
         <f>IF(BR18='Resultats Reals'!$K$2,5,0)</f>
@@ -11435,7 +11436,7 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.25">
@@ -11953,7 +11954,7 @@
       </c>
       <c r="CD20">
         <f>IFERROR(VLOOKUP(BT20,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE20">
         <f>IF(BR20='Resultats Reals'!$K$2,5,0)</f>
@@ -11961,7 +11962,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.25">
@@ -12216,7 +12217,7 @@
       </c>
       <c r="CD21">
         <f>IFERROR(VLOOKUP(BT21,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE21">
         <f>IF(BR21='Resultats Reals'!$K$2,5,0)</f>
@@ -12224,7 +12225,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.25">
@@ -12479,7 +12480,7 @@
       </c>
       <c r="CD22">
         <f>IFERROR(VLOOKUP(BT22,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE22">
         <f>IF(BR22='Resultats Reals'!$K$2,5,0)</f>
@@ -12487,7 +12488,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.25">
@@ -13005,7 +13006,7 @@
       </c>
       <c r="CD24">
         <f>IFERROR(VLOOKUP(BT24,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE24">
         <f>IF(BR24='Resultats Reals'!$K$2,5,0)</f>
@@ -13013,7 +13014,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.25">
@@ -13534,7 +13535,7 @@
       </c>
       <c r="CD26">
         <f>IFERROR(VLOOKUP(BT26,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE26">
         <f>IF(BR26='Resultats Reals'!$K$2,5,0)</f>
@@ -13542,7 +13543,7 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.25">
@@ -14060,7 +14061,7 @@
       </c>
       <c r="CD28">
         <f>IFERROR(VLOOKUP(BT28,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE28">
         <f>IF(BR28='Resultats Reals'!$K$2,5,0)</f>
@@ -14068,7 +14069,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.25">
@@ -14326,7 +14327,7 @@
       </c>
       <c r="CD29">
         <f>IFERROR(VLOOKUP(BT29,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE29">
         <f>IF(BR29='Resultats Reals'!$K$2,5,0)</f>
@@ -14334,7 +14335,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.25">
@@ -14852,7 +14853,7 @@
       </c>
       <c r="CD31">
         <f>IFERROR(VLOOKUP(BT31,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE31">
         <f>IF(BR31='Resultats Reals'!$K$2,5,0)</f>
@@ -14860,7 +14861,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.25">
@@ -15118,7 +15119,7 @@
       </c>
       <c r="CD32">
         <f>IFERROR(VLOOKUP(BT32,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE32">
         <f>IF(BR32='Resultats Reals'!$K$2,5,0)</f>
@@ -15126,7 +15127,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.25">
@@ -15650,7 +15651,7 @@
       </c>
       <c r="CD34">
         <f>IFERROR(VLOOKUP(BT34,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE34">
         <f>IF(BR34='Resultats Reals'!$K$2,5,0)</f>
@@ -15658,7 +15659,7 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.25">
@@ -16705,7 +16706,7 @@
       </c>
       <c r="CD38">
         <f>IFERROR(VLOOKUP(BT38,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE38">
         <f>IF(BR38='Resultats Reals'!$K$2,5,0)</f>
@@ -16713,7 +16714,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.25">
@@ -17237,7 +17238,7 @@
       </c>
       <c r="CD40">
         <f>IFERROR(VLOOKUP(BT40,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE40">
         <f>IF(BR40='Resultats Reals'!$K$2,5,0)</f>
@@ -17245,7 +17246,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.25">
@@ -17763,7 +17764,7 @@
       </c>
       <c r="CD42">
         <f>IFERROR(VLOOKUP(BT42,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE42">
         <f>IF(BR42='Resultats Reals'!$K$2,5,0)</f>
@@ -17771,7 +17772,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.25">
@@ -18292,7 +18293,7 @@
       </c>
       <c r="CD44">
         <f>IFERROR(VLOOKUP(BT44,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE44">
         <f>IF(BR44='Resultats Reals'!$K$2,5,0)</f>
@@ -18300,7 +18301,7 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.25">
@@ -19650,7 +19651,7 @@
       <c r="A2" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="13">
         <v>40</v>
       </c>
     </row>
@@ -19658,7 +19659,7 @@
       <c r="A3" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="13">
         <v>40</v>
       </c>
     </row>
@@ -19666,7 +19667,7 @@
       <c r="A4" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="13">
         <v>39.5</v>
       </c>
     </row>
@@ -19674,7 +19675,7 @@
       <c r="A5" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="13">
         <v>39.5</v>
       </c>
     </row>
@@ -19682,7 +19683,7 @@
       <c r="A6" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="13">
         <v>39.5</v>
       </c>
     </row>
@@ -19690,7 +19691,7 @@
       <c r="A7" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="13">
         <v>38.5</v>
       </c>
     </row>
@@ -19698,7 +19699,7 @@
       <c r="A8" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="13">
         <v>38.5</v>
       </c>
     </row>
@@ -19706,7 +19707,7 @@
       <c r="A9" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="13">
         <v>37.5</v>
       </c>
     </row>
@@ -19714,7 +19715,7 @@
       <c r="A10" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="13">
         <v>37.5</v>
       </c>
     </row>
@@ -19722,7 +19723,7 @@
       <c r="A11" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="13">
         <v>37.5</v>
       </c>
     </row>
@@ -19730,7 +19731,7 @@
       <c r="A12" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="13">
         <v>37.5</v>
       </c>
     </row>
@@ -19738,7 +19739,7 @@
       <c r="A13" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="13">
         <v>37</v>
       </c>
     </row>
@@ -19746,7 +19747,7 @@
       <c r="A14" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="13">
         <v>37</v>
       </c>
     </row>
@@ -19754,7 +19755,7 @@
       <c r="A15" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="13">
         <v>37</v>
       </c>
     </row>
@@ -19762,7 +19763,7 @@
       <c r="A16" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="13">
         <v>36.5</v>
       </c>
     </row>
@@ -19770,7 +19771,7 @@
       <c r="A17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="13">
         <v>36.5</v>
       </c>
     </row>
@@ -19778,7 +19779,7 @@
       <c r="A18" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="13">
         <v>36</v>
       </c>
     </row>
@@ -19786,7 +19787,7 @@
       <c r="A19" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="13">
         <v>36</v>
       </c>
     </row>
@@ -19794,7 +19795,7 @@
       <c r="A20" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="13">
         <v>36</v>
       </c>
     </row>
@@ -19802,7 +19803,7 @@
       <c r="A21" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="13">
         <v>36</v>
       </c>
     </row>
@@ -19810,7 +19811,7 @@
       <c r="A22" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="13">
         <v>35.5</v>
       </c>
     </row>
@@ -19818,7 +19819,7 @@
       <c r="A23" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="13">
         <v>35.5</v>
       </c>
     </row>
@@ -19826,7 +19827,7 @@
       <c r="A24" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="13">
         <v>35.5</v>
       </c>
     </row>
@@ -19834,7 +19835,7 @@
       <c r="A25" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="13">
         <v>35.5</v>
       </c>
     </row>
@@ -19842,7 +19843,7 @@
       <c r="A26" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="13">
         <v>35</v>
       </c>
     </row>
@@ -19850,7 +19851,7 @@
       <c r="A27" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="13">
         <v>34.5</v>
       </c>
     </row>
@@ -19858,7 +19859,7 @@
       <c r="A28" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="13">
         <v>34.5</v>
       </c>
     </row>
@@ -19866,7 +19867,7 @@
       <c r="A29" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="13">
         <v>34</v>
       </c>
     </row>
@@ -19874,7 +19875,7 @@
       <c r="A30" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="13">
         <v>34</v>
       </c>
     </row>
@@ -19882,7 +19883,7 @@
       <c r="A31" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="13">
         <v>34</v>
       </c>
     </row>
@@ -19890,7 +19891,7 @@
       <c r="A32" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="13">
         <v>33.5</v>
       </c>
     </row>
@@ -19898,7 +19899,7 @@
       <c r="A33" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="13">
         <v>33.5</v>
       </c>
     </row>
@@ -19906,7 +19907,7 @@
       <c r="A34" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="13">
         <v>33.5</v>
       </c>
     </row>
@@ -19914,7 +19915,7 @@
       <c r="A35" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="13">
         <v>33</v>
       </c>
     </row>
@@ -19922,7 +19923,7 @@
       <c r="A36" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="13">
         <v>33</v>
       </c>
     </row>
@@ -19930,7 +19931,7 @@
       <c r="A37" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="13">
         <v>33</v>
       </c>
     </row>
@@ -19938,7 +19939,7 @@
       <c r="A38" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="13">
         <v>32.5</v>
       </c>
     </row>
@@ -19946,7 +19947,7 @@
       <c r="A39" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="13">
         <v>32.5</v>
       </c>
     </row>
@@ -19954,7 +19955,7 @@
       <c r="A40" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="13">
         <v>32.5</v>
       </c>
     </row>
@@ -19962,7 +19963,7 @@
       <c r="A41" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="13">
         <v>32.5</v>
       </c>
     </row>
@@ -19970,7 +19971,7 @@
       <c r="A42" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="13">
         <v>32.5</v>
       </c>
     </row>
@@ -19978,7 +19979,7 @@
       <c r="A43" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="13">
         <v>31.5</v>
       </c>
     </row>
@@ -19986,7 +19987,7 @@
       <c r="A44" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="13">
         <v>31.5</v>
       </c>
     </row>
@@ -19994,7 +19995,7 @@
       <c r="A45" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="13">
         <v>30</v>
       </c>
     </row>
@@ -20002,7 +20003,7 @@
       <c r="A46" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="13">
         <v>29</v>
       </c>
     </row>
@@ -20010,7 +20011,7 @@
       <c r="A47" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="13">
         <v>28</v>
       </c>
     </row>
@@ -20018,7 +20019,7 @@
       <c r="A48" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="13">
         <v>28</v>
       </c>
     </row>
@@ -20026,7 +20027,7 @@
       <c r="A49" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="13">
         <v>20.5</v>
       </c>
     </row>
@@ -20034,7 +20035,7 @@
       <c r="A50" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="13">
         <v>1662</v>
       </c>
     </row>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7FD4372-6CF4-4BD7-BE5E-62711F9400BD}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97F5CD4-316D-6E41-A837-797711BDE8C7}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3723" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3723" uniqueCount="246">
   <si>
     <t>Grup</t>
   </si>
@@ -5383,7 +5383,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -5994,24 +5994,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="19" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="1" max="2" width="9.953125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.953125" customWidth="1"/>
+    <col min="5" max="5" width="16.0078125" customWidth="1"/>
+    <col min="6" max="6" width="14.9296875" customWidth="1"/>
+    <col min="7" max="7" width="13.98828125" customWidth="1"/>
+    <col min="8" max="8" width="18.96484375" customWidth="1"/>
+    <col min="9" max="9" width="14.9296875" customWidth="1"/>
+    <col min="10" max="10" width="11.97265625" customWidth="1"/>
+    <col min="11" max="11" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.953125" customWidth="1"/>
+    <col min="13" max="13" width="18.96484375" customWidth="1"/>
+    <col min="14" max="14" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -6116,7 +6116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -6283,7 +6283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>24</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>24</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
@@ -6482,7 +6482,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>29</v>
       </c>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
@@ -6549,7 +6549,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -6557,10 +6557,10 @@
         <v>10</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -6571,7 +6571,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>31</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
@@ -6634,81 +6634,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.45703125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB2)&gt;0,1,0)</f>
@@ -7222,10 +7222,10 @@
       </c>
       <c r="CF2" s="7">
         <f>SUM(BU2:CE2)</f>
-        <v>35</v>
+        <v>34.5</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>151</v>
       </c>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB3)&gt;0,1,0)</f>
@@ -7485,10 +7485,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" ref="CF3:CF49" si="0">SUM(BU3:CE3)</f>
-        <v>40</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB4)&gt;0,1,0)</f>
@@ -7748,10 +7748,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>158</v>
       </c>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB5)&gt;0,1,0)</f>
@@ -8011,10 +8011,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>160</v>
       </c>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB7)&gt;0,1,0)</f>
@@ -8537,10 +8537,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>162</v>
       </c>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0),1,0))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB8)&gt;0,1,0)</f>
@@ -8800,10 +8800,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>21.5</v>
+        <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>167</v>
       </c>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB9)&gt;0,1,0)</f>
@@ -9066,10 +9066,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB10)&gt;0,1,0)</f>
@@ -9329,10 +9329,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>211</v>
       </c>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB11)&gt;0,1,0)</f>
@@ -9592,10 +9592,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>212</v>
       </c>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL12)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB12)&gt;0,1,0)</f>
@@ -9855,10 +9855,10 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>171</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>231</v>
       </c>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB14)&gt;0,1,0)</f>
@@ -10381,10 +10381,10 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>172</v>
       </c>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB15)&gt;0,1,0)</f>
@@ -10644,10 +10644,10 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>232</v>
       </c>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB16)&gt;0,1,0)</f>
@@ -10907,10 +10907,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33.5</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>173</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>233</v>
       </c>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB18)&gt;0,1,0)</f>
@@ -11436,10 +11436,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>176</v>
       </c>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB19)&gt;0,1,0)</f>
@@ -11699,10 +11699,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>177</v>
       </c>
@@ -11965,7 +11965,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>178</v>
       </c>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB21)&gt;0,1,0)</f>
@@ -12225,10 +12225,10 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>179</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>235</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>181</v>
       </c>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0),1,0))</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB24)&gt;0,1,0)</f>
@@ -13014,10 +13014,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>234</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>182</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>184</v>
       </c>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB27)&gt;0,1,0)</f>
@@ -13806,10 +13806,10 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>185</v>
       </c>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB28)&gt;0,1,0)</f>
@@ -14069,10 +14069,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>187</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>188</v>
       </c>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB30)&gt;0,1,0)</f>
@@ -14598,10 +14598,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>236</v>
       </c>
@@ -14864,7 +14864,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>190</v>
       </c>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB32)&gt;0,1,0)</f>
@@ -15127,10 +15127,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>213</v>
       </c>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB33)&gt;0,1,0)</f>
@@ -15393,10 +15393,10 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>192</v>
       </c>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB34)&gt;0,1,0)</f>
@@ -15659,10 +15659,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>214</v>
       </c>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB35)&gt;0,1,0)</f>
@@ -15922,10 +15922,10 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33.5</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>194</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>195</v>
       </c>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB37)&gt;0,1,0)</f>
@@ -16448,10 +16448,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>215</v>
       </c>
@@ -16717,7 +16717,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB39)&gt;0,1,0)</f>
@@ -16980,10 +16980,10 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>216</v>
       </c>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB40)&gt;0,1,0)</f>
@@ -17246,10 +17246,10 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>201</v>
       </c>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB41)&gt;0,1,0)</f>
@@ -17509,10 +17509,10 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34.5</v>
       </c>
     </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>203</v>
       </c>
@@ -17736,7 +17736,7 @@
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB42)&gt;0,1,0)</f>
@@ -17772,10 +17772,10 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>204</v>
       </c>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB43)&gt;0,1,0)</f>
@@ -18038,10 +18038,10 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>217</v>
       </c>
@@ -18265,7 +18265,7 @@
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB44)&gt;0,1,0)</f>
@@ -18301,10 +18301,10 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>206</v>
       </c>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB45)&gt;0,1,0)</f>
@@ -18564,10 +18564,10 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>207</v>
       </c>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB46)&gt;0,1,0)</f>
@@ -18830,10 +18830,10 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>209</v>
       </c>
@@ -19096,7 +19096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>210</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB49)&gt;0,1,0)</f>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
   </sheetData>
@@ -19633,13 +19633,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B685708-150B-4E4B-A92F-D93C2F7040BE}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.2890625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>223</v>
       </c>
@@ -19647,7 +19647,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>151</v>
       </c>
@@ -19655,7 +19655,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>159</v>
       </c>
@@ -19663,7 +19663,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>158</v>
       </c>
@@ -19671,7 +19671,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>203</v>
       </c>
@@ -19679,7 +19679,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>182</v>
       </c>
@@ -19687,7 +19687,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>215</v>
       </c>
@@ -19695,7 +19695,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>181</v>
       </c>
@@ -19703,7 +19703,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>177</v>
       </c>
@@ -19711,7 +19711,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>233</v>
       </c>
@@ -19719,7 +19719,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>190</v>
       </c>
@@ -19727,7 +19727,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>192</v>
       </c>
@@ -19735,7 +19735,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>236</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>194</v>
       </c>
@@ -19751,7 +19751,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>160</v>
       </c>
@@ -19759,7 +19759,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>211</v>
       </c>
@@ -19767,7 +19767,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>187</v>
       </c>
@@ -19775,7 +19775,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>169</v>
       </c>
@@ -19783,7 +19783,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>207</v>
       </c>
@@ -19791,7 +19791,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>167</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>185</v>
       </c>
@@ -19807,7 +19807,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>231</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>204</v>
       </c>
@@ -19823,7 +19823,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>178</v>
       </c>
@@ -19831,7 +19831,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>155</v>
       </c>
@@ -19839,7 +19839,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>201</v>
       </c>
@@ -19847,7 +19847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>115</v>
       </c>
@@ -19855,7 +19855,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>217</v>
       </c>
@@ -19863,7 +19863,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>172</v>
       </c>
@@ -19871,7 +19871,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>195</v>
       </c>
@@ -19879,7 +19879,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>232</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>214</v>
       </c>
@@ -19895,7 +19895,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>171</v>
       </c>
@@ -19903,7 +19903,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>213</v>
       </c>
@@ -19911,7 +19911,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>188</v>
       </c>
@@ -19919,7 +19919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>176</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>173</v>
       </c>
@@ -19935,7 +19935,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>216</v>
       </c>
@@ -19943,7 +19943,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>209</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>184</v>
       </c>
@@ -19959,7 +19959,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>218</v>
       </c>
@@ -19967,7 +19967,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>206</v>
       </c>
@@ -19975,7 +19975,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>210</v>
       </c>
@@ -19983,7 +19983,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>212</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>179</v>
       </c>
@@ -19999,7 +19999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>198</v>
       </c>
@@ -20007,7 +20007,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>235</v>
       </c>
@@ -20015,7 +20015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>234</v>
       </c>
@@ -20023,7 +20023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>162</v>
       </c>
@@ -20031,7 +20031,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>222</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97F5CD4-316D-6E41-A837-797711BDE8C7}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8B954A-130C-AB48-85B7-53B7F32DE475}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6360,7 +6360,7 @@
         <v>25</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -6568,7 +6568,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -6579,7 +6579,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -6590,7 +6590,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N2)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z2)&gt;0),1,0))</f>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB2)&gt;0,1,0)</f>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="CF2" s="7">
         <f>SUM(BU2:CE2)</f>
-        <v>34.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.2">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N3)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z3)&gt;0),1,0))</f>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" ref="CF3:CF49" si="0">SUM(BU3:CE3)</f>
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.2">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N4)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z4)&gt;0),1,0))</f>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB4)&gt;0,1,0)</f>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.2">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N5)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z5)&gt;0),1,0))</f>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB5)&gt;0,1,0)</f>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.2">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N6)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z6)&gt;0),1,0))</f>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB6)&gt;0,1,0)</f>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.2">
@@ -8497,11 +8497,11 @@
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z7)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB7)&gt;0,1,0)</f>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.2">
@@ -8760,11 +8760,11 @@
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z8)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0),1,0))</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB8)&gt;0,1,0)</f>
@@ -8800,7 +8800,7 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.2">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N9)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z9)&gt;0),1,0))</f>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.2">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N10)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z10)&gt;0),1,0))</f>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.2">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N11)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z11)&gt;0),1,0))</f>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.2">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N12)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z12)&gt;0),1,0))</f>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.2">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N13)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z13)&gt;0),1,0))</f>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N14)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z14)&gt;0),1,0))</f>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB14)&gt;0,1,0)</f>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.2">
@@ -10604,11 +10604,11 @@
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z15)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB15)&gt;0,1,0)</f>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.2">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z16)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0),1,0))</f>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.2">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N17)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z17)&gt;0),1,0))</f>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.2">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N18)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z18)&gt;0),1,0))</f>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB18)&gt;0,1,0)</f>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.2">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z19)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0),1,0))</f>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="CD19">
         <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE19">
         <f>IF(BR19='Resultats Reals'!$K$2,5,0)</f>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.2">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N20)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z20)&gt;0),1,0))</f>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB20)&gt;0,1,0)</f>
@@ -11962,7 +11962,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.2">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N21)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z21)&gt;0),1,0))</f>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.2">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z22)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL22)&gt;0),1,0))</f>
@@ -12488,7 +12488,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.2">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z23)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL23)&gt;0),1,0))</f>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.2">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N24)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z24)&gt;0),1,0))</f>
@@ -12978,7 +12978,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0),1,0))</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB24)&gt;0,1,0)</f>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.2">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z25)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL25)&gt;0),1,0))</f>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:84" x14ac:dyDescent="0.2">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N26)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z26)&gt;0),1,0))</f>
@@ -13543,7 +13543,7 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.2">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N27)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z27)&gt;0),1,0))</f>
@@ -13806,7 +13806,7 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.2">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N28)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z28)&gt;0),1,0))</f>
@@ -14069,7 +14069,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.2">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N29)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z29)&gt;0),1,0))</f>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.2">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N30)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z30)&gt;0),1,0))</f>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB30)&gt;0,1,0)</f>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.2">
@@ -14817,7 +14817,7 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N31)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z31)&gt;0),1,0))</f>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.2">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N32)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z32)&gt;0),1,0))</f>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB32)&gt;0,1,0)</f>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.2">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N33)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z33)&gt;0),1,0))</f>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.2">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N34)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z34)&gt;0),1,0))</f>
@@ -15659,7 +15659,7 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.2">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N35)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z35)&gt;0),1,0))</f>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.2">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N36)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z36)&gt;0),1,0))</f>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.2">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N37)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z37)&gt;0),1,0))</f>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.2">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N38)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z38)&gt;0),1,0))</f>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.2">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z39)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0),1,0))</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.2">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z40)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0),1,0))</f>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.2">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N41)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z41)&gt;0),1,0))</f>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB41)&gt;0,1,0)</f>
@@ -17509,7 +17509,7 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.2">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N42)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z42)&gt;0),1,0))</f>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.2">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N43)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z43)&gt;0),1,0))</f>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.2">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z44)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0),1,0))</f>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.2">
@@ -18520,7 +18520,7 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N45)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z45)&gt;0),1,0))</f>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.2">
@@ -18786,7 +18786,7 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N46)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z46)&gt;0),1,0))</f>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.2">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N47)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z47)&gt;0),1,0))</f>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB47)&gt;0,1,0)</f>
@@ -19093,7 +19093,7 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.2">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z48)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL48)&gt;0),1,0))</f>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.2">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N49)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z49)&gt;0),1,0))</f>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
     </row>
   </sheetData>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8B954A-130C-AB48-85B7-53B7F32DE475}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583BFA46-1FFE-704A-965E-468D1FFD2F12}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -776,6 +776,9 @@
   </si>
   <si>
     <t>Administració</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panamà </t>
   </si>
 </sst>
 </file>
@@ -5383,7 +5386,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6168,7 +6171,7 @@
         <v>13</v>
       </c>
       <c r="N5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -6612,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>138</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -7182,7 +7185,7 @@
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z2)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0),1,0))</f>
@@ -7222,7 +7225,7 @@
       </c>
       <c r="CF2" s="7">
         <f>SUM(BU2:CE2)</f>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.2">
@@ -7445,7 +7448,7 @@
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z3)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0),1,0))</f>
@@ -7485,7 +7488,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" ref="CF3:CF49" si="0">SUM(BU3:CE3)</f>
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.2">
@@ -7708,7 +7711,7 @@
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z4)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0),1,0))</f>
@@ -7748,7 +7751,7 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.2">
@@ -7971,7 +7974,7 @@
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z5)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0),1,0))</f>
@@ -8011,7 +8014,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.2">
@@ -8234,7 +8237,7 @@
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z6)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0),1,0))</f>
@@ -8274,7 +8277,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.2">
@@ -8497,7 +8500,7 @@
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z7)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0),1,0))</f>
@@ -8537,7 +8540,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.2">
@@ -8756,7 +8759,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N8)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z8)&gt;0),1,0))</f>
@@ -8800,7 +8803,7 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="9" spans="1:84" x14ac:dyDescent="0.2">
@@ -9026,7 +9029,7 @@
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z9)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0),1,0))</f>
@@ -9066,7 +9069,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.2">
@@ -9289,7 +9292,7 @@
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z10)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0),1,0))</f>
@@ -9329,7 +9332,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.2">
@@ -9552,7 +9555,7 @@
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z11)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0),1,0))</f>
@@ -9592,7 +9595,7 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="12" spans="1:84" x14ac:dyDescent="0.2">
@@ -9811,7 +9814,7 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N12)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z12)&gt;0),1,0))</f>
@@ -9855,7 +9858,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.2">
@@ -10082,7 +10085,7 @@
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL13)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB13)&gt;0,1,0)</f>
@@ -10118,7 +10121,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.2">
@@ -10341,7 +10344,7 @@
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z14)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0),1,0))</f>
@@ -10381,7 +10384,7 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.2">
@@ -10604,7 +10607,7 @@
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z15)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0),1,0))</f>
@@ -10644,7 +10647,7 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:84" x14ac:dyDescent="0.2">
@@ -10867,7 +10870,7 @@
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z16)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0),1,0))</f>
@@ -10907,7 +10910,7 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="17" spans="1:84" x14ac:dyDescent="0.2">
@@ -11396,7 +11399,7 @@
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z18)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0),1,0))</f>
@@ -11436,7 +11439,7 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="19" spans="1:84" x14ac:dyDescent="0.2">
@@ -11659,7 +11662,7 @@
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z19)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0),1,0))</f>
@@ -11699,7 +11702,7 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.2">
@@ -11922,7 +11925,7 @@
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z20)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0),1,0))</f>
@@ -11962,7 +11965,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.2">
@@ -12185,7 +12188,7 @@
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z21)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0),1,0))</f>
@@ -12225,7 +12228,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.2">
@@ -12444,7 +12447,7 @@
       </c>
       <c r="BU22">
         <f>IF(C22='Resultats Reals'!$C$2,2,IF(OR(C22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C22)&gt;0),1,0))+IF(D22='Resultats Reals'!$C$5,2,IF(OR(D22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D22)&gt;0),1,0))+IF(E22='Resultats Reals'!$C$8,2,IF(OR(E22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E22)&gt;0),1,0))+IF(F22='Resultats Reals'!$C$11,2,IF(OR(F22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F22)&gt;0),1,0))+IF(G22='Resultats Reals'!$C$14,2,IF(OR(G22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G22)&gt;0),1,0))+IF(H22='Resultats Reals'!$C$17,2,IF(OR(H22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H22)&gt;0),1,0))+IF(I22='Resultats Reals'!$C$20,2,IF(OR(I22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I22)&gt;0),1,0))+IF(J22='Resultats Reals'!$C$23,2,IF(OR(J22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J22)&gt;0),1,0))+IF(K22='Resultats Reals'!$C$26,2,IF(OR(K22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K22)&gt;0),1,0))+IF(L22='Resultats Reals'!$C$29,2,IF(OR(L22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L22)&gt;0),1,0))+IF(M22='Resultats Reals'!$C$32,2,IF(OR(M22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M22)&gt;0),1,0))+IF(N22='Resultats Reals'!$C$35,2,IF(OR(N22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N22)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z22)&gt;0),1,0))</f>
@@ -12488,7 +12491,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.2">
@@ -12707,7 +12710,7 @@
       </c>
       <c r="BU23">
         <f>IF(C23='Resultats Reals'!$C$2,2,IF(OR(C23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C23)&gt;0),1,0))+IF(D23='Resultats Reals'!$C$5,2,IF(OR(D23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D23)&gt;0),1,0))+IF(E23='Resultats Reals'!$C$8,2,IF(OR(E23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E23)&gt;0),1,0))+IF(F23='Resultats Reals'!$C$11,2,IF(OR(F23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F23)&gt;0),1,0))+IF(G23='Resultats Reals'!$C$14,2,IF(OR(G23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G23)&gt;0),1,0))+IF(H23='Resultats Reals'!$C$17,2,IF(OR(H23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H23)&gt;0),1,0))+IF(I23='Resultats Reals'!$C$20,2,IF(OR(I23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I23)&gt;0),1,0))+IF(J23='Resultats Reals'!$C$23,2,IF(OR(J23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J23)&gt;0),1,0))+IF(K23='Resultats Reals'!$C$26,2,IF(OR(K23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K23)&gt;0),1,0))+IF(L23='Resultats Reals'!$C$29,2,IF(OR(L23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L23)&gt;0),1,0))+IF(M23='Resultats Reals'!$C$32,2,IF(OR(M23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M23)&gt;0),1,0))+IF(N23='Resultats Reals'!$C$35,2,IF(OR(N23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N23)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z23)&gt;0),1,0))</f>
@@ -12743,7 +12746,7 @@
       </c>
       <c r="CD23">
         <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE23">
         <f>IF(BR23='Resultats Reals'!$K$2,5,0)</f>
@@ -12974,7 +12977,7 @@
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z24)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0),1,0))</f>
@@ -13014,7 +13017,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.2">
@@ -13233,7 +13236,7 @@
       </c>
       <c r="BU25">
         <f>IF(C25='Resultats Reals'!$C$2,2,IF(OR(C25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C25)&gt;0),1,0))+IF(D25='Resultats Reals'!$C$5,2,IF(OR(D25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D25)&gt;0),1,0))+IF(E25='Resultats Reals'!$C$8,2,IF(OR(E25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E25)&gt;0),1,0))+IF(F25='Resultats Reals'!$C$11,2,IF(OR(F25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F25)&gt;0),1,0))+IF(G25='Resultats Reals'!$C$14,2,IF(OR(G25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G25)&gt;0),1,0))+IF(H25='Resultats Reals'!$C$17,2,IF(OR(H25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H25)&gt;0),1,0))+IF(I25='Resultats Reals'!$C$20,2,IF(OR(I25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I25)&gt;0),1,0))+IF(J25='Resultats Reals'!$C$23,2,IF(OR(J25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J25)&gt;0),1,0))+IF(K25='Resultats Reals'!$C$26,2,IF(OR(K25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K25)&gt;0),1,0))+IF(L25='Resultats Reals'!$C$29,2,IF(OR(L25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L25)&gt;0),1,0))+IF(M25='Resultats Reals'!$C$32,2,IF(OR(M25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M25)&gt;0),1,0))+IF(N25='Resultats Reals'!$C$35,2,IF(OR(N25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N25)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z25)&gt;0),1,0))</f>
@@ -13277,7 +13280,7 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:84" x14ac:dyDescent="0.2">
@@ -13503,7 +13506,7 @@
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z26)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL26)&gt;0),1,0))</f>
@@ -13543,7 +13546,7 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="27" spans="1:84" x14ac:dyDescent="0.2">
@@ -13766,7 +13769,7 @@
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z27)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0),1,0))</f>
@@ -13806,7 +13809,7 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.2">
@@ -14029,7 +14032,7 @@
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z28)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0),1,0))</f>
@@ -14069,7 +14072,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.2">
@@ -14295,7 +14298,7 @@
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z29)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL29)&gt;0),1,0))</f>
@@ -14335,7 +14338,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.2">
@@ -14558,7 +14561,7 @@
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z30)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0),1,0))</f>
@@ -14598,7 +14601,7 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.2">
@@ -14821,7 +14824,7 @@
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z31)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL31)&gt;0),1,0))</f>
@@ -14861,7 +14864,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.2">
@@ -15087,7 +15090,7 @@
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z32)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0),1,0))</f>
@@ -15127,7 +15130,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.2">
@@ -15353,7 +15356,7 @@
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z33)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0),1,0))</f>
@@ -15393,7 +15396,7 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.2">
@@ -15623,7 +15626,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB34)&gt;0,1,0)</f>
@@ -15659,7 +15662,7 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:84" x14ac:dyDescent="0.2">
@@ -15882,7 +15885,7 @@
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z35)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0),1,0))</f>
@@ -15914,7 +15917,7 @@
       </c>
       <c r="CD35">
         <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE35">
         <f>IF(BR35='Resultats Reals'!$K$2,5,0)</f>
@@ -15922,7 +15925,7 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.2">
@@ -16145,7 +16148,7 @@
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z36)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL36)&gt;0),1,0))</f>
@@ -16177,7 +16180,7 @@
       </c>
       <c r="CD36">
         <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE36">
         <f>IF(BR36='Resultats Reals'!$K$2,5,0)</f>
@@ -16185,7 +16188,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.2">
@@ -16408,7 +16411,7 @@
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z37)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0),1,0))</f>
@@ -16448,7 +16451,7 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.2">
@@ -16674,7 +16677,7 @@
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z38)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL38)&gt;0),1,0))</f>
@@ -16714,7 +16717,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.2">
@@ -16940,7 +16943,7 @@
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z39)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0),1,0))</f>
@@ -16980,7 +16983,7 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.2">
@@ -17202,7 +17205,7 @@
       </c>
       <c r="BU40">
         <f>IF(C40='Resultats Reals'!$C$2,2,IF(OR(C40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C40)&gt;0),1,0))+IF(D40='Resultats Reals'!$C$5,2,IF(OR(D40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D40)&gt;0),1,0))+IF(E40='Resultats Reals'!$C$8,2,IF(OR(E40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E40)&gt;0),1,0))+IF(F40='Resultats Reals'!$C$11,2,IF(OR(F40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F40)&gt;0),1,0))+IF(G40='Resultats Reals'!$C$14,2,IF(OR(G40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G40)&gt;0),1,0))+IF(H40='Resultats Reals'!$C$17,2,IF(OR(H40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H40)&gt;0),1,0))+IF(I40='Resultats Reals'!$C$20,2,IF(OR(I40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I40)&gt;0),1,0))+IF(J40='Resultats Reals'!$C$23,2,IF(OR(J40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J40)&gt;0),1,0))+IF(K40='Resultats Reals'!$C$26,2,IF(OR(K40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K40)&gt;0),1,0))+IF(L40='Resultats Reals'!$C$29,2,IF(OR(L40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L40)&gt;0),1,0))+IF(M40='Resultats Reals'!$C$32,2,IF(OR(M40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M40)&gt;0),1,0))+IF(N40='Resultats Reals'!$C$35,2,IF(OR(N40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N40)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z40)&gt;0),1,0))</f>
@@ -17246,7 +17249,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.2">
@@ -17469,7 +17472,7 @@
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z41)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0),1,0))</f>
@@ -17509,7 +17512,7 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.2">
@@ -17732,7 +17735,7 @@
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z42)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0),1,0))</f>
@@ -17772,7 +17775,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.2">
@@ -17998,7 +18001,7 @@
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z43)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0),1,0))</f>
@@ -18030,7 +18033,7 @@
       </c>
       <c r="CD43">
         <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE43">
         <f>IF(BR43='Resultats Reals'!$K$2,5,0)</f>
@@ -18038,7 +18041,7 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.2">
@@ -18261,7 +18264,7 @@
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z44)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0),1,0))</f>
@@ -18301,7 +18304,7 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:84" x14ac:dyDescent="0.2">
@@ -18524,7 +18527,7 @@
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z45)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0),1,0))</f>
@@ -18556,7 +18559,7 @@
       </c>
       <c r="CD45">
         <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE45">
         <f>IF(BR45='Resultats Reals'!$K$2,5,0)</f>
@@ -18564,7 +18567,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.2">
@@ -18790,7 +18793,7 @@
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z46)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0),1,0))</f>
@@ -18830,7 +18833,7 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.2">
@@ -19053,7 +19056,7 @@
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z47)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0),1,0))</f>
@@ -19093,7 +19096,7 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.2">
@@ -19320,7 +19323,7 @@
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL48)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB48)&gt;0,1,0)</f>
@@ -19356,7 +19359,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.2">
@@ -19582,7 +19585,7 @@
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z49)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0),1,0))</f>
@@ -19622,7 +19625,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
     </row>
   </sheetData>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583BFA46-1FFE-704A-965E-468D1FFD2F12}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB30C6A-DE91-0D4E-9A20-6B04A3C137AA}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5386,7 +5386,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6171,7 +6171,7 @@
         <v>13</v>
       </c>
       <c r="N5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="CD23">
         <f>IFERROR(VLOOKUP(BT23,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE23">
         <f>IF(BR23='Resultats Reals'!$K$2,5,0)</f>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.2">
@@ -15917,7 +15917,7 @@
       </c>
       <c r="CD35">
         <f>IFERROR(VLOOKUP(BT35,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE35">
         <f>IF(BR35='Resultats Reals'!$K$2,5,0)</f>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.2">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="CD36">
         <f>IFERROR(VLOOKUP(BT36,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE36">
         <f>IF(BR36='Resultats Reals'!$K$2,5,0)</f>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.2">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="CD43">
         <f>IFERROR(VLOOKUP(BT43,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE43">
         <f>IF(BR43='Resultats Reals'!$K$2,5,0)</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.2">
@@ -18559,7 +18559,7 @@
       </c>
       <c r="CD45">
         <f>IFERROR(VLOOKUP(BT45,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE45">
         <f>IF(BR45='Resultats Reals'!$K$2,5,0)</f>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.2">

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BB30C6A-DE91-0D4E-9A20-6B04A3C137AA}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31ABCF45-F4D2-964E-BF53-6CD18288EE02}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5386,7 +5386,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6571,7 +6571,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -6582,7 +6582,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -6593,7 +6593,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -6615,7 +6615,7 @@
         <v>8</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>245</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -6626,7 +6626,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>150</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -7181,15 +7181,15 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N2)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z2)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL2)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB2)&gt;0,1,0)</f>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="CF2" s="7">
         <f>SUM(BU2:CE2)</f>
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3" spans="1:84" x14ac:dyDescent="0.2">
@@ -7444,15 +7444,15 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N3)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z3)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL3)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB3)&gt;0,1,0)</f>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" ref="CF3:CF49" si="0">SUM(BU3:CE3)</f>
-        <v>36.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:84" x14ac:dyDescent="0.2">
@@ -7707,15 +7707,15 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N4)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z4)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL4)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB4)&gt;0,1,0)</f>
@@ -7751,7 +7751,7 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="5" spans="1:84" x14ac:dyDescent="0.2">
@@ -7970,15 +7970,15 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N5)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z5)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL5)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB5)&gt;0,1,0)</f>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:84" x14ac:dyDescent="0.2">
@@ -8233,15 +8233,15 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N6)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z6)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL6)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB6)&gt;0,1,0)</f>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:84" x14ac:dyDescent="0.2">
@@ -8496,15 +8496,15 @@
       </c>
       <c r="BU7">
         <f>IF(C7='Resultats Reals'!$C$2,2,IF(OR(C7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C7)&gt;0),1,0))+IF(D7='Resultats Reals'!$C$5,2,IF(OR(D7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D7)&gt;0),1,0))+IF(E7='Resultats Reals'!$C$8,2,IF(OR(E7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E7)&gt;0),1,0))+IF(F7='Resultats Reals'!$C$11,2,IF(OR(F7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F7)&gt;0),1,0))+IF(G7='Resultats Reals'!$C$14,2,IF(OR(G7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G7)&gt;0),1,0))+IF(H7='Resultats Reals'!$C$17,2,IF(OR(H7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H7)&gt;0),1,0))+IF(I7='Resultats Reals'!$C$20,2,IF(OR(I7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I7)&gt;0),1,0))+IF(J7='Resultats Reals'!$C$23,2,IF(OR(J7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J7)&gt;0),1,0))+IF(K7='Resultats Reals'!$C$26,2,IF(OR(K7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K7)&gt;0),1,0))+IF(L7='Resultats Reals'!$C$29,2,IF(OR(L7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L7)&gt;0),1,0))+IF(M7='Resultats Reals'!$C$32,2,IF(OR(M7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M7)&gt;0),1,0))+IF(N7='Resultats Reals'!$C$35,2,IF(OR(N7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N7)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BV7">
         <f>IF(O7='Resultats Reals'!$C$3,2,IF(OR(O7='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O7)&gt;0),1,0))+IF(P7='Resultats Reals'!$C$6,2,IF(OR(P7='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P7)&gt;0),1,0))+IF(Q7='Resultats Reals'!$C$9,2,IF(OR(Q7='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q7)&gt;0),1,0))+IF(R7='Resultats Reals'!$C$12,2,IF(OR(R7='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R7)&gt;0),1,0))+IF(S7='Resultats Reals'!$C$15,2,IF(OR(S7='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S7)&gt;0),1,0))+IF(T7='Resultats Reals'!$C$18,2,IF(OR(T7='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T7)&gt;0),1,0))+IF(U7='Resultats Reals'!$C$21,2,IF(OR(U7='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U7)&gt;0),1,0))+IF(V7='Resultats Reals'!$C$24,2,IF(OR(V7='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V7)&gt;0),1,0))+IF(W7='Resultats Reals'!$C$27,2,IF(OR(W7='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W7)&gt;0),1,0))+IF(X7='Resultats Reals'!$C$30,2,IF(OR(X7='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X7)&gt;0),1,0))+IF(Y7='Resultats Reals'!$C$33,2,IF(OR(Y7='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y7)&gt;0),1,0))+IF(Z7='Resultats Reals'!$C$36,2,IF(OR(Z7='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z7)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL7)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB7)&gt;0,1,0)</f>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="8" spans="1:84" x14ac:dyDescent="0.2">
@@ -8759,11 +8759,11 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N8)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z8)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL8)&gt;0),1,0))</f>
@@ -9025,15 +9025,15 @@
       </c>
       <c r="BU9">
         <f>IF(C9='Resultats Reals'!$C$2,2,IF(OR(C9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C9)&gt;0),1,0))+IF(D9='Resultats Reals'!$C$5,2,IF(OR(D9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D9)&gt;0),1,0))+IF(E9='Resultats Reals'!$C$8,2,IF(OR(E9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E9)&gt;0),1,0))+IF(F9='Resultats Reals'!$C$11,2,IF(OR(F9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F9)&gt;0),1,0))+IF(G9='Resultats Reals'!$C$14,2,IF(OR(G9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G9)&gt;0),1,0))+IF(H9='Resultats Reals'!$C$17,2,IF(OR(H9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H9)&gt;0),1,0))+IF(I9='Resultats Reals'!$C$20,2,IF(OR(I9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I9)&gt;0),1,0))+IF(J9='Resultats Reals'!$C$23,2,IF(OR(J9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J9)&gt;0),1,0))+IF(K9='Resultats Reals'!$C$26,2,IF(OR(K9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K9)&gt;0),1,0))+IF(L9='Resultats Reals'!$C$29,2,IF(OR(L9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L9)&gt;0),1,0))+IF(M9='Resultats Reals'!$C$32,2,IF(OR(M9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M9)&gt;0),1,0))+IF(N9='Resultats Reals'!$C$35,2,IF(OR(N9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N9)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV9">
         <f>IF(O9='Resultats Reals'!$C$3,2,IF(OR(O9='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O9)&gt;0),1,0))+IF(P9='Resultats Reals'!$C$6,2,IF(OR(P9='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P9)&gt;0),1,0))+IF(Q9='Resultats Reals'!$C$9,2,IF(OR(Q9='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q9)&gt;0),1,0))+IF(R9='Resultats Reals'!$C$12,2,IF(OR(R9='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R9)&gt;0),1,0))+IF(S9='Resultats Reals'!$C$15,2,IF(OR(S9='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S9)&gt;0),1,0))+IF(T9='Resultats Reals'!$C$18,2,IF(OR(T9='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T9)&gt;0),1,0))+IF(U9='Resultats Reals'!$C$21,2,IF(OR(U9='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U9)&gt;0),1,0))+IF(V9='Resultats Reals'!$C$24,2,IF(OR(V9='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V9)&gt;0),1,0))+IF(W9='Resultats Reals'!$C$27,2,IF(OR(W9='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W9)&gt;0),1,0))+IF(X9='Resultats Reals'!$C$30,2,IF(OR(X9='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X9)&gt;0),1,0))+IF(Y9='Resultats Reals'!$C$33,2,IF(OR(Y9='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y9)&gt;0),1,0))+IF(Z9='Resultats Reals'!$C$36,2,IF(OR(Z9='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z9)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL9)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB9)&gt;0,1,0)</f>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="10" spans="1:84" x14ac:dyDescent="0.2">
@@ -9288,15 +9288,15 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N10)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z10)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL10)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB10)&gt;0,1,0)</f>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:84" x14ac:dyDescent="0.2">
@@ -9551,11 +9551,11 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N11)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z11)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL11)&gt;0),1,0))</f>
@@ -9814,15 +9814,15 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N12)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z12)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL12)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB12)&gt;0,1,0)</f>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="13" spans="1:84" x14ac:dyDescent="0.2">
@@ -10077,11 +10077,11 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N13)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z13)&gt;0),1,0))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL13)&gt;0),1,0))</f>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="14" spans="1:84" x14ac:dyDescent="0.2">
@@ -10340,15 +10340,15 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N14)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z14)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL14)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB14)&gt;0,1,0)</f>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="15" spans="1:84" x14ac:dyDescent="0.2">
@@ -10603,11 +10603,11 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N15)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z15)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL15)&gt;0),1,0))</f>
@@ -10866,11 +10866,11 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N16)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z16)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL16)&gt;0),1,0))</f>
@@ -11129,15 +11129,15 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N17)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z17)&gt;0),1,0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL17)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX17">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB17)&gt;0,1,0)</f>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="18" spans="1:84" x14ac:dyDescent="0.2">
@@ -11395,11 +11395,11 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N18)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z18)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL18)&gt;0),1,0))</f>
@@ -11658,15 +11658,15 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N19)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z19)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL19)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB19)&gt;0,1,0)</f>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="20" spans="1:84" x14ac:dyDescent="0.2">
@@ -11921,15 +11921,15 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N20)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z20)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL20)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB20)&gt;0,1,0)</f>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:84" x14ac:dyDescent="0.2">
@@ -12184,15 +12184,15 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N21)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z21)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL21)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB21)&gt;0,1,0)</f>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="22" spans="1:84" x14ac:dyDescent="0.2">
@@ -12447,15 +12447,15 @@
       </c>
       <c r="BU22">
         <f>IF(C22='Resultats Reals'!$C$2,2,IF(OR(C22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C22)&gt;0),1,0))+IF(D22='Resultats Reals'!$C$5,2,IF(OR(D22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D22)&gt;0),1,0))+IF(E22='Resultats Reals'!$C$8,2,IF(OR(E22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E22)&gt;0),1,0))+IF(F22='Resultats Reals'!$C$11,2,IF(OR(F22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F22)&gt;0),1,0))+IF(G22='Resultats Reals'!$C$14,2,IF(OR(G22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G22)&gt;0),1,0))+IF(H22='Resultats Reals'!$C$17,2,IF(OR(H22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H22)&gt;0),1,0))+IF(I22='Resultats Reals'!$C$20,2,IF(OR(I22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I22)&gt;0),1,0))+IF(J22='Resultats Reals'!$C$23,2,IF(OR(J22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J22)&gt;0),1,0))+IF(K22='Resultats Reals'!$C$26,2,IF(OR(K22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K22)&gt;0),1,0))+IF(L22='Resultats Reals'!$C$29,2,IF(OR(L22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L22)&gt;0),1,0))+IF(M22='Resultats Reals'!$C$32,2,IF(OR(M22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M22)&gt;0),1,0))+IF(N22='Resultats Reals'!$C$35,2,IF(OR(N22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N22)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z22)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL22)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX22">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA22)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB22)&gt;0,1,0)</f>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="23" spans="1:84" x14ac:dyDescent="0.2">
@@ -12710,15 +12710,15 @@
       </c>
       <c r="BU23">
         <f>IF(C23='Resultats Reals'!$C$2,2,IF(OR(C23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C23)&gt;0),1,0))+IF(D23='Resultats Reals'!$C$5,2,IF(OR(D23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D23)&gt;0),1,0))+IF(E23='Resultats Reals'!$C$8,2,IF(OR(E23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E23)&gt;0),1,0))+IF(F23='Resultats Reals'!$C$11,2,IF(OR(F23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F23)&gt;0),1,0))+IF(G23='Resultats Reals'!$C$14,2,IF(OR(G23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G23)&gt;0),1,0))+IF(H23='Resultats Reals'!$C$17,2,IF(OR(H23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H23)&gt;0),1,0))+IF(I23='Resultats Reals'!$C$20,2,IF(OR(I23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I23)&gt;0),1,0))+IF(J23='Resultats Reals'!$C$23,2,IF(OR(J23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J23)&gt;0),1,0))+IF(K23='Resultats Reals'!$C$26,2,IF(OR(K23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K23)&gt;0),1,0))+IF(L23='Resultats Reals'!$C$29,2,IF(OR(L23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L23)&gt;0),1,0))+IF(M23='Resultats Reals'!$C$32,2,IF(OR(M23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M23)&gt;0),1,0))+IF(N23='Resultats Reals'!$C$35,2,IF(OR(N23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N23)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z23)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL23)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX23">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA23)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB23)&gt;0,1,0)</f>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="24" spans="1:84" x14ac:dyDescent="0.2">
@@ -12973,15 +12973,15 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N24)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z24)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL24)&gt;0),1,0))</f>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB24)&gt;0,1,0)</f>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:84" x14ac:dyDescent="0.2">
@@ -13236,15 +13236,15 @@
       </c>
       <c r="BU25">
         <f>IF(C25='Resultats Reals'!$C$2,2,IF(OR(C25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C25)&gt;0),1,0))+IF(D25='Resultats Reals'!$C$5,2,IF(OR(D25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D25)&gt;0),1,0))+IF(E25='Resultats Reals'!$C$8,2,IF(OR(E25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E25)&gt;0),1,0))+IF(F25='Resultats Reals'!$C$11,2,IF(OR(F25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F25)&gt;0),1,0))+IF(G25='Resultats Reals'!$C$14,2,IF(OR(G25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G25)&gt;0),1,0))+IF(H25='Resultats Reals'!$C$17,2,IF(OR(H25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H25)&gt;0),1,0))+IF(I25='Resultats Reals'!$C$20,2,IF(OR(I25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I25)&gt;0),1,0))+IF(J25='Resultats Reals'!$C$23,2,IF(OR(J25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J25)&gt;0),1,0))+IF(K25='Resultats Reals'!$C$26,2,IF(OR(K25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K25)&gt;0),1,0))+IF(L25='Resultats Reals'!$C$29,2,IF(OR(L25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L25)&gt;0),1,0))+IF(M25='Resultats Reals'!$C$32,2,IF(OR(M25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M25)&gt;0),1,0))+IF(N25='Resultats Reals'!$C$35,2,IF(OR(N25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N25)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z25)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL25)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX25">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA25)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB25)&gt;0,1,0)</f>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="26" spans="1:84" x14ac:dyDescent="0.2">
@@ -13502,11 +13502,11 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N26)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z26)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL26)&gt;0),1,0))</f>
@@ -13765,15 +13765,15 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N27)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z27)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL27)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB27)&gt;0,1,0)</f>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="28" spans="1:84" x14ac:dyDescent="0.2">
@@ -14028,15 +14028,15 @@
       </c>
       <c r="BU28">
         <f>IF(C28='Resultats Reals'!$C$2,2,IF(OR(C28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C28)&gt;0),1,0))+IF(D28='Resultats Reals'!$C$5,2,IF(OR(D28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D28)&gt;0),1,0))+IF(E28='Resultats Reals'!$C$8,2,IF(OR(E28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E28)&gt;0),1,0))+IF(F28='Resultats Reals'!$C$11,2,IF(OR(F28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F28)&gt;0),1,0))+IF(G28='Resultats Reals'!$C$14,2,IF(OR(G28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G28)&gt;0),1,0))+IF(H28='Resultats Reals'!$C$17,2,IF(OR(H28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H28)&gt;0),1,0))+IF(I28='Resultats Reals'!$C$20,2,IF(OR(I28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I28)&gt;0),1,0))+IF(J28='Resultats Reals'!$C$23,2,IF(OR(J28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J28)&gt;0),1,0))+IF(K28='Resultats Reals'!$C$26,2,IF(OR(K28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K28)&gt;0),1,0))+IF(L28='Resultats Reals'!$C$29,2,IF(OR(L28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L28)&gt;0),1,0))+IF(M28='Resultats Reals'!$C$32,2,IF(OR(M28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M28)&gt;0),1,0))+IF(N28='Resultats Reals'!$C$35,2,IF(OR(N28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N28)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV28">
         <f>IF(O28='Resultats Reals'!$C$3,2,IF(OR(O28='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O28)&gt;0),1,0))+IF(P28='Resultats Reals'!$C$6,2,IF(OR(P28='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P28)&gt;0),1,0))+IF(Q28='Resultats Reals'!$C$9,2,IF(OR(Q28='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q28)&gt;0),1,0))+IF(R28='Resultats Reals'!$C$12,2,IF(OR(R28='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R28)&gt;0),1,0))+IF(S28='Resultats Reals'!$C$15,2,IF(OR(S28='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S28)&gt;0),1,0))+IF(T28='Resultats Reals'!$C$18,2,IF(OR(T28='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T28)&gt;0),1,0))+IF(U28='Resultats Reals'!$C$21,2,IF(OR(U28='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U28)&gt;0),1,0))+IF(V28='Resultats Reals'!$C$24,2,IF(OR(V28='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V28)&gt;0),1,0))+IF(W28='Resultats Reals'!$C$27,2,IF(OR(W28='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W28)&gt;0),1,0))+IF(X28='Resultats Reals'!$C$30,2,IF(OR(X28='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X28)&gt;0),1,0))+IF(Y28='Resultats Reals'!$C$33,2,IF(OR(Y28='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y28)&gt;0),1,0))+IF(Z28='Resultats Reals'!$C$36,2,IF(OR(Z28='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z28)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL28)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB28)&gt;0,1,0)</f>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:84" x14ac:dyDescent="0.2">
@@ -14294,15 +14294,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N29)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z29)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL29)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB29)&gt;0,1,0)</f>
@@ -14338,7 +14338,7 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="30" spans="1:84" x14ac:dyDescent="0.2">
@@ -14557,15 +14557,15 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N30)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z30)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL30)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB30)&gt;0,1,0)</f>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:84" x14ac:dyDescent="0.2">
@@ -14820,15 +14820,15 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N31)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z31)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL31)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX31">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB31)&gt;0,1,0)</f>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="32" spans="1:84" x14ac:dyDescent="0.2">
@@ -15086,15 +15086,15 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N32)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z32)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL32)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB32)&gt;0,1,0)</f>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="33" spans="1:84" x14ac:dyDescent="0.2">
@@ -15352,15 +15352,15 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N33)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z33)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL33)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB33)&gt;0,1,0)</f>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="34" spans="1:84" x14ac:dyDescent="0.2">
@@ -15618,11 +15618,11 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N34)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z34)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL34)&gt;0),1,0))</f>
@@ -15881,15 +15881,15 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N35)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z35)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL35)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB35)&gt;0,1,0)</f>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:84" x14ac:dyDescent="0.2">
@@ -16144,15 +16144,15 @@
       </c>
       <c r="BU36">
         <f>IF(C36='Resultats Reals'!$C$2,2,IF(OR(C36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C36)&gt;0),1,0))+IF(D36='Resultats Reals'!$C$5,2,IF(OR(D36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D36)&gt;0),1,0))+IF(E36='Resultats Reals'!$C$8,2,IF(OR(E36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E36)&gt;0),1,0))+IF(F36='Resultats Reals'!$C$11,2,IF(OR(F36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F36)&gt;0),1,0))+IF(G36='Resultats Reals'!$C$14,2,IF(OR(G36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G36)&gt;0),1,0))+IF(H36='Resultats Reals'!$C$17,2,IF(OR(H36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H36)&gt;0),1,0))+IF(I36='Resultats Reals'!$C$20,2,IF(OR(I36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I36)&gt;0),1,0))+IF(J36='Resultats Reals'!$C$23,2,IF(OR(J36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J36)&gt;0),1,0))+IF(K36='Resultats Reals'!$C$26,2,IF(OR(K36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K36)&gt;0),1,0))+IF(L36='Resultats Reals'!$C$29,2,IF(OR(L36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L36)&gt;0),1,0))+IF(M36='Resultats Reals'!$C$32,2,IF(OR(M36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M36)&gt;0),1,0))+IF(N36='Resultats Reals'!$C$35,2,IF(OR(N36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N36)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV36">
         <f>IF(O36='Resultats Reals'!$C$3,2,IF(OR(O36='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O36)&gt;0),1,0))+IF(P36='Resultats Reals'!$C$6,2,IF(OR(P36='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P36)&gt;0),1,0))+IF(Q36='Resultats Reals'!$C$9,2,IF(OR(Q36='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q36)&gt;0),1,0))+IF(R36='Resultats Reals'!$C$12,2,IF(OR(R36='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R36)&gt;0),1,0))+IF(S36='Resultats Reals'!$C$15,2,IF(OR(S36='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S36)&gt;0),1,0))+IF(T36='Resultats Reals'!$C$18,2,IF(OR(T36='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T36)&gt;0),1,0))+IF(U36='Resultats Reals'!$C$21,2,IF(OR(U36='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U36)&gt;0),1,0))+IF(V36='Resultats Reals'!$C$24,2,IF(OR(V36='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V36)&gt;0),1,0))+IF(W36='Resultats Reals'!$C$27,2,IF(OR(W36='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W36)&gt;0),1,0))+IF(X36='Resultats Reals'!$C$30,2,IF(OR(X36='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X36)&gt;0),1,0))+IF(Y36='Resultats Reals'!$C$33,2,IF(OR(Y36='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y36)&gt;0),1,0))+IF(Z36='Resultats Reals'!$C$36,2,IF(OR(Z36='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z36)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL36)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB36)&gt;0,1,0)</f>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:84" x14ac:dyDescent="0.2">
@@ -16407,15 +16407,15 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N37)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z37)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL37)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB37)&gt;0,1,0)</f>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:84" x14ac:dyDescent="0.2">
@@ -16673,15 +16673,15 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N38)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z38)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL38)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB38)&gt;0,1,0)</f>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:84" x14ac:dyDescent="0.2">
@@ -16939,15 +16939,15 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N39)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z39)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL39)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB39)&gt;0,1,0)</f>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:84" x14ac:dyDescent="0.2">
@@ -17205,15 +17205,15 @@
       </c>
       <c r="BU40">
         <f>IF(C40='Resultats Reals'!$C$2,2,IF(OR(C40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C40)&gt;0),1,0))+IF(D40='Resultats Reals'!$C$5,2,IF(OR(D40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D40)&gt;0),1,0))+IF(E40='Resultats Reals'!$C$8,2,IF(OR(E40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E40)&gt;0),1,0))+IF(F40='Resultats Reals'!$C$11,2,IF(OR(F40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F40)&gt;0),1,0))+IF(G40='Resultats Reals'!$C$14,2,IF(OR(G40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G40)&gt;0),1,0))+IF(H40='Resultats Reals'!$C$17,2,IF(OR(H40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H40)&gt;0),1,0))+IF(I40='Resultats Reals'!$C$20,2,IF(OR(I40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I40)&gt;0),1,0))+IF(J40='Resultats Reals'!$C$23,2,IF(OR(J40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J40)&gt;0),1,0))+IF(K40='Resultats Reals'!$C$26,2,IF(OR(K40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K40)&gt;0),1,0))+IF(L40='Resultats Reals'!$C$29,2,IF(OR(L40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L40)&gt;0),1,0))+IF(M40='Resultats Reals'!$C$32,2,IF(OR(M40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M40)&gt;0),1,0))+IF(N40='Resultats Reals'!$C$35,2,IF(OR(N40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N40)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z40)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL40)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB40)&gt;0,1,0)</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:84" x14ac:dyDescent="0.2">
@@ -17468,15 +17468,15 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N41)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z41)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL41)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB41)&gt;0,1,0)</f>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="42" spans="1:84" x14ac:dyDescent="0.2">
@@ -17731,15 +17731,15 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N42)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z42)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL42)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB42)&gt;0,1,0)</f>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:84" x14ac:dyDescent="0.2">
@@ -17997,15 +17997,15 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N43)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z43)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL43)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB43)&gt;0,1,0)</f>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:84" x14ac:dyDescent="0.2">
@@ -18260,11 +18260,11 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N44)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z44)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL44)&gt;0),1,0))</f>
@@ -18523,15 +18523,15 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N45)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z45)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL45)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB45)&gt;0,1,0)</f>
@@ -18567,7 +18567,7 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="46" spans="1:84" x14ac:dyDescent="0.2">
@@ -18789,15 +18789,15 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N46)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z46)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL46)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB46)&gt;0,1,0)</f>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:84" x14ac:dyDescent="0.2">
@@ -19052,15 +19052,15 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N47)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z47)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL47)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB47)&gt;0,1,0)</f>
@@ -19096,7 +19096,7 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>26.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:84" x14ac:dyDescent="0.2">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N48)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z48)&gt;0),1,0))</f>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.2">
@@ -19581,15 +19581,15 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N49)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$17,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$17,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$17,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$17,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$17,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$17,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$17,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$17,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$17,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$17,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$17,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$17,Z49)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,AL49)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$E$2:$E$17,BB49)&gt;0,1,0)</f>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31ABCF45-F4D2-964E-BF53-6CD18288EE02}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{C2D31FD4-C9ED-4BA7-BCD4-E33D8656D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E3B8DC-46B2-1043-A87B-FF4A963457F8}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5386,7 +5386,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFFCF57E-C36F-4EF8-AEAB-FCFB0875ACC7}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -19308,10 +19308,10 @@
         <v>122</v>
       </c>
       <c r="BS48" t="s">
+        <v>17</v>
+      </c>
+      <c r="BT48" t="s">
         <v>15</v>
-      </c>
-      <c r="BT48" t="s">
-        <v>17</v>
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$17,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$17,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$17,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$17,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$17,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$17,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$17,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$17,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$17,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$17,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$17,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$17,N48)&gt;0),1,0))</f>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="CD48">
         <f>IFERROR(VLOOKUP(BT48,'Resultats Reals'!$M$2:$N$100,2,FALSE),0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE48">
         <f>IF(BR48='Resultats Reals'!$K$2,5,0)</f>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="49" spans="1:84" x14ac:dyDescent="0.2">

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3AC0F75-9892-45D7-914D-FC2256B7A251}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90846946-BB60-6E4E-A735-2CB702BF1354}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gràfics!$A$1:$B$49</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -5400,7 +5400,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6008,24 +6008,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="1" max="2" width="9.953125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.953125" customWidth="1"/>
+    <col min="5" max="6" width="16.0078125" customWidth="1"/>
+    <col min="7" max="7" width="14.9296875" customWidth="1"/>
+    <col min="8" max="8" width="13.98828125" customWidth="1"/>
+    <col min="9" max="9" width="18.96484375" customWidth="1"/>
+    <col min="10" max="10" width="14.9296875" customWidth="1"/>
+    <col min="11" max="11" width="11.97265625" customWidth="1"/>
+    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.953125" customWidth="1"/>
+    <col min="14" max="14" width="18.96484375" customWidth="1"/>
+    <col min="15" max="15" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6066,7 +6066,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6231,7 +6231,7 @@
         <v>231</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>100</v>
@@ -6249,7 +6249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6436,7 +6436,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6487,7 +6487,7 @@
         <v>Noruega</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>França</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>Àustria</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>Colòmbia</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>RD Congo</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6577,7 +6577,7 @@
         <v>Anglaterra</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6621,7 +6621,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6663,7 +6663,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6705,7 +6705,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6789,81 +6789,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.45703125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7377,10 +7377,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>39</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7640,10 +7640,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7903,10 +7903,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8166,10 +8166,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8429,10 +8429,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8692,10 +8692,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8919,7 +8919,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -8955,10 +8955,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9221,10 +9221,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
@@ -9747,10 +9747,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10273,10 +10273,10 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>38.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>157</v>
       </c>
@@ -10802,7 +10802,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11062,10 +11062,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -11289,7 +11289,7 @@
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX17">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
@@ -11325,10 +11325,10 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
@@ -11591,10 +11591,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -11854,10 +11854,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12117,10 +12117,10 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -12383,7 +12383,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -12909,7 +12909,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13169,10 +13169,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>175</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13698,10 +13698,10 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -13964,7 +13964,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>179</v>
       </c>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14224,10 +14224,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>181</v>
       </c>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14490,10 +14490,10 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14717,7 +14717,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14753,10 +14753,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -15019,7 +15019,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15282,10 +15282,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -15551,7 +15551,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15814,10 +15814,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -16080,7 +16080,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16340,10 +16340,10 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16603,10 +16603,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -16833,7 +16833,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16869,10 +16869,10 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -17138,7 +17138,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17401,10 +17401,10 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
@@ -17664,10 +17664,10 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17927,10 +17927,10 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
@@ -18193,10 +18193,10 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18456,10 +18456,10 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>209</v>
       </c>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18719,10 +18719,10 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -18985,10 +18985,10 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -19251,7 +19251,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19511,10 +19511,10 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -19741,7 +19741,7 @@
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -19788,13 +19788,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.2890625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>244</v>
       </c>
@@ -19802,7 +19802,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>124</v>
       </c>
@@ -19810,7 +19810,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
@@ -19818,7 +19818,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
@@ -19826,7 +19826,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>138</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
@@ -19842,7 +19842,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>206</v>
       </c>
@@ -19850,7 +19850,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>174</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
@@ -19866,7 +19866,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>189</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>185</v>
       </c>
@@ -19882,7 +19882,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>192</v>
       </c>
@@ -19898,7 +19898,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>137</v>
       </c>
@@ -19906,7 +19906,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>179</v>
       </c>
@@ -19914,7 +19914,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>147</v>
       </c>
@@ -19922,7 +19922,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>202</v>
       </c>
@@ -19930,7 +19930,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>166</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>191</v>
       </c>
@@ -19946,7 +19946,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>156</v>
       </c>
@@ -19954,7 +19954,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>176</v>
       </c>
@@ -19962,7 +19962,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>210</v>
       </c>
@@ -19970,7 +19970,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>196</v>
       </c>
@@ -19978,7 +19978,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>150</v>
       </c>
@@ -19986,7 +19986,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>130</v>
       </c>
@@ -19994,7 +19994,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>159</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>154</v>
       </c>
@@ -20010,7 +20010,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>157</v>
       </c>
@@ -20018,7 +20018,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>169</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>214</v>
       </c>
@@ -20034,7 +20034,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>198</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>203</v>
       </c>
@@ -20050,7 +20050,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>84</v>
       </c>
@@ -20058,7 +20058,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>168</v>
       </c>
@@ -20066,7 +20066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>209</v>
       </c>
@@ -20074,7 +20074,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>160</v>
       </c>
@@ -20082,7 +20082,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>181</v>
       </c>
@@ -20090,7 +20090,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>184</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>187</v>
       </c>
@@ -20106,7 +20106,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
@@ -20114,7 +20114,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
@@ -20122,7 +20122,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>153</v>
       </c>
@@ -20130,7 +20130,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>178</v>
       </c>
@@ -20138,7 +20138,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>182</v>
       </c>
@@ -20146,7 +20146,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>213</v>
       </c>
@@ -20154,7 +20154,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>170</v>
       </c>
@@ -20162,7 +20162,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>172</v>
       </c>
@@ -20170,7 +20170,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>175</v>
       </c>
@@ -20178,7 +20178,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
@@ -20186,7 +20186,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>246</v>
       </c>
@@ -20203,247 +20203,247 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>247</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90846946-BB60-6E4E-A735-2CB702BF1354}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6287A4CF-6CB1-478C-BA13-FA1DE3F3EDCE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -904,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -926,7 +926,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6008,24 +6007,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.953125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.953125" customWidth="1"/>
-    <col min="5" max="6" width="16.0078125" customWidth="1"/>
-    <col min="7" max="7" width="14.9296875" customWidth="1"/>
-    <col min="8" max="8" width="13.98828125" customWidth="1"/>
-    <col min="9" max="9" width="18.96484375" customWidth="1"/>
-    <col min="10" max="10" width="14.9296875" customWidth="1"/>
-    <col min="11" max="11" width="11.97265625" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.953125" customWidth="1"/>
-    <col min="14" max="14" width="18.96484375" customWidth="1"/>
-    <col min="15" max="15" width="9.953125" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6066,7 +6065,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6107,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6139,7 +6138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6197,7 +6196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6223,7 +6222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6249,7 +6248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6275,7 +6274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6301,7 +6300,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6347,7 +6346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6370,7 +6369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6394,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6418,7 +6417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6436,7 +6435,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6454,7 +6453,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6487,7 +6486,7 @@
         <v>Noruega</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6502,7 +6501,7 @@
         <v>França</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6532,7 +6531,7 @@
         <v>Àustria</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6547,7 +6546,7 @@
         <v>Colòmbia</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>RD Congo</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6577,7 +6576,7 @@
         <v>Anglaterra</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6592,7 +6591,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6603,11 +6602,11 @@
         <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6621,7 +6620,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6635,7 +6634,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6649,7 +6648,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6663,7 +6662,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6677,7 +6676,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6691,7 +6690,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6705,7 +6704,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6716,7 +6715,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6727,7 +6726,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6738,7 +6737,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6789,81 +6788,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.45703125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7117,7 +7116,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7341,7 +7340,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7377,10 +7376,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>39.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7604,7 +7603,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7640,10 +7639,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7867,7 +7866,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7903,10 +7902,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8130,7 +8129,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8166,10 +8165,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8393,7 +8392,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8429,10 +8428,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8656,7 +8655,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8692,10 +8691,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8919,7 +8918,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -8955,10 +8954,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30.5</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9185,7 +9184,7 @@
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9221,10 +9220,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9444,7 +9443,7 @@
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
@@ -9484,10 +9483,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9711,7 +9710,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
@@ -9747,10 +9746,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -9970,7 +9969,7 @@
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
@@ -10010,10 +10009,10 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -10237,7 +10236,7 @@
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10273,10 +10272,10 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -10496,7 +10495,7 @@
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
@@ -10536,10 +10535,10 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>157</v>
       </c>
@@ -10759,7 +10758,7 @@
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
@@ -10799,10 +10798,10 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -11026,7 +11025,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11062,10 +11061,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -11289,7 +11288,7 @@
       </c>
       <c r="BW17">
         <f>IF(AA17='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0,2,0.5),IF(OR(AA17='Resultats Reals'!$C$2,AA17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA17)&gt;0),1,0))+IF(AB17='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0,2,0.5),IF(OR(AB17='Resultats Reals'!$C$5,AB17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB17)&gt;0),1,0))+IF(AC17='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0,2,0.5),IF(OR(AC17='Resultats Reals'!$C$8,AC17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC17)&gt;0),1,0))+IF(AD17='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0,2,0.5),IF(OR(AD17='Resultats Reals'!$C$11,AD17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD17)&gt;0),1,0))+IF(AE17='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0,2,0.5),IF(OR(AE17='Resultats Reals'!$C$14,AE17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE17)&gt;0),1,0))+IF(AF17='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0,2,0.5),IF(OR(AF17='Resultats Reals'!$C$17,AF17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF17)&gt;0),1,0))+IF(AG17='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0,2,0.5),IF(OR(AG17='Resultats Reals'!$C$20,AG17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG17)&gt;0),1,0))+IF(AH17='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0,2,0.5),IF(OR(AH17='Resultats Reals'!$C$23,AH17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH17)&gt;0),1,0))+IF(AI17='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0,2,0.5),IF(OR(AI17='Resultats Reals'!$C$26,AI17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI17)&gt;0),1,0))+IF(AJ17='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0,2,0.5),IF(OR(AJ17='Resultats Reals'!$C$29,AJ17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ17)&gt;0),1,0))+IF(AK17='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0,2,0.5),IF(OR(AK17='Resultats Reals'!$C$32,AK17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK17)&gt;0),1,0))+IF(AL17='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0,2,0.5),IF(OR(AL17='Resultats Reals'!$C$35,AL17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL17)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX17">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA17)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB17)&gt;0,1,0)</f>
@@ -11325,10 +11324,10 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -11555,7 +11554,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
@@ -11591,10 +11590,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -11818,7 +11817,7 @@
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -11854,10 +11853,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -12081,7 +12080,7 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12117,10 +12116,10 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -12340,7 +12339,7 @@
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
@@ -12380,10 +12379,10 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -12603,7 +12602,7 @@
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
@@ -12643,10 +12642,10 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -12866,7 +12865,7 @@
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
@@ -12906,10 +12905,10 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -13133,7 +13132,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13169,10 +13168,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>175</v>
       </c>
@@ -13392,7 +13391,7 @@
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
@@ -13432,10 +13431,10 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>33.5</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -13662,7 +13661,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13698,10 +13697,10 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -13921,7 +13920,7 @@
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
@@ -13961,10 +13960,10 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>179</v>
       </c>
@@ -14188,7 +14187,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14224,10 +14223,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>181</v>
       </c>
@@ -14450,11 +14449,11 @@
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14490,10 +14489,10 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14717,7 +14716,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14753,10 +14752,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -14976,7 +14975,7 @@
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
@@ -15016,10 +15015,10 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -15246,7 +15245,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15282,10 +15281,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -15508,7 +15507,7 @@
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
@@ -15548,10 +15547,10 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -15778,7 +15777,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15814,10 +15813,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -16037,7 +16036,7 @@
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
@@ -16077,10 +16076,10 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -16304,7 +16303,7 @@
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16340,10 +16339,10 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -16567,7 +16566,7 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16603,10 +16602,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -16833,7 +16832,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16869,10 +16868,10 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -17095,7 +17094,7 @@
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
@@ -17135,10 +17134,10 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -17365,7 +17364,7 @@
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17401,10 +17400,10 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -17624,11 +17623,11 @@
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
@@ -17667,7 +17666,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -17891,7 +17890,7 @@
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17927,10 +17926,10 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -18157,7 +18156,7 @@
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
@@ -18193,10 +18192,10 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -18420,7 +18419,7 @@
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18456,10 +18455,10 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>209</v>
       </c>
@@ -18683,7 +18682,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18719,10 +18718,10 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -18949,7 +18948,7 @@
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -18985,10 +18984,10 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -19204,7 +19203,7 @@
       </c>
       <c r="BU47">
         <f>IF(C47='Resultats Reals'!$C$2,2,IF(OR(C47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C47)&gt;0),1,0))+IF(D47='Resultats Reals'!$C$5,2,IF(OR(D47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D47)&gt;0),1,0))+IF(E47='Resultats Reals'!$C$8,2,IF(OR(E47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E47)&gt;0),1,0))+IF(F47='Resultats Reals'!$C$11,2,IF(OR(F47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F47)&gt;0),1,0))+IF(G47='Resultats Reals'!$C$14,2,IF(OR(G47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G47)&gt;0),1,0))+IF(H47='Resultats Reals'!$C$17,2,IF(OR(H47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H47)&gt;0),1,0))+IF(I47='Resultats Reals'!$C$20,2,IF(OR(I47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I47)&gt;0),1,0))+IF(J47='Resultats Reals'!$C$23,2,IF(OR(J47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J47)&gt;0),1,0))+IF(K47='Resultats Reals'!$C$26,2,IF(OR(K47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K47)&gt;0),1,0))+IF(L47='Resultats Reals'!$C$29,2,IF(OR(L47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L47)&gt;0),1,0))+IF(M47='Resultats Reals'!$C$32,2,IF(OR(M47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M47)&gt;0),1,0))+IF(N47='Resultats Reals'!$C$35,2,IF(OR(N47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N47)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z47)&gt;0),1,0))</f>
@@ -19248,10 +19247,10 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -19475,7 +19474,7 @@
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19511,10 +19510,10 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -19741,7 +19740,7 @@
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19777,7 +19776,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
   </sheetData>
@@ -19788,13 +19787,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.2890625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>244</v>
       </c>
@@ -19802,395 +19801,395 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2">
         <v>45.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3">
         <v>45.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5">
         <v>44.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6">
         <v>44.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8">
         <v>42.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9">
         <v>42.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10">
         <v>42.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14">
         <v>41.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15">
         <v>41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22">
         <v>40.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23">
         <v>40.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24">
         <v>40.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26">
         <v>39.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27">
         <v>39.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28">
         <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29">
         <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30">
         <v>39.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31">
         <v>39.5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35">
         <v>38.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36">
         <v>38.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37">
         <v>38.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38">
         <v>38.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39">
         <v>37.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40">
         <v>37.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41">
         <v>37.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42">
         <v>36.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43">
         <v>36.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45">
         <v>34.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46">
         <v>34.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47">
         <v>34.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48">
         <v>32.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49">
         <v>28.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50">
         <v>1906</v>
       </c>
     </row>
@@ -20203,247 +20202,247 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>247</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6287A4CF-6CB1-478C-BA13-FA1DE3F3EDCE}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C495C53-540F-8F4A-8581-D45B33C883F5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -904,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -926,6 +926,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6007,24 +6008,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
+    <col min="1" max="2" width="9.953125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.953125" customWidth="1"/>
+    <col min="5" max="6" width="16.0078125" customWidth="1"/>
+    <col min="7" max="7" width="14.9296875" customWidth="1"/>
+    <col min="8" max="8" width="13.98828125" customWidth="1"/>
+    <col min="9" max="9" width="18.96484375" customWidth="1"/>
+    <col min="10" max="10" width="14.9296875" customWidth="1"/>
+    <col min="11" max="11" width="11.97265625" customWidth="1"/>
+    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.953125" customWidth="1"/>
+    <col min="14" max="14" width="18.96484375" customWidth="1"/>
+    <col min="15" max="15" width="9.953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6065,7 +6066,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6106,7 +6107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6138,7 +6139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6167,7 +6168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6196,7 +6197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6207,7 +6208,7 @@
         <v>99</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>229</v>
@@ -6222,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6248,7 +6249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6256,7 +6257,7 @@
         <v>228</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>89</v>
@@ -6274,7 +6275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6300,7 +6301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6308,7 +6309,7 @@
         <v>231</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>90</v>
@@ -6323,7 +6324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6346,7 +6347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6377,7 +6378,7 @@
         <v>231</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="E13" s="14" t="str">
         <f>+C18</f>
@@ -6393,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6414,10 +6415,10 @@
         <v>167</v>
       </c>
       <c r="O14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6435,7 +6436,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6453,7 +6454,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6471,7 +6472,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6486,7 +6487,7 @@
         <v>Noruega</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6501,7 +6502,7 @@
         <v>França</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6516,7 +6517,7 @@
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6531,7 +6532,7 @@
         <v>Àustria</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6546,7 +6547,7 @@
         <v>Colòmbia</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>RD Congo</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6576,7 +6577,7 @@
         <v>Anglaterra</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6591,7 +6592,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6602,11 +6603,11 @@
         <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6617,10 +6618,10 @@
         <v>94</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6634,7 +6635,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6648,7 +6649,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6676,7 +6677,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6690,7 +6691,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6715,7 +6716,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6726,7 +6727,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6737,7 +6738,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6788,81 +6789,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.45703125" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
     <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7116,7 +7117,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7332,7 +7333,7 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
@@ -7340,7 +7341,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7376,10 +7377,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>41</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7595,7 +7596,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
@@ -7603,7 +7604,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7639,10 +7640,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7858,7 +7859,7 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
@@ -7866,7 +7867,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7902,10 +7903,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8121,7 +8122,7 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
@@ -8129,7 +8130,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8165,10 +8166,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8384,7 +8385,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
@@ -8392,7 +8393,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8428,10 +8429,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8655,7 +8656,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8691,10 +8692,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8910,7 +8911,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N8)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
@@ -8918,7 +8919,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -8954,10 +8955,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9184,7 +9185,7 @@
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9220,10 +9221,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9439,15 +9440,15 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
@@ -9483,10 +9484,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9702,7 +9703,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
@@ -9710,7 +9711,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
@@ -9746,10 +9747,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -9965,7 +9966,7 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N12)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
@@ -9973,7 +9974,7 @@
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
@@ -10009,10 +10010,10 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -10228,7 +10229,7 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
@@ -10236,7 +10237,7 @@
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10272,10 +10273,10 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -10491,7 +10492,7 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
@@ -10499,7 +10500,7 @@
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
@@ -10535,10 +10536,10 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>157</v>
       </c>
@@ -10754,15 +10755,15 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
@@ -10798,10 +10799,10 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -11017,7 +11018,7 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
@@ -11025,7 +11026,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11061,10 +11062,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -11280,7 +11281,7 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N17)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
@@ -11324,10 +11325,10 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>38.5</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -11546,7 +11547,7 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
@@ -11554,7 +11555,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
@@ -11590,10 +11591,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -11809,15 +11810,15 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -11845,7 +11846,7 @@
       </c>
       <c r="CD19">
         <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CE19">
         <f>IF(BR19='Resultats Reals'!$L$2,5,0)</f>
@@ -11853,10 +11854,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -12072,7 +12073,7 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
@@ -12080,7 +12081,7 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12116,10 +12117,10 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -12335,7 +12336,7 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
@@ -12343,7 +12344,7 @@
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
@@ -12379,10 +12380,10 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -12598,11 +12599,11 @@
       </c>
       <c r="BU22">
         <f>IF(C22='Resultats Reals'!$C$2,2,IF(OR(C22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C22)&gt;0),1,0))+IF(D22='Resultats Reals'!$C$5,2,IF(OR(D22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D22)&gt;0),1,0))+IF(E22='Resultats Reals'!$C$8,2,IF(OR(E22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E22)&gt;0),1,0))+IF(F22='Resultats Reals'!$C$11,2,IF(OR(F22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F22)&gt;0),1,0))+IF(G22='Resultats Reals'!$C$14,2,IF(OR(G22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G22)&gt;0),1,0))+IF(H22='Resultats Reals'!$C$17,2,IF(OR(H22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H22)&gt;0),1,0))+IF(I22='Resultats Reals'!$C$20,2,IF(OR(I22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I22)&gt;0),1,0))+IF(J22='Resultats Reals'!$C$23,2,IF(OR(J22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J22)&gt;0),1,0))+IF(K22='Resultats Reals'!$C$26,2,IF(OR(K22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K22)&gt;0),1,0))+IF(L22='Resultats Reals'!$C$29,2,IF(OR(L22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L22)&gt;0),1,0))+IF(M22='Resultats Reals'!$C$32,2,IF(OR(M22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M22)&gt;0),1,0))+IF(N22='Resultats Reals'!$C$35,2,IF(OR(N22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N22)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
@@ -12642,10 +12643,10 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -12861,11 +12862,11 @@
       </c>
       <c r="BU23">
         <f>IF(C23='Resultats Reals'!$C$2,2,IF(OR(C23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C23)&gt;0),1,0))+IF(D23='Resultats Reals'!$C$5,2,IF(OR(D23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D23)&gt;0),1,0))+IF(E23='Resultats Reals'!$C$8,2,IF(OR(E23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E23)&gt;0),1,0))+IF(F23='Resultats Reals'!$C$11,2,IF(OR(F23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F23)&gt;0),1,0))+IF(G23='Resultats Reals'!$C$14,2,IF(OR(G23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G23)&gt;0),1,0))+IF(H23='Resultats Reals'!$C$17,2,IF(OR(H23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H23)&gt;0),1,0))+IF(I23='Resultats Reals'!$C$20,2,IF(OR(I23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I23)&gt;0),1,0))+IF(J23='Resultats Reals'!$C$23,2,IF(OR(J23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J23)&gt;0),1,0))+IF(K23='Resultats Reals'!$C$26,2,IF(OR(K23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K23)&gt;0),1,0))+IF(L23='Resultats Reals'!$C$29,2,IF(OR(L23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L23)&gt;0),1,0))+IF(M23='Resultats Reals'!$C$32,2,IF(OR(M23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M23)&gt;0),1,0))+IF(N23='Resultats Reals'!$C$35,2,IF(OR(N23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N23)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
@@ -12905,10 +12906,10 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -13124,7 +13125,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
@@ -13132,7 +13133,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13168,10 +13169,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>175</v>
       </c>
@@ -13387,11 +13388,11 @@
       </c>
       <c r="BU25">
         <f>IF(C25='Resultats Reals'!$C$2,2,IF(OR(C25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C25)&gt;0),1,0))+IF(D25='Resultats Reals'!$C$5,2,IF(OR(D25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D25)&gt;0),1,0))+IF(E25='Resultats Reals'!$C$8,2,IF(OR(E25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E25)&gt;0),1,0))+IF(F25='Resultats Reals'!$C$11,2,IF(OR(F25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F25)&gt;0),1,0))+IF(G25='Resultats Reals'!$C$14,2,IF(OR(G25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G25)&gt;0),1,0))+IF(H25='Resultats Reals'!$C$17,2,IF(OR(H25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H25)&gt;0),1,0))+IF(I25='Resultats Reals'!$C$20,2,IF(OR(I25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I25)&gt;0),1,0))+IF(J25='Resultats Reals'!$C$23,2,IF(OR(J25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J25)&gt;0),1,0))+IF(K25='Resultats Reals'!$C$26,2,IF(OR(K25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K25)&gt;0),1,0))+IF(L25='Resultats Reals'!$C$29,2,IF(OR(L25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L25)&gt;0),1,0))+IF(M25='Resultats Reals'!$C$32,2,IF(OR(M25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M25)&gt;0),1,0))+IF(N25='Resultats Reals'!$C$35,2,IF(OR(N25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N25)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
@@ -13431,10 +13432,10 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -13653,7 +13654,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
@@ -13661,7 +13662,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13697,10 +13698,10 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -13916,7 +13917,7 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
@@ -13924,7 +13925,7 @@
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
@@ -13960,10 +13961,10 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>179</v>
       </c>
@@ -14187,7 +14188,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14223,10 +14224,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>181</v>
       </c>
@@ -14445,15 +14446,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14489,10 +14490,10 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14708,7 +14709,7 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
@@ -14716,7 +14717,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14752,10 +14753,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>38.5</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -14971,7 +14972,7 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
@@ -14979,7 +14980,7 @@
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX31">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
@@ -15015,10 +15016,10 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>37.5</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -15237,7 +15238,7 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
@@ -15245,7 +15246,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15281,10 +15282,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -15503,7 +15504,7 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
@@ -15511,7 +15512,7 @@
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
@@ -15547,10 +15548,10 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -15769,7 +15770,7 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
@@ -15777,7 +15778,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15813,10 +15814,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -16032,15 +16033,15 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
@@ -16076,10 +16077,10 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -16303,7 +16304,7 @@
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16339,10 +16340,10 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -16558,7 +16559,7 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
@@ -16566,7 +16567,7 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16602,10 +16603,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -16824,7 +16825,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
@@ -16832,7 +16833,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16868,10 +16869,10 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -17090,7 +17091,7 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Resultats Reals'!$C$5,2,IF(OR(D39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D39)&gt;0),1,0))+IF(E39='Resultats Reals'!$C$8,2,IF(OR(E39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E39)&gt;0),1,0))+IF(F39='Resultats Reals'!$C$11,2,IF(OR(F39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F39)&gt;0),1,0))+IF(G39='Resultats Reals'!$C$14,2,IF(OR(G39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G39)&gt;0),1,0))+IF(H39='Resultats Reals'!$C$17,2,IF(OR(H39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H39)&gt;0),1,0))+IF(I39='Resultats Reals'!$C$20,2,IF(OR(I39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I39)&gt;0),1,0))+IF(J39='Resultats Reals'!$C$23,2,IF(OR(J39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J39)&gt;0),1,0))+IF(K39='Resultats Reals'!$C$26,2,IF(OR(K39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K39)&gt;0),1,0))+IF(L39='Resultats Reals'!$C$29,2,IF(OR(L39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L39)&gt;0),1,0))+IF(M39='Resultats Reals'!$C$32,2,IF(OR(M39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M39)&gt;0),1,0))+IF(N39='Resultats Reals'!$C$35,2,IF(OR(N39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N39)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV39">
         <f>IF(O39='Resultats Reals'!$C$3,2,IF(OR(O39='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O39)&gt;0),1,0))+IF(P39='Resultats Reals'!$C$6,2,IF(OR(P39='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P39)&gt;0),1,0))+IF(Q39='Resultats Reals'!$C$9,2,IF(OR(Q39='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q39)&gt;0),1,0))+IF(R39='Resultats Reals'!$C$12,2,IF(OR(R39='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R39)&gt;0),1,0))+IF(S39='Resultats Reals'!$C$15,2,IF(OR(S39='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S39)&gt;0),1,0))+IF(T39='Resultats Reals'!$C$18,2,IF(OR(T39='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T39)&gt;0),1,0))+IF(U39='Resultats Reals'!$C$21,2,IF(OR(U39='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U39)&gt;0),1,0))+IF(V39='Resultats Reals'!$C$24,2,IF(OR(V39='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V39)&gt;0),1,0))+IF(W39='Resultats Reals'!$C$27,2,IF(OR(W39='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W39)&gt;0),1,0))+IF(X39='Resultats Reals'!$C$30,2,IF(OR(X39='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X39)&gt;0),1,0))+IF(Y39='Resultats Reals'!$C$33,2,IF(OR(Y39='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y39)&gt;0),1,0))+IF(Z39='Resultats Reals'!$C$36,2,IF(OR(Z39='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z39)&gt;0),1,0))</f>
@@ -17098,7 +17099,7 @@
       </c>
       <c r="BW39">
         <f>IF(AA39='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0,2,0.5),IF(OR(AA39='Resultats Reals'!$C$2,AA39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA39)&gt;0),1,0))+IF(AB39='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0,2,0.5),IF(OR(AB39='Resultats Reals'!$C$5,AB39='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB39)&gt;0),1,0))+IF(AC39='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0,2,0.5),IF(OR(AC39='Resultats Reals'!$C$8,AC39='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC39)&gt;0),1,0))+IF(AD39='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0,2,0.5),IF(OR(AD39='Resultats Reals'!$C$11,AD39='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD39)&gt;0),1,0))+IF(AE39='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0,2,0.5),IF(OR(AE39='Resultats Reals'!$C$14,AE39='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE39)&gt;0),1,0))+IF(AF39='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0,2,0.5),IF(OR(AF39='Resultats Reals'!$C$17,AF39='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF39)&gt;0),1,0))+IF(AG39='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0,2,0.5),IF(OR(AG39='Resultats Reals'!$C$20,AG39='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG39)&gt;0),1,0))+IF(AH39='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0,2,0.5),IF(OR(AH39='Resultats Reals'!$C$23,AH39='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH39)&gt;0),1,0))+IF(AI39='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0,2,0.5),IF(OR(AI39='Resultats Reals'!$C$26,AI39='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI39)&gt;0),1,0))+IF(AJ39='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0,2,0.5),IF(OR(AJ39='Resultats Reals'!$C$29,AJ39='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ39)&gt;0),1,0))+IF(AK39='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0,2,0.5),IF(OR(AK39='Resultats Reals'!$C$32,AK39='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK39)&gt;0),1,0))+IF(AL39='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0,2,0.5),IF(OR(AL39='Resultats Reals'!$C$35,AL39='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL39)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX39">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA39)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB39)&gt;0,1,0)</f>
@@ -17134,10 +17135,10 @@
       </c>
       <c r="CF39" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="40" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>202</v>
       </c>
@@ -17356,7 +17357,7 @@
       </c>
       <c r="BU40">
         <f>IF(C40='Resultats Reals'!$C$2,2,IF(OR(C40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C40)&gt;0),1,0))+IF(D40='Resultats Reals'!$C$5,2,IF(OR(D40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D40)&gt;0),1,0))+IF(E40='Resultats Reals'!$C$8,2,IF(OR(E40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E40)&gt;0),1,0))+IF(F40='Resultats Reals'!$C$11,2,IF(OR(F40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F40)&gt;0),1,0))+IF(G40='Resultats Reals'!$C$14,2,IF(OR(G40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G40)&gt;0),1,0))+IF(H40='Resultats Reals'!$C$17,2,IF(OR(H40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H40)&gt;0),1,0))+IF(I40='Resultats Reals'!$C$20,2,IF(OR(I40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I40)&gt;0),1,0))+IF(J40='Resultats Reals'!$C$23,2,IF(OR(J40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J40)&gt;0),1,0))+IF(K40='Resultats Reals'!$C$26,2,IF(OR(K40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K40)&gt;0),1,0))+IF(L40='Resultats Reals'!$C$29,2,IF(OR(L40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L40)&gt;0),1,0))+IF(M40='Resultats Reals'!$C$32,2,IF(OR(M40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M40)&gt;0),1,0))+IF(N40='Resultats Reals'!$C$35,2,IF(OR(N40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N40)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BV40">
         <f>IF(O40='Resultats Reals'!$C$3,2,IF(OR(O40='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O40)&gt;0),1,0))+IF(P40='Resultats Reals'!$C$6,2,IF(OR(P40='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P40)&gt;0),1,0))+IF(Q40='Resultats Reals'!$C$9,2,IF(OR(Q40='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q40)&gt;0),1,0))+IF(R40='Resultats Reals'!$C$12,2,IF(OR(R40='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R40)&gt;0),1,0))+IF(S40='Resultats Reals'!$C$15,2,IF(OR(S40='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S40)&gt;0),1,0))+IF(T40='Resultats Reals'!$C$18,2,IF(OR(T40='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T40)&gt;0),1,0))+IF(U40='Resultats Reals'!$C$21,2,IF(OR(U40='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U40)&gt;0),1,0))+IF(V40='Resultats Reals'!$C$24,2,IF(OR(V40='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V40)&gt;0),1,0))+IF(W40='Resultats Reals'!$C$27,2,IF(OR(W40='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W40)&gt;0),1,0))+IF(X40='Resultats Reals'!$C$30,2,IF(OR(X40='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X40)&gt;0),1,0))+IF(Y40='Resultats Reals'!$C$33,2,IF(OR(Y40='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y40)&gt;0),1,0))+IF(Z40='Resultats Reals'!$C$36,2,IF(OR(Z40='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z40)&gt;0),1,0))</f>
@@ -17364,7 +17365,7 @@
       </c>
       <c r="BW40">
         <f>IF(AA40='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0,2,0.5),IF(OR(AA40='Resultats Reals'!$C$2,AA40='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA40)&gt;0),1,0))+IF(AB40='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0,2,0.5),IF(OR(AB40='Resultats Reals'!$C$5,AB40='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB40)&gt;0),1,0))+IF(AC40='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0,2,0.5),IF(OR(AC40='Resultats Reals'!$C$8,AC40='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC40)&gt;0),1,0))+IF(AD40='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0,2,0.5),IF(OR(AD40='Resultats Reals'!$C$11,AD40='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD40)&gt;0),1,0))+IF(AE40='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0,2,0.5),IF(OR(AE40='Resultats Reals'!$C$14,AE40='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE40)&gt;0),1,0))+IF(AF40='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0,2,0.5),IF(OR(AF40='Resultats Reals'!$C$17,AF40='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF40)&gt;0),1,0))+IF(AG40='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0,2,0.5),IF(OR(AG40='Resultats Reals'!$C$20,AG40='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG40)&gt;0),1,0))+IF(AH40='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0,2,0.5),IF(OR(AH40='Resultats Reals'!$C$23,AH40='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH40)&gt;0),1,0))+IF(AI40='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0,2,0.5),IF(OR(AI40='Resultats Reals'!$C$26,AI40='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI40)&gt;0),1,0))+IF(AJ40='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0,2,0.5),IF(OR(AJ40='Resultats Reals'!$C$29,AJ40='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ40)&gt;0),1,0))+IF(AK40='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0,2,0.5),IF(OR(AK40='Resultats Reals'!$C$32,AK40='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK40)&gt;0),1,0))+IF(AL40='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0,2,0.5),IF(OR(AL40='Resultats Reals'!$C$35,AL40='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL40)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX40">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA40)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB40)&gt;0,1,0)</f>
@@ -17400,10 +17401,10 @@
       </c>
       <c r="CF40" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="41" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -17619,7 +17620,7 @@
       </c>
       <c r="BU41">
         <f>IF(C41='Resultats Reals'!$C$2,2,IF(OR(C41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C41)&gt;0),1,0))+IF(D41='Resultats Reals'!$C$5,2,IF(OR(D41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D41)&gt;0),1,0))+IF(E41='Resultats Reals'!$C$8,2,IF(OR(E41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E41)&gt;0),1,0))+IF(F41='Resultats Reals'!$C$11,2,IF(OR(F41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F41)&gt;0),1,0))+IF(G41='Resultats Reals'!$C$14,2,IF(OR(G41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G41)&gt;0),1,0))+IF(H41='Resultats Reals'!$C$17,2,IF(OR(H41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H41)&gt;0),1,0))+IF(I41='Resultats Reals'!$C$20,2,IF(OR(I41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I41)&gt;0),1,0))+IF(J41='Resultats Reals'!$C$23,2,IF(OR(J41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J41)&gt;0),1,0))+IF(K41='Resultats Reals'!$C$26,2,IF(OR(K41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K41)&gt;0),1,0))+IF(L41='Resultats Reals'!$C$29,2,IF(OR(L41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L41)&gt;0),1,0))+IF(M41='Resultats Reals'!$C$32,2,IF(OR(M41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M41)&gt;0),1,0))+IF(N41='Resultats Reals'!$C$35,2,IF(OR(N41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N41)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV41">
         <f>IF(O41='Resultats Reals'!$C$3,2,IF(OR(O41='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O41)&gt;0),1,0))+IF(P41='Resultats Reals'!$C$6,2,IF(OR(P41='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P41)&gt;0),1,0))+IF(Q41='Resultats Reals'!$C$9,2,IF(OR(Q41='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q41)&gt;0),1,0))+IF(R41='Resultats Reals'!$C$12,2,IF(OR(R41='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R41)&gt;0),1,0))+IF(S41='Resultats Reals'!$C$15,2,IF(OR(S41='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S41)&gt;0),1,0))+IF(T41='Resultats Reals'!$C$18,2,IF(OR(T41='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T41)&gt;0),1,0))+IF(U41='Resultats Reals'!$C$21,2,IF(OR(U41='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U41)&gt;0),1,0))+IF(V41='Resultats Reals'!$C$24,2,IF(OR(V41='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V41)&gt;0),1,0))+IF(W41='Resultats Reals'!$C$27,2,IF(OR(W41='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W41)&gt;0),1,0))+IF(X41='Resultats Reals'!$C$30,2,IF(OR(X41='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X41)&gt;0),1,0))+IF(Y41='Resultats Reals'!$C$33,2,IF(OR(Y41='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y41)&gt;0),1,0))+IF(Z41='Resultats Reals'!$C$36,2,IF(OR(Z41='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z41)&gt;0),1,0))</f>
@@ -17627,7 +17628,7 @@
       </c>
       <c r="BW41">
         <f>IF(AA41='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0,2,0.5),IF(OR(AA41='Resultats Reals'!$C$2,AA41='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA41)&gt;0),1,0))+IF(AB41='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0,2,0.5),IF(OR(AB41='Resultats Reals'!$C$5,AB41='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB41)&gt;0),1,0))+IF(AC41='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0,2,0.5),IF(OR(AC41='Resultats Reals'!$C$8,AC41='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC41)&gt;0),1,0))+IF(AD41='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0,2,0.5),IF(OR(AD41='Resultats Reals'!$C$11,AD41='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD41)&gt;0),1,0))+IF(AE41='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0,2,0.5),IF(OR(AE41='Resultats Reals'!$C$14,AE41='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE41)&gt;0),1,0))+IF(AF41='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0,2,0.5),IF(OR(AF41='Resultats Reals'!$C$17,AF41='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF41)&gt;0),1,0))+IF(AG41='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0,2,0.5),IF(OR(AG41='Resultats Reals'!$C$20,AG41='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG41)&gt;0),1,0))+IF(AH41='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0,2,0.5),IF(OR(AH41='Resultats Reals'!$C$23,AH41='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH41)&gt;0),1,0))+IF(AI41='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0,2,0.5),IF(OR(AI41='Resultats Reals'!$C$26,AI41='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI41)&gt;0),1,0))+IF(AJ41='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0,2,0.5),IF(OR(AJ41='Resultats Reals'!$C$29,AJ41='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ41)&gt;0),1,0))+IF(AK41='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0,2,0.5),IF(OR(AK41='Resultats Reals'!$C$32,AK41='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK41)&gt;0),1,0))+IF(AL41='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0,2,0.5),IF(OR(AL41='Resultats Reals'!$C$35,AL41='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL41)&gt;0),1,0))</f>
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BX41">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA41)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB41)&gt;0,1,0)</f>
@@ -17663,10 +17664,10 @@
       </c>
       <c r="CF41" s="7">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="42" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -17882,7 +17883,7 @@
       </c>
       <c r="BU42">
         <f>IF(C42='Resultats Reals'!$C$2,2,IF(OR(C42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C42)&gt;0),1,0))+IF(D42='Resultats Reals'!$C$5,2,IF(OR(D42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D42)&gt;0),1,0))+IF(E42='Resultats Reals'!$C$8,2,IF(OR(E42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E42)&gt;0),1,0))+IF(F42='Resultats Reals'!$C$11,2,IF(OR(F42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F42)&gt;0),1,0))+IF(G42='Resultats Reals'!$C$14,2,IF(OR(G42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G42)&gt;0),1,0))+IF(H42='Resultats Reals'!$C$17,2,IF(OR(H42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H42)&gt;0),1,0))+IF(I42='Resultats Reals'!$C$20,2,IF(OR(I42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I42)&gt;0),1,0))+IF(J42='Resultats Reals'!$C$23,2,IF(OR(J42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J42)&gt;0),1,0))+IF(K42='Resultats Reals'!$C$26,2,IF(OR(K42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K42)&gt;0),1,0))+IF(L42='Resultats Reals'!$C$29,2,IF(OR(L42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L42)&gt;0),1,0))+IF(M42='Resultats Reals'!$C$32,2,IF(OR(M42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M42)&gt;0),1,0))+IF(N42='Resultats Reals'!$C$35,2,IF(OR(N42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N42)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV42">
         <f>IF(O42='Resultats Reals'!$C$3,2,IF(OR(O42='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O42)&gt;0),1,0))+IF(P42='Resultats Reals'!$C$6,2,IF(OR(P42='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P42)&gt;0),1,0))+IF(Q42='Resultats Reals'!$C$9,2,IF(OR(Q42='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q42)&gt;0),1,0))+IF(R42='Resultats Reals'!$C$12,2,IF(OR(R42='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R42)&gt;0),1,0))+IF(S42='Resultats Reals'!$C$15,2,IF(OR(S42='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S42)&gt;0),1,0))+IF(T42='Resultats Reals'!$C$18,2,IF(OR(T42='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T42)&gt;0),1,0))+IF(U42='Resultats Reals'!$C$21,2,IF(OR(U42='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U42)&gt;0),1,0))+IF(V42='Resultats Reals'!$C$24,2,IF(OR(V42='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V42)&gt;0),1,0))+IF(W42='Resultats Reals'!$C$27,2,IF(OR(W42='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W42)&gt;0),1,0))+IF(X42='Resultats Reals'!$C$30,2,IF(OR(X42='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X42)&gt;0),1,0))+IF(Y42='Resultats Reals'!$C$33,2,IF(OR(Y42='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y42)&gt;0),1,0))+IF(Z42='Resultats Reals'!$C$36,2,IF(OR(Z42='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z42)&gt;0),1,0))</f>
@@ -17890,7 +17891,7 @@
       </c>
       <c r="BW42">
         <f>IF(AA42='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0,2,0.5),IF(OR(AA42='Resultats Reals'!$C$2,AA42='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA42)&gt;0),1,0))+IF(AB42='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0,2,0.5),IF(OR(AB42='Resultats Reals'!$C$5,AB42='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB42)&gt;0),1,0))+IF(AC42='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0,2,0.5),IF(OR(AC42='Resultats Reals'!$C$8,AC42='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC42)&gt;0),1,0))+IF(AD42='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0,2,0.5),IF(OR(AD42='Resultats Reals'!$C$11,AD42='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD42)&gt;0),1,0))+IF(AE42='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0,2,0.5),IF(OR(AE42='Resultats Reals'!$C$14,AE42='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE42)&gt;0),1,0))+IF(AF42='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0,2,0.5),IF(OR(AF42='Resultats Reals'!$C$17,AF42='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF42)&gt;0),1,0))+IF(AG42='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0,2,0.5),IF(OR(AG42='Resultats Reals'!$C$20,AG42='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG42)&gt;0),1,0))+IF(AH42='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0,2,0.5),IF(OR(AH42='Resultats Reals'!$C$23,AH42='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH42)&gt;0),1,0))+IF(AI42='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0,2,0.5),IF(OR(AI42='Resultats Reals'!$C$26,AI42='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI42)&gt;0),1,0))+IF(AJ42='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0,2,0.5),IF(OR(AJ42='Resultats Reals'!$C$29,AJ42='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ42)&gt;0),1,0))+IF(AK42='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0,2,0.5),IF(OR(AK42='Resultats Reals'!$C$32,AK42='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK42)&gt;0),1,0))+IF(AL42='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0,2,0.5),IF(OR(AL42='Resultats Reals'!$C$35,AL42='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL42)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX42">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA42)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB42)&gt;0,1,0)</f>
@@ -17926,10 +17927,10 @@
       </c>
       <c r="CF42" s="7">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="43" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>206</v>
       </c>
@@ -18148,7 +18149,7 @@
       </c>
       <c r="BU43">
         <f>IF(C43='Resultats Reals'!$C$2,2,IF(OR(C43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C43)&gt;0),1,0))+IF(D43='Resultats Reals'!$C$5,2,IF(OR(D43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D43)&gt;0),1,0))+IF(E43='Resultats Reals'!$C$8,2,IF(OR(E43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E43)&gt;0),1,0))+IF(F43='Resultats Reals'!$C$11,2,IF(OR(F43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F43)&gt;0),1,0))+IF(G43='Resultats Reals'!$C$14,2,IF(OR(G43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G43)&gt;0),1,0))+IF(H43='Resultats Reals'!$C$17,2,IF(OR(H43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H43)&gt;0),1,0))+IF(I43='Resultats Reals'!$C$20,2,IF(OR(I43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I43)&gt;0),1,0))+IF(J43='Resultats Reals'!$C$23,2,IF(OR(J43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J43)&gt;0),1,0))+IF(K43='Resultats Reals'!$C$26,2,IF(OR(K43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K43)&gt;0),1,0))+IF(L43='Resultats Reals'!$C$29,2,IF(OR(L43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L43)&gt;0),1,0))+IF(M43='Resultats Reals'!$C$32,2,IF(OR(M43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M43)&gt;0),1,0))+IF(N43='Resultats Reals'!$C$35,2,IF(OR(N43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N43)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV43">
         <f>IF(O43='Resultats Reals'!$C$3,2,IF(OR(O43='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O43)&gt;0),1,0))+IF(P43='Resultats Reals'!$C$6,2,IF(OR(P43='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P43)&gt;0),1,0))+IF(Q43='Resultats Reals'!$C$9,2,IF(OR(Q43='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q43)&gt;0),1,0))+IF(R43='Resultats Reals'!$C$12,2,IF(OR(R43='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R43)&gt;0),1,0))+IF(S43='Resultats Reals'!$C$15,2,IF(OR(S43='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S43)&gt;0),1,0))+IF(T43='Resultats Reals'!$C$18,2,IF(OR(T43='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T43)&gt;0),1,0))+IF(U43='Resultats Reals'!$C$21,2,IF(OR(U43='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U43)&gt;0),1,0))+IF(V43='Resultats Reals'!$C$24,2,IF(OR(V43='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V43)&gt;0),1,0))+IF(W43='Resultats Reals'!$C$27,2,IF(OR(W43='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W43)&gt;0),1,0))+IF(X43='Resultats Reals'!$C$30,2,IF(OR(X43='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X43)&gt;0),1,0))+IF(Y43='Resultats Reals'!$C$33,2,IF(OR(Y43='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y43)&gt;0),1,0))+IF(Z43='Resultats Reals'!$C$36,2,IF(OR(Z43='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z43)&gt;0),1,0))</f>
@@ -18156,7 +18157,7 @@
       </c>
       <c r="BW43">
         <f>IF(AA43='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0,2,0.5),IF(OR(AA43='Resultats Reals'!$C$2,AA43='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA43)&gt;0),1,0))+IF(AB43='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0,2,0.5),IF(OR(AB43='Resultats Reals'!$C$5,AB43='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB43)&gt;0),1,0))+IF(AC43='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0,2,0.5),IF(OR(AC43='Resultats Reals'!$C$8,AC43='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC43)&gt;0),1,0))+IF(AD43='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0,2,0.5),IF(OR(AD43='Resultats Reals'!$C$11,AD43='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD43)&gt;0),1,0))+IF(AE43='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0,2,0.5),IF(OR(AE43='Resultats Reals'!$C$14,AE43='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE43)&gt;0),1,0))+IF(AF43='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0,2,0.5),IF(OR(AF43='Resultats Reals'!$C$17,AF43='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF43)&gt;0),1,0))+IF(AG43='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0,2,0.5),IF(OR(AG43='Resultats Reals'!$C$20,AG43='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG43)&gt;0),1,0))+IF(AH43='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0,2,0.5),IF(OR(AH43='Resultats Reals'!$C$23,AH43='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH43)&gt;0),1,0))+IF(AI43='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0,2,0.5),IF(OR(AI43='Resultats Reals'!$C$26,AI43='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI43)&gt;0),1,0))+IF(AJ43='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0,2,0.5),IF(OR(AJ43='Resultats Reals'!$C$29,AJ43='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ43)&gt;0),1,0))+IF(AK43='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0,2,0.5),IF(OR(AK43='Resultats Reals'!$C$32,AK43='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK43)&gt;0),1,0))+IF(AL43='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0,2,0.5),IF(OR(AL43='Resultats Reals'!$C$35,AL43='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL43)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BX43">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA43)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB43)&gt;0,1,0)</f>
@@ -18192,10 +18193,10 @@
       </c>
       <c r="CF43" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>45.5</v>
       </c>
     </row>
-    <row r="44" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>208</v>
       </c>
@@ -18411,7 +18412,7 @@
       </c>
       <c r="BU44">
         <f>IF(C44='Resultats Reals'!$C$2,2,IF(OR(C44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C44)&gt;0),1,0))+IF(D44='Resultats Reals'!$C$5,2,IF(OR(D44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D44)&gt;0),1,0))+IF(E44='Resultats Reals'!$C$8,2,IF(OR(E44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E44)&gt;0),1,0))+IF(F44='Resultats Reals'!$C$11,2,IF(OR(F44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F44)&gt;0),1,0))+IF(G44='Resultats Reals'!$C$14,2,IF(OR(G44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G44)&gt;0),1,0))+IF(H44='Resultats Reals'!$C$17,2,IF(OR(H44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H44)&gt;0),1,0))+IF(I44='Resultats Reals'!$C$20,2,IF(OR(I44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I44)&gt;0),1,0))+IF(J44='Resultats Reals'!$C$23,2,IF(OR(J44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J44)&gt;0),1,0))+IF(K44='Resultats Reals'!$C$26,2,IF(OR(K44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K44)&gt;0),1,0))+IF(L44='Resultats Reals'!$C$29,2,IF(OR(L44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L44)&gt;0),1,0))+IF(M44='Resultats Reals'!$C$32,2,IF(OR(M44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M44)&gt;0),1,0))+IF(N44='Resultats Reals'!$C$35,2,IF(OR(N44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N44)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV44">
         <f>IF(O44='Resultats Reals'!$C$3,2,IF(OR(O44='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O44)&gt;0),1,0))+IF(P44='Resultats Reals'!$C$6,2,IF(OR(P44='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P44)&gt;0),1,0))+IF(Q44='Resultats Reals'!$C$9,2,IF(OR(Q44='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q44)&gt;0),1,0))+IF(R44='Resultats Reals'!$C$12,2,IF(OR(R44='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R44)&gt;0),1,0))+IF(S44='Resultats Reals'!$C$15,2,IF(OR(S44='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S44)&gt;0),1,0))+IF(T44='Resultats Reals'!$C$18,2,IF(OR(T44='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T44)&gt;0),1,0))+IF(U44='Resultats Reals'!$C$21,2,IF(OR(U44='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U44)&gt;0),1,0))+IF(V44='Resultats Reals'!$C$24,2,IF(OR(V44='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V44)&gt;0),1,0))+IF(W44='Resultats Reals'!$C$27,2,IF(OR(W44='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W44)&gt;0),1,0))+IF(X44='Resultats Reals'!$C$30,2,IF(OR(X44='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X44)&gt;0),1,0))+IF(Y44='Resultats Reals'!$C$33,2,IF(OR(Y44='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y44)&gt;0),1,0))+IF(Z44='Resultats Reals'!$C$36,2,IF(OR(Z44='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z44)&gt;0),1,0))</f>
@@ -18419,7 +18420,7 @@
       </c>
       <c r="BW44">
         <f>IF(AA44='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0,2,0.5),IF(OR(AA44='Resultats Reals'!$C$2,AA44='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA44)&gt;0),1,0))+IF(AB44='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0,2,0.5),IF(OR(AB44='Resultats Reals'!$C$5,AB44='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB44)&gt;0),1,0))+IF(AC44='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0,2,0.5),IF(OR(AC44='Resultats Reals'!$C$8,AC44='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC44)&gt;0),1,0))+IF(AD44='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0,2,0.5),IF(OR(AD44='Resultats Reals'!$C$11,AD44='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD44)&gt;0),1,0))+IF(AE44='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0,2,0.5),IF(OR(AE44='Resultats Reals'!$C$14,AE44='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE44)&gt;0),1,0))+IF(AF44='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0,2,0.5),IF(OR(AF44='Resultats Reals'!$C$17,AF44='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF44)&gt;0),1,0))+IF(AG44='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0,2,0.5),IF(OR(AG44='Resultats Reals'!$C$20,AG44='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG44)&gt;0),1,0))+IF(AH44='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0,2,0.5),IF(OR(AH44='Resultats Reals'!$C$23,AH44='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH44)&gt;0),1,0))+IF(AI44='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0,2,0.5),IF(OR(AI44='Resultats Reals'!$C$26,AI44='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI44)&gt;0),1,0))+IF(AJ44='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0,2,0.5),IF(OR(AJ44='Resultats Reals'!$C$29,AJ44='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ44)&gt;0),1,0))+IF(AK44='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0,2,0.5),IF(OR(AK44='Resultats Reals'!$C$32,AK44='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK44)&gt;0),1,0))+IF(AL44='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0,2,0.5),IF(OR(AL44='Resultats Reals'!$C$35,AL44='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL44)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX44">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA44)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB44)&gt;0,1,0)</f>
@@ -18455,10 +18456,10 @@
       </c>
       <c r="CF44" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>46.5</v>
       </c>
     </row>
-    <row r="45" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>209</v>
       </c>
@@ -18674,7 +18675,7 @@
       </c>
       <c r="BU45">
         <f>IF(C45='Resultats Reals'!$C$2,2,IF(OR(C45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C45)&gt;0),1,0))+IF(D45='Resultats Reals'!$C$5,2,IF(OR(D45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D45)&gt;0),1,0))+IF(E45='Resultats Reals'!$C$8,2,IF(OR(E45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E45)&gt;0),1,0))+IF(F45='Resultats Reals'!$C$11,2,IF(OR(F45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F45)&gt;0),1,0))+IF(G45='Resultats Reals'!$C$14,2,IF(OR(G45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G45)&gt;0),1,0))+IF(H45='Resultats Reals'!$C$17,2,IF(OR(H45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H45)&gt;0),1,0))+IF(I45='Resultats Reals'!$C$20,2,IF(OR(I45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I45)&gt;0),1,0))+IF(J45='Resultats Reals'!$C$23,2,IF(OR(J45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J45)&gt;0),1,0))+IF(K45='Resultats Reals'!$C$26,2,IF(OR(K45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K45)&gt;0),1,0))+IF(L45='Resultats Reals'!$C$29,2,IF(OR(L45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L45)&gt;0),1,0))+IF(M45='Resultats Reals'!$C$32,2,IF(OR(M45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M45)&gt;0),1,0))+IF(N45='Resultats Reals'!$C$35,2,IF(OR(N45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N45)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BV45">
         <f>IF(O45='Resultats Reals'!$C$3,2,IF(OR(O45='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O45)&gt;0),1,0))+IF(P45='Resultats Reals'!$C$6,2,IF(OR(P45='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P45)&gt;0),1,0))+IF(Q45='Resultats Reals'!$C$9,2,IF(OR(Q45='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q45)&gt;0),1,0))+IF(R45='Resultats Reals'!$C$12,2,IF(OR(R45='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R45)&gt;0),1,0))+IF(S45='Resultats Reals'!$C$15,2,IF(OR(S45='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S45)&gt;0),1,0))+IF(T45='Resultats Reals'!$C$18,2,IF(OR(T45='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T45)&gt;0),1,0))+IF(U45='Resultats Reals'!$C$21,2,IF(OR(U45='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U45)&gt;0),1,0))+IF(V45='Resultats Reals'!$C$24,2,IF(OR(V45='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V45)&gt;0),1,0))+IF(W45='Resultats Reals'!$C$27,2,IF(OR(W45='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W45)&gt;0),1,0))+IF(X45='Resultats Reals'!$C$30,2,IF(OR(X45='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X45)&gt;0),1,0))+IF(Y45='Resultats Reals'!$C$33,2,IF(OR(Y45='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y45)&gt;0),1,0))+IF(Z45='Resultats Reals'!$C$36,2,IF(OR(Z45='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z45)&gt;0),1,0))</f>
@@ -18682,7 +18683,7 @@
       </c>
       <c r="BW45">
         <f>IF(AA45='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0,2,0.5),IF(OR(AA45='Resultats Reals'!$C$2,AA45='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA45)&gt;0),1,0))+IF(AB45='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0,2,0.5),IF(OR(AB45='Resultats Reals'!$C$5,AB45='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB45)&gt;0),1,0))+IF(AC45='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0,2,0.5),IF(OR(AC45='Resultats Reals'!$C$8,AC45='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC45)&gt;0),1,0))+IF(AD45='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0,2,0.5),IF(OR(AD45='Resultats Reals'!$C$11,AD45='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD45)&gt;0),1,0))+IF(AE45='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0,2,0.5),IF(OR(AE45='Resultats Reals'!$C$14,AE45='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE45)&gt;0),1,0))+IF(AF45='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0,2,0.5),IF(OR(AF45='Resultats Reals'!$C$17,AF45='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF45)&gt;0),1,0))+IF(AG45='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0,2,0.5),IF(OR(AG45='Resultats Reals'!$C$20,AG45='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG45)&gt;0),1,0))+IF(AH45='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0,2,0.5),IF(OR(AH45='Resultats Reals'!$C$23,AH45='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH45)&gt;0),1,0))+IF(AI45='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0,2,0.5),IF(OR(AI45='Resultats Reals'!$C$26,AI45='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI45)&gt;0),1,0))+IF(AJ45='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0,2,0.5),IF(OR(AJ45='Resultats Reals'!$C$29,AJ45='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ45)&gt;0),1,0))+IF(AK45='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0,2,0.5),IF(OR(AK45='Resultats Reals'!$C$32,AK45='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK45)&gt;0),1,0))+IF(AL45='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0,2,0.5),IF(OR(AL45='Resultats Reals'!$C$35,AL45='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL45)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="BX45">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA45)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB45)&gt;0,1,0)</f>
@@ -18718,10 +18719,10 @@
       </c>
       <c r="CF45" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>210</v>
       </c>
@@ -18940,7 +18941,7 @@
       </c>
       <c r="BU46">
         <f>IF(C46='Resultats Reals'!$C$2,2,IF(OR(C46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C46)&gt;0),1,0))+IF(D46='Resultats Reals'!$C$5,2,IF(OR(D46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D46)&gt;0),1,0))+IF(E46='Resultats Reals'!$C$8,2,IF(OR(E46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E46)&gt;0),1,0))+IF(F46='Resultats Reals'!$C$11,2,IF(OR(F46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F46)&gt;0),1,0))+IF(G46='Resultats Reals'!$C$14,2,IF(OR(G46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G46)&gt;0),1,0))+IF(H46='Resultats Reals'!$C$17,2,IF(OR(H46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H46)&gt;0),1,0))+IF(I46='Resultats Reals'!$C$20,2,IF(OR(I46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I46)&gt;0),1,0))+IF(J46='Resultats Reals'!$C$23,2,IF(OR(J46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J46)&gt;0),1,0))+IF(K46='Resultats Reals'!$C$26,2,IF(OR(K46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K46)&gt;0),1,0))+IF(L46='Resultats Reals'!$C$29,2,IF(OR(L46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L46)&gt;0),1,0))+IF(M46='Resultats Reals'!$C$32,2,IF(OR(M46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M46)&gt;0),1,0))+IF(N46='Resultats Reals'!$C$35,2,IF(OR(N46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N46)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BV46">
         <f>IF(O46='Resultats Reals'!$C$3,2,IF(OR(O46='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O46)&gt;0),1,0))+IF(P46='Resultats Reals'!$C$6,2,IF(OR(P46='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P46)&gt;0),1,0))+IF(Q46='Resultats Reals'!$C$9,2,IF(OR(Q46='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q46)&gt;0),1,0))+IF(R46='Resultats Reals'!$C$12,2,IF(OR(R46='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R46)&gt;0),1,0))+IF(S46='Resultats Reals'!$C$15,2,IF(OR(S46='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S46)&gt;0),1,0))+IF(T46='Resultats Reals'!$C$18,2,IF(OR(T46='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T46)&gt;0),1,0))+IF(U46='Resultats Reals'!$C$21,2,IF(OR(U46='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U46)&gt;0),1,0))+IF(V46='Resultats Reals'!$C$24,2,IF(OR(V46='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V46)&gt;0),1,0))+IF(W46='Resultats Reals'!$C$27,2,IF(OR(W46='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W46)&gt;0),1,0))+IF(X46='Resultats Reals'!$C$30,2,IF(OR(X46='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X46)&gt;0),1,0))+IF(Y46='Resultats Reals'!$C$33,2,IF(OR(Y46='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y46)&gt;0),1,0))+IF(Z46='Resultats Reals'!$C$36,2,IF(OR(Z46='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z46)&gt;0),1,0))</f>
@@ -18948,7 +18949,7 @@
       </c>
       <c r="BW46">
         <f>IF(AA46='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0,2,0.5),IF(OR(AA46='Resultats Reals'!$C$2,AA46='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA46)&gt;0),1,0))+IF(AB46='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0,2,0.5),IF(OR(AB46='Resultats Reals'!$C$5,AB46='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB46)&gt;0),1,0))+IF(AC46='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0,2,0.5),IF(OR(AC46='Resultats Reals'!$C$8,AC46='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC46)&gt;0),1,0))+IF(AD46='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0,2,0.5),IF(OR(AD46='Resultats Reals'!$C$11,AD46='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD46)&gt;0),1,0))+IF(AE46='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0,2,0.5),IF(OR(AE46='Resultats Reals'!$C$14,AE46='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE46)&gt;0),1,0))+IF(AF46='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0,2,0.5),IF(OR(AF46='Resultats Reals'!$C$17,AF46='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF46)&gt;0),1,0))+IF(AG46='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0,2,0.5),IF(OR(AG46='Resultats Reals'!$C$20,AG46='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG46)&gt;0),1,0))+IF(AH46='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0,2,0.5),IF(OR(AH46='Resultats Reals'!$C$23,AH46='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH46)&gt;0),1,0))+IF(AI46='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0,2,0.5),IF(OR(AI46='Resultats Reals'!$C$26,AI46='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI46)&gt;0),1,0))+IF(AJ46='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0,2,0.5),IF(OR(AJ46='Resultats Reals'!$C$29,AJ46='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ46)&gt;0),1,0))+IF(AK46='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0,2,0.5),IF(OR(AK46='Resultats Reals'!$C$32,AK46='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK46)&gt;0),1,0))+IF(AL46='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0,2,0.5),IF(OR(AL46='Resultats Reals'!$C$35,AL46='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL46)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX46">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA46)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB46)&gt;0,1,0)</f>
@@ -18984,10 +18985,10 @@
       </c>
       <c r="CF46" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>213</v>
       </c>
@@ -19207,11 +19208,11 @@
       </c>
       <c r="BV47">
         <f>IF(O47='Resultats Reals'!$C$3,2,IF(OR(O47='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O47)&gt;0),1,0))+IF(P47='Resultats Reals'!$C$6,2,IF(OR(P47='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P47)&gt;0),1,0))+IF(Q47='Resultats Reals'!$C$9,2,IF(OR(Q47='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q47)&gt;0),1,0))+IF(R47='Resultats Reals'!$C$12,2,IF(OR(R47='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R47)&gt;0),1,0))+IF(S47='Resultats Reals'!$C$15,2,IF(OR(S47='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S47)&gt;0),1,0))+IF(T47='Resultats Reals'!$C$18,2,IF(OR(T47='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T47)&gt;0),1,0))+IF(U47='Resultats Reals'!$C$21,2,IF(OR(U47='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U47)&gt;0),1,0))+IF(V47='Resultats Reals'!$C$24,2,IF(OR(V47='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V47)&gt;0),1,0))+IF(W47='Resultats Reals'!$C$27,2,IF(OR(W47='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W47)&gt;0),1,0))+IF(X47='Resultats Reals'!$C$30,2,IF(OR(X47='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X47)&gt;0),1,0))+IF(Y47='Resultats Reals'!$C$33,2,IF(OR(Y47='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y47)&gt;0),1,0))+IF(Z47='Resultats Reals'!$C$36,2,IF(OR(Z47='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z47)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BW47">
         <f>IF(AA47='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0,2,0.5),IF(OR(AA47='Resultats Reals'!$C$2,AA47='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA47)&gt;0),1,0))+IF(AB47='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0,2,0.5),IF(OR(AB47='Resultats Reals'!$C$5,AB47='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB47)&gt;0),1,0))+IF(AC47='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0,2,0.5),IF(OR(AC47='Resultats Reals'!$C$8,AC47='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC47)&gt;0),1,0))+IF(AD47='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0,2,0.5),IF(OR(AD47='Resultats Reals'!$C$11,AD47='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD47)&gt;0),1,0))+IF(AE47='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0,2,0.5),IF(OR(AE47='Resultats Reals'!$C$14,AE47='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE47)&gt;0),1,0))+IF(AF47='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0,2,0.5),IF(OR(AF47='Resultats Reals'!$C$17,AF47='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF47)&gt;0),1,0))+IF(AG47='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0,2,0.5),IF(OR(AG47='Resultats Reals'!$C$20,AG47='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG47)&gt;0),1,0))+IF(AH47='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0,2,0.5),IF(OR(AH47='Resultats Reals'!$C$23,AH47='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH47)&gt;0),1,0))+IF(AI47='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0,2,0.5),IF(OR(AI47='Resultats Reals'!$C$26,AI47='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI47)&gt;0),1,0))+IF(AJ47='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0,2,0.5),IF(OR(AJ47='Resultats Reals'!$C$29,AJ47='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ47)&gt;0),1,0))+IF(AK47='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0,2,0.5),IF(OR(AK47='Resultats Reals'!$C$32,AK47='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK47)&gt;0),1,0))+IF(AL47='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0,2,0.5),IF(OR(AL47='Resultats Reals'!$C$35,AL47='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL47)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX47">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA47)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB47)&gt;0,1,0)</f>
@@ -19247,10 +19248,10 @@
       </c>
       <c r="CF47" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>214</v>
       </c>
@@ -19466,7 +19467,7 @@
       </c>
       <c r="BU48">
         <f>IF(C48='Resultats Reals'!$C$2,2,IF(OR(C48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C48)&gt;0),1,0))+IF(D48='Resultats Reals'!$C$5,2,IF(OR(D48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D48)&gt;0),1,0))+IF(E48='Resultats Reals'!$C$8,2,IF(OR(E48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E48)&gt;0),1,0))+IF(F48='Resultats Reals'!$C$11,2,IF(OR(F48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F48)&gt;0),1,0))+IF(G48='Resultats Reals'!$C$14,2,IF(OR(G48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G48)&gt;0),1,0))+IF(H48='Resultats Reals'!$C$17,2,IF(OR(H48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H48)&gt;0),1,0))+IF(I48='Resultats Reals'!$C$20,2,IF(OR(I48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I48)&gt;0),1,0))+IF(J48='Resultats Reals'!$C$23,2,IF(OR(J48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J48)&gt;0),1,0))+IF(K48='Resultats Reals'!$C$26,2,IF(OR(K48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K48)&gt;0),1,0))+IF(L48='Resultats Reals'!$C$29,2,IF(OR(L48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L48)&gt;0),1,0))+IF(M48='Resultats Reals'!$C$32,2,IF(OR(M48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M48)&gt;0),1,0))+IF(N48='Resultats Reals'!$C$35,2,IF(OR(N48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N48)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BV48">
         <f>IF(O48='Resultats Reals'!$C$3,2,IF(OR(O48='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O48)&gt;0),1,0))+IF(P48='Resultats Reals'!$C$6,2,IF(OR(P48='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P48)&gt;0),1,0))+IF(Q48='Resultats Reals'!$C$9,2,IF(OR(Q48='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q48)&gt;0),1,0))+IF(R48='Resultats Reals'!$C$12,2,IF(OR(R48='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R48)&gt;0),1,0))+IF(S48='Resultats Reals'!$C$15,2,IF(OR(S48='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S48)&gt;0),1,0))+IF(T48='Resultats Reals'!$C$18,2,IF(OR(T48='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T48)&gt;0),1,0))+IF(U48='Resultats Reals'!$C$21,2,IF(OR(U48='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U48)&gt;0),1,0))+IF(V48='Resultats Reals'!$C$24,2,IF(OR(V48='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V48)&gt;0),1,0))+IF(W48='Resultats Reals'!$C$27,2,IF(OR(W48='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W48)&gt;0),1,0))+IF(X48='Resultats Reals'!$C$30,2,IF(OR(X48='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X48)&gt;0),1,0))+IF(Y48='Resultats Reals'!$C$33,2,IF(OR(Y48='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y48)&gt;0),1,0))+IF(Z48='Resultats Reals'!$C$36,2,IF(OR(Z48='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z48)&gt;0),1,0))</f>
@@ -19474,7 +19475,7 @@
       </c>
       <c r="BW48">
         <f>IF(AA48='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0,2,0.5),IF(OR(AA48='Resultats Reals'!$C$2,AA48='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA48)&gt;0),1,0))+IF(AB48='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0,2,0.5),IF(OR(AB48='Resultats Reals'!$C$5,AB48='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB48)&gt;0),1,0))+IF(AC48='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0,2,0.5),IF(OR(AC48='Resultats Reals'!$C$8,AC48='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC48)&gt;0),1,0))+IF(AD48='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0,2,0.5),IF(OR(AD48='Resultats Reals'!$C$11,AD48='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD48)&gt;0),1,0))+IF(AE48='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0,2,0.5),IF(OR(AE48='Resultats Reals'!$C$14,AE48='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE48)&gt;0),1,0))+IF(AF48='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0,2,0.5),IF(OR(AF48='Resultats Reals'!$C$17,AF48='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF48)&gt;0),1,0))+IF(AG48='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0,2,0.5),IF(OR(AG48='Resultats Reals'!$C$20,AG48='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG48)&gt;0),1,0))+IF(AH48='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0,2,0.5),IF(OR(AH48='Resultats Reals'!$C$23,AH48='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH48)&gt;0),1,0))+IF(AI48='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0,2,0.5),IF(OR(AI48='Resultats Reals'!$C$26,AI48='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI48)&gt;0),1,0))+IF(AJ48='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0,2,0.5),IF(OR(AJ48='Resultats Reals'!$C$29,AJ48='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ48)&gt;0),1,0))+IF(AK48='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0,2,0.5),IF(OR(AK48='Resultats Reals'!$C$32,AK48='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK48)&gt;0),1,0))+IF(AL48='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0,2,0.5),IF(OR(AL48='Resultats Reals'!$C$35,AL48='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL48)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="BX48">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA48)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB48)&gt;0,1,0)</f>
@@ -19510,10 +19511,10 @@
       </c>
       <c r="CF48" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>215</v>
       </c>
@@ -19732,7 +19733,7 @@
       </c>
       <c r="BU49">
         <f>IF(C49='Resultats Reals'!$C$2,2,IF(OR(C49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C49)&gt;0),1,0))+IF(D49='Resultats Reals'!$C$5,2,IF(OR(D49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D49)&gt;0),1,0))+IF(E49='Resultats Reals'!$C$8,2,IF(OR(E49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E49)&gt;0),1,0))+IF(F49='Resultats Reals'!$C$11,2,IF(OR(F49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F49)&gt;0),1,0))+IF(G49='Resultats Reals'!$C$14,2,IF(OR(G49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G49)&gt;0),1,0))+IF(H49='Resultats Reals'!$C$17,2,IF(OR(H49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H49)&gt;0),1,0))+IF(I49='Resultats Reals'!$C$20,2,IF(OR(I49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I49)&gt;0),1,0))+IF(J49='Resultats Reals'!$C$23,2,IF(OR(J49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J49)&gt;0),1,0))+IF(K49='Resultats Reals'!$C$26,2,IF(OR(K49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K49)&gt;0),1,0))+IF(L49='Resultats Reals'!$C$29,2,IF(OR(L49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L49)&gt;0),1,0))+IF(M49='Resultats Reals'!$C$32,2,IF(OR(M49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M49)&gt;0),1,0))+IF(N49='Resultats Reals'!$C$35,2,IF(OR(N49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N49)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BV49">
         <f>IF(O49='Resultats Reals'!$C$3,2,IF(OR(O49='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O49)&gt;0),1,0))+IF(P49='Resultats Reals'!$C$6,2,IF(OR(P49='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P49)&gt;0),1,0))+IF(Q49='Resultats Reals'!$C$9,2,IF(OR(Q49='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q49)&gt;0),1,0))+IF(R49='Resultats Reals'!$C$12,2,IF(OR(R49='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R49)&gt;0),1,0))+IF(S49='Resultats Reals'!$C$15,2,IF(OR(S49='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S49)&gt;0),1,0))+IF(T49='Resultats Reals'!$C$18,2,IF(OR(T49='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T49)&gt;0),1,0))+IF(U49='Resultats Reals'!$C$21,2,IF(OR(U49='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U49)&gt;0),1,0))+IF(V49='Resultats Reals'!$C$24,2,IF(OR(V49='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V49)&gt;0),1,0))+IF(W49='Resultats Reals'!$C$27,2,IF(OR(W49='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W49)&gt;0),1,0))+IF(X49='Resultats Reals'!$C$30,2,IF(OR(X49='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X49)&gt;0),1,0))+IF(Y49='Resultats Reals'!$C$33,2,IF(OR(Y49='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y49)&gt;0),1,0))+IF(Z49='Resultats Reals'!$C$36,2,IF(OR(Z49='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z49)&gt;0),1,0))</f>
@@ -19740,7 +19741,7 @@
       </c>
       <c r="BW49">
         <f>IF(AA49='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0,2,0.5),IF(OR(AA49='Resultats Reals'!$C$2,AA49='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA49)&gt;0),1,0))+IF(AB49='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0,2,0.5),IF(OR(AB49='Resultats Reals'!$C$5,AB49='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB49)&gt;0),1,0))+IF(AC49='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0,2,0.5),IF(OR(AC49='Resultats Reals'!$C$8,AC49='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC49)&gt;0),1,0))+IF(AD49='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0,2,0.5),IF(OR(AD49='Resultats Reals'!$C$11,AD49='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD49)&gt;0),1,0))+IF(AE49='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0,2,0.5),IF(OR(AE49='Resultats Reals'!$C$14,AE49='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE49)&gt;0),1,0))+IF(AF49='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0,2,0.5),IF(OR(AF49='Resultats Reals'!$C$17,AF49='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF49)&gt;0),1,0))+IF(AG49='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0,2,0.5),IF(OR(AG49='Resultats Reals'!$C$20,AG49='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG49)&gt;0),1,0))+IF(AH49='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0,2,0.5),IF(OR(AH49='Resultats Reals'!$C$23,AH49='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH49)&gt;0),1,0))+IF(AI49='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0,2,0.5),IF(OR(AI49='Resultats Reals'!$C$26,AI49='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI49)&gt;0),1,0))+IF(AJ49='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0,2,0.5),IF(OR(AJ49='Resultats Reals'!$C$29,AJ49='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ49)&gt;0),1,0))+IF(AK49='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0,2,0.5),IF(OR(AK49='Resultats Reals'!$C$32,AK49='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK49)&gt;0),1,0))+IF(AL49='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0,2,0.5),IF(OR(AL49='Resultats Reals'!$C$35,AL49='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL49)&gt;0),1,0))</f>
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="BX49">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA49)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB49)&gt;0,1,0)</f>
@@ -19776,7 +19777,7 @@
       </c>
       <c r="CF49" s="7">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -19787,13 +19788,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.2890625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>244</v>
       </c>
@@ -19801,395 +19802,395 @@
         <v>245</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="15">
         <v>45.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="15">
         <v>45.5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="15">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="15">
         <v>44.5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="15">
         <v>44.5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="15">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="15">
         <v>42.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="15">
         <v>42.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="15">
         <v>42.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="15">
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="15">
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="15">
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="15">
         <v>41.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="15">
         <v>41.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="15">
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="15">
         <v>40.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="15">
         <v>40.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="15">
         <v>40.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="15">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="15">
         <v>39.5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="15">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="15">
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="15">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="15">
         <v>38.5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="15">
         <v>38.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="15">
         <v>38.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="15">
         <v>38.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="15">
         <v>37.5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="15">
         <v>37.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="15">
         <v>37.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="15">
         <v>36.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="15">
         <v>36.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="15">
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="15">
         <v>34.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="15">
         <v>34.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="15">
         <v>34.5</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="15">
         <v>32.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="15">
         <v>28.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="15">
         <v>1906</v>
       </c>
     </row>
@@ -20202,247 +20203,247 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD580F6-5A13-42DB-9425-D37D8B9AE6C2}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.37109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>247</v>
       </c>

--- a/Porra_Mundial_Final_Definitiva.xlsx
+++ b/Porra_Mundial_Final_Definitiva.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/Porra Mundial/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sorigue365-my.sharepoint.com/personal/marc_llopis_sorigue_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_77D7F8CFEFB5B4E2EEC1568F97B647076E5C66F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C495C53-540F-8F4A-8581-D45B33C883F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF45C1D3-80F2-4166-ACDC-440814324E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultats Reals" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -904,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -926,7 +926,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -944,10 +943,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Marc Llopis" refreshedDate="46191.502336689817" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:CF49" sheet="Porra"/>
+    <worksheetSource ref="A1:CF49" sheet="Porra" r:id="rId2"/>
   </cacheSource>
   <cacheFields count="84">
     <cacheField name="Participants" numFmtId="0">
@@ -5400,7 +5403,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="TablaDinámica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Participant">
   <location ref="A1:B50" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="84">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -6008,24 +6011,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O37"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.953125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.953125" customWidth="1"/>
-    <col min="5" max="6" width="16.0078125" customWidth="1"/>
-    <col min="7" max="7" width="14.9296875" customWidth="1"/>
-    <col min="8" max="8" width="13.98828125" customWidth="1"/>
-    <col min="9" max="9" width="18.96484375" customWidth="1"/>
-    <col min="10" max="10" width="14.9296875" customWidth="1"/>
-    <col min="11" max="11" width="11.97265625" customWidth="1"/>
-    <col min="12" max="12" width="14.796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.953125" customWidth="1"/>
-    <col min="14" max="14" width="18.96484375" customWidth="1"/>
-    <col min="15" max="15" width="9.953125" customWidth="1"/>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="19" customWidth="1"/>
+    <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>217</v>
       </c>
@@ -6066,7 +6069,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>227</v>
       </c>
@@ -6107,7 +6110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>227</v>
       </c>
@@ -6139,7 +6142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>227</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>232</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>232</v>
       </c>
@@ -6208,7 +6211,7 @@
         <v>99</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>229</v>
@@ -6223,7 +6226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>232</v>
       </c>
@@ -6249,7 +6252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>233</v>
       </c>
@@ -6257,7 +6260,7 @@
         <v>228</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>89</v>
@@ -6275,7 +6278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>233</v>
       </c>
@@ -6301,7 +6304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -6309,7 +6312,7 @@
         <v>231</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="E10" s="14" t="s">
         <v>90</v>
@@ -6324,7 +6327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>234</v>
       </c>
@@ -6347,7 +6350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>234</v>
       </c>
@@ -6370,7 +6373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>234</v>
       </c>
@@ -6378,7 +6381,7 @@
         <v>231</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E13" s="14" t="str">
         <f>+C18</f>
@@ -6394,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>235</v>
       </c>
@@ -6415,10 +6418,10 @@
         <v>167</v>
       </c>
       <c r="O14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>235</v>
       </c>
@@ -6436,7 +6439,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>235</v>
       </c>
@@ -6454,7 +6457,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
@@ -6472,7 +6475,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>236</v>
       </c>
@@ -6487,7 +6490,7 @@
         <v>Noruega</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>236</v>
       </c>
@@ -6502,7 +6505,7 @@
         <v>França</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>237</v>
       </c>
@@ -6517,7 +6520,7 @@
         <v>Argentina</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>237</v>
       </c>
@@ -6532,7 +6535,7 @@
         <v>Àustria</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>237</v>
       </c>
@@ -6547,7 +6550,7 @@
         <v>Colòmbia</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -6562,7 +6565,7 @@
         <v>RD Congo</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>238</v>
       </c>
@@ -6577,7 +6580,7 @@
         <v>Anglaterra</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>238</v>
       </c>
@@ -6592,7 +6595,7 @@
         <v>Ghana</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>239</v>
       </c>
@@ -6603,11 +6606,11 @@
         <v>118</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>239</v>
       </c>
@@ -6618,10 +6621,10 @@
         <v>94</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>239</v>
       </c>
@@ -6635,7 +6638,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>240</v>
       </c>
@@ -6649,7 +6652,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>240</v>
       </c>
@@ -6663,7 +6666,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>240</v>
       </c>
@@ -6677,7 +6680,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>241</v>
       </c>
@@ -6691,7 +6694,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>241</v>
       </c>
@@ -6705,7 +6708,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>241</v>
       </c>
@@ -6716,7 +6719,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>242</v>
       </c>
@@ -6727,7 +6730,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>242</v>
       </c>
@@ -6738,7 +6741,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>242</v>
       </c>
@@ -6789,81 +6792,81 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CF49"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.45703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.45703125" customWidth="1"/>
-    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.68359375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.953125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.55078125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.28125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="10.76171875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="9.4140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.37109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="13.44921875" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.8359375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="53" max="54" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="56" max="65" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="67" max="68" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="12.9140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="14.52734375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.31640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="10.76171875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="13.85546875" customWidth="1"/>
-    <col min="84" max="84" width="11.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="54" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="56" max="65" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="68" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="12.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="13.88671875" customWidth="1"/>
+    <col min="84" max="84" width="11.109375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -7117,7 +7120,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>84</v>
       </c>
@@ -7333,7 +7336,7 @@
       </c>
       <c r="BU2">
         <f>IF(C2='Resultats Reals'!$C$2,2,IF(OR(C2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C2)&gt;0),1,0))+IF(D2='Resultats Reals'!$C$5,2,IF(OR(D2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D2)&gt;0),1,0))+IF(E2='Resultats Reals'!$C$8,2,IF(OR(E2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E2)&gt;0),1,0))+IF(F2='Resultats Reals'!$C$11,2,IF(OR(F2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F2)&gt;0),1,0))+IF(G2='Resultats Reals'!$C$14,2,IF(OR(G2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G2)&gt;0),1,0))+IF(H2='Resultats Reals'!$C$17,2,IF(OR(H2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H2)&gt;0),1,0))+IF(I2='Resultats Reals'!$C$20,2,IF(OR(I2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I2)&gt;0),1,0))+IF(J2='Resultats Reals'!$C$23,2,IF(OR(J2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J2)&gt;0),1,0))+IF(K2='Resultats Reals'!$C$26,2,IF(OR(K2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K2)&gt;0),1,0))+IF(L2='Resultats Reals'!$C$29,2,IF(OR(L2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L2)&gt;0),1,0))+IF(M2='Resultats Reals'!$C$32,2,IF(OR(M2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M2)&gt;0),1,0))+IF(N2='Resultats Reals'!$C$35,2,IF(OR(N2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N2)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV2">
         <f>IF(O2='Resultats Reals'!$C$3,2,IF(OR(O2='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O2)&gt;0),1,0))+IF(P2='Resultats Reals'!$C$6,2,IF(OR(P2='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P2)&gt;0),1,0))+IF(Q2='Resultats Reals'!$C$9,2,IF(OR(Q2='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q2)&gt;0),1,0))+IF(R2='Resultats Reals'!$C$12,2,IF(OR(R2='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R2)&gt;0),1,0))+IF(S2='Resultats Reals'!$C$15,2,IF(OR(S2='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S2)&gt;0),1,0))+IF(T2='Resultats Reals'!$C$18,2,IF(OR(T2='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T2)&gt;0),1,0))+IF(U2='Resultats Reals'!$C$21,2,IF(OR(U2='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U2)&gt;0),1,0))+IF(V2='Resultats Reals'!$C$24,2,IF(OR(V2='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V2)&gt;0),1,0))+IF(W2='Resultats Reals'!$C$27,2,IF(OR(W2='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W2)&gt;0),1,0))+IF(X2='Resultats Reals'!$C$30,2,IF(OR(X2='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X2)&gt;0),1,0))+IF(Y2='Resultats Reals'!$C$33,2,IF(OR(Y2='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y2)&gt;0),1,0))+IF(Z2='Resultats Reals'!$C$36,2,IF(OR(Z2='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z2)&gt;0),1,0))</f>
@@ -7341,7 +7344,7 @@
       </c>
       <c r="BW2">
         <f>IF(AA2='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0,2,0.5),IF(OR(AA2='Resultats Reals'!$C$2,AA2='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA2)&gt;0),1,0))+IF(AB2='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0,2,0.5),IF(OR(AB2='Resultats Reals'!$C$5,AB2='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB2)&gt;0),1,0))+IF(AC2='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0,2,0.5),IF(OR(AC2='Resultats Reals'!$C$8,AC2='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC2)&gt;0),1,0))+IF(AD2='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0,2,0.5),IF(OR(AD2='Resultats Reals'!$C$11,AD2='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD2)&gt;0),1,0))+IF(AE2='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0,2,0.5),IF(OR(AE2='Resultats Reals'!$C$14,AE2='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE2)&gt;0),1,0))+IF(AF2='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0,2,0.5),IF(OR(AF2='Resultats Reals'!$C$17,AF2='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF2)&gt;0),1,0))+IF(AG2='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0,2,0.5),IF(OR(AG2='Resultats Reals'!$C$20,AG2='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG2)&gt;0),1,0))+IF(AH2='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0,2,0.5),IF(OR(AH2='Resultats Reals'!$C$23,AH2='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH2)&gt;0),1,0))+IF(AI2='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0,2,0.5),IF(OR(AI2='Resultats Reals'!$C$26,AI2='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI2)&gt;0),1,0))+IF(AJ2='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0,2,0.5),IF(OR(AJ2='Resultats Reals'!$C$29,AJ2='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ2)&gt;0),1,0))+IF(AK2='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0,2,0.5),IF(OR(AK2='Resultats Reals'!$C$32,AK2='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK2)&gt;0),1,0))+IF(AL2='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0,2,0.5),IF(OR(AL2='Resultats Reals'!$C$35,AL2='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL2)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA2)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB2)&gt;0,1,0)</f>
@@ -7377,10 +7380,10 @@
       </c>
       <c r="CF2" s="7">
         <f t="shared" ref="CF2:CF49" si="0">SUM(BU2:CE2)</f>
-        <v>43.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -7596,7 +7599,7 @@
       </c>
       <c r="BU3">
         <f>IF(C3='Resultats Reals'!$C$2,2,IF(OR(C3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C3)&gt;0),1,0))+IF(D3='Resultats Reals'!$C$5,2,IF(OR(D3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D3)&gt;0),1,0))+IF(E3='Resultats Reals'!$C$8,2,IF(OR(E3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E3)&gt;0),1,0))+IF(F3='Resultats Reals'!$C$11,2,IF(OR(F3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F3)&gt;0),1,0))+IF(G3='Resultats Reals'!$C$14,2,IF(OR(G3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G3)&gt;0),1,0))+IF(H3='Resultats Reals'!$C$17,2,IF(OR(H3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H3)&gt;0),1,0))+IF(I3='Resultats Reals'!$C$20,2,IF(OR(I3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I3)&gt;0),1,0))+IF(J3='Resultats Reals'!$C$23,2,IF(OR(J3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J3)&gt;0),1,0))+IF(K3='Resultats Reals'!$C$26,2,IF(OR(K3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K3)&gt;0),1,0))+IF(L3='Resultats Reals'!$C$29,2,IF(OR(L3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L3)&gt;0),1,0))+IF(M3='Resultats Reals'!$C$32,2,IF(OR(M3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M3)&gt;0),1,0))+IF(N3='Resultats Reals'!$C$35,2,IF(OR(N3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N3)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV3">
         <f>IF(O3='Resultats Reals'!$C$3,2,IF(OR(O3='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O3)&gt;0),1,0))+IF(P3='Resultats Reals'!$C$6,2,IF(OR(P3='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P3)&gt;0),1,0))+IF(Q3='Resultats Reals'!$C$9,2,IF(OR(Q3='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q3)&gt;0),1,0))+IF(R3='Resultats Reals'!$C$12,2,IF(OR(R3='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R3)&gt;0),1,0))+IF(S3='Resultats Reals'!$C$15,2,IF(OR(S3='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S3)&gt;0),1,0))+IF(T3='Resultats Reals'!$C$18,2,IF(OR(T3='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T3)&gt;0),1,0))+IF(U3='Resultats Reals'!$C$21,2,IF(OR(U3='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U3)&gt;0),1,0))+IF(V3='Resultats Reals'!$C$24,2,IF(OR(V3='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V3)&gt;0),1,0))+IF(W3='Resultats Reals'!$C$27,2,IF(OR(W3='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W3)&gt;0),1,0))+IF(X3='Resultats Reals'!$C$30,2,IF(OR(X3='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X3)&gt;0),1,0))+IF(Y3='Resultats Reals'!$C$33,2,IF(OR(Y3='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y3)&gt;0),1,0))+IF(Z3='Resultats Reals'!$C$36,2,IF(OR(Z3='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z3)&gt;0),1,0))</f>
@@ -7604,7 +7607,7 @@
       </c>
       <c r="BW3">
         <f>IF(AA3='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0,2,0.5),IF(OR(AA3='Resultats Reals'!$C$2,AA3='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA3)&gt;0),1,0))+IF(AB3='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0,2,0.5),IF(OR(AB3='Resultats Reals'!$C$5,AB3='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB3)&gt;0),1,0))+IF(AC3='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0,2,0.5),IF(OR(AC3='Resultats Reals'!$C$8,AC3='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC3)&gt;0),1,0))+IF(AD3='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0,2,0.5),IF(OR(AD3='Resultats Reals'!$C$11,AD3='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD3)&gt;0),1,0))+IF(AE3='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0,2,0.5),IF(OR(AE3='Resultats Reals'!$C$14,AE3='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE3)&gt;0),1,0))+IF(AF3='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0,2,0.5),IF(OR(AF3='Resultats Reals'!$C$17,AF3='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF3)&gt;0),1,0))+IF(AG3='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0,2,0.5),IF(OR(AG3='Resultats Reals'!$C$20,AG3='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG3)&gt;0),1,0))+IF(AH3='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0,2,0.5),IF(OR(AH3='Resultats Reals'!$C$23,AH3='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH3)&gt;0),1,0))+IF(AI3='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0,2,0.5),IF(OR(AI3='Resultats Reals'!$C$26,AI3='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI3)&gt;0),1,0))+IF(AJ3='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0,2,0.5),IF(OR(AJ3='Resultats Reals'!$C$29,AJ3='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ3)&gt;0),1,0))+IF(AK3='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0,2,0.5),IF(OR(AK3='Resultats Reals'!$C$32,AK3='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK3)&gt;0),1,0))+IF(AL3='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0,2,0.5),IF(OR(AL3='Resultats Reals'!$C$35,AL3='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL3)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX3">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA3)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB3)&gt;0,1,0)</f>
@@ -7640,10 +7643,10 @@
       </c>
       <c r="CF3" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="4" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -7859,7 +7862,7 @@
       </c>
       <c r="BU4">
         <f>IF(C4='Resultats Reals'!$C$2,2,IF(OR(C4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C4)&gt;0),1,0))+IF(D4='Resultats Reals'!$C$5,2,IF(OR(D4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D4)&gt;0),1,0))+IF(E4='Resultats Reals'!$C$8,2,IF(OR(E4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E4)&gt;0),1,0))+IF(F4='Resultats Reals'!$C$11,2,IF(OR(F4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F4)&gt;0),1,0))+IF(G4='Resultats Reals'!$C$14,2,IF(OR(G4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G4)&gt;0),1,0))+IF(H4='Resultats Reals'!$C$17,2,IF(OR(H4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H4)&gt;0),1,0))+IF(I4='Resultats Reals'!$C$20,2,IF(OR(I4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I4)&gt;0),1,0))+IF(J4='Resultats Reals'!$C$23,2,IF(OR(J4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J4)&gt;0),1,0))+IF(K4='Resultats Reals'!$C$26,2,IF(OR(K4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K4)&gt;0),1,0))+IF(L4='Resultats Reals'!$C$29,2,IF(OR(L4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L4)&gt;0),1,0))+IF(M4='Resultats Reals'!$C$32,2,IF(OR(M4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M4)&gt;0),1,0))+IF(N4='Resultats Reals'!$C$35,2,IF(OR(N4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N4)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV4">
         <f>IF(O4='Resultats Reals'!$C$3,2,IF(OR(O4='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O4)&gt;0),1,0))+IF(P4='Resultats Reals'!$C$6,2,IF(OR(P4='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P4)&gt;0),1,0))+IF(Q4='Resultats Reals'!$C$9,2,IF(OR(Q4='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q4)&gt;0),1,0))+IF(R4='Resultats Reals'!$C$12,2,IF(OR(R4='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R4)&gt;0),1,0))+IF(S4='Resultats Reals'!$C$15,2,IF(OR(S4='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S4)&gt;0),1,0))+IF(T4='Resultats Reals'!$C$18,2,IF(OR(T4='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T4)&gt;0),1,0))+IF(U4='Resultats Reals'!$C$21,2,IF(OR(U4='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U4)&gt;0),1,0))+IF(V4='Resultats Reals'!$C$24,2,IF(OR(V4='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V4)&gt;0),1,0))+IF(W4='Resultats Reals'!$C$27,2,IF(OR(W4='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W4)&gt;0),1,0))+IF(X4='Resultats Reals'!$C$30,2,IF(OR(X4='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X4)&gt;0),1,0))+IF(Y4='Resultats Reals'!$C$33,2,IF(OR(Y4='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y4)&gt;0),1,0))+IF(Z4='Resultats Reals'!$C$36,2,IF(OR(Z4='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z4)&gt;0),1,0))</f>
@@ -7867,7 +7870,7 @@
       </c>
       <c r="BW4">
         <f>IF(AA4='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0,2,0.5),IF(OR(AA4='Resultats Reals'!$C$2,AA4='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA4)&gt;0),1,0))+IF(AB4='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0,2,0.5),IF(OR(AB4='Resultats Reals'!$C$5,AB4='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB4)&gt;0),1,0))+IF(AC4='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0,2,0.5),IF(OR(AC4='Resultats Reals'!$C$8,AC4='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC4)&gt;0),1,0))+IF(AD4='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0,2,0.5),IF(OR(AD4='Resultats Reals'!$C$11,AD4='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD4)&gt;0),1,0))+IF(AE4='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0,2,0.5),IF(OR(AE4='Resultats Reals'!$C$14,AE4='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE4)&gt;0),1,0))+IF(AF4='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0,2,0.5),IF(OR(AF4='Resultats Reals'!$C$17,AF4='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF4)&gt;0),1,0))+IF(AG4='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0,2,0.5),IF(OR(AG4='Resultats Reals'!$C$20,AG4='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG4)&gt;0),1,0))+IF(AH4='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0,2,0.5),IF(OR(AH4='Resultats Reals'!$C$23,AH4='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH4)&gt;0),1,0))+IF(AI4='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0,2,0.5),IF(OR(AI4='Resultats Reals'!$C$26,AI4='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI4)&gt;0),1,0))+IF(AJ4='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0,2,0.5),IF(OR(AJ4='Resultats Reals'!$C$29,AJ4='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ4)&gt;0),1,0))+IF(AK4='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0,2,0.5),IF(OR(AK4='Resultats Reals'!$C$32,AK4='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK4)&gt;0),1,0))+IF(AL4='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0,2,0.5),IF(OR(AL4='Resultats Reals'!$C$35,AL4='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL4)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX4">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA4)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB4)&gt;0,1,0)</f>
@@ -7903,10 +7906,10 @@
       </c>
       <c r="CF4" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -8122,7 +8125,7 @@
       </c>
       <c r="BU5">
         <f>IF(C5='Resultats Reals'!$C$2,2,IF(OR(C5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C5)&gt;0),1,0))+IF(D5='Resultats Reals'!$C$5,2,IF(OR(D5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D5)&gt;0),1,0))+IF(E5='Resultats Reals'!$C$8,2,IF(OR(E5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E5)&gt;0),1,0))+IF(F5='Resultats Reals'!$C$11,2,IF(OR(F5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F5)&gt;0),1,0))+IF(G5='Resultats Reals'!$C$14,2,IF(OR(G5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G5)&gt;0),1,0))+IF(H5='Resultats Reals'!$C$17,2,IF(OR(H5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H5)&gt;0),1,0))+IF(I5='Resultats Reals'!$C$20,2,IF(OR(I5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I5)&gt;0),1,0))+IF(J5='Resultats Reals'!$C$23,2,IF(OR(J5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J5)&gt;0),1,0))+IF(K5='Resultats Reals'!$C$26,2,IF(OR(K5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K5)&gt;0),1,0))+IF(L5='Resultats Reals'!$C$29,2,IF(OR(L5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L5)&gt;0),1,0))+IF(M5='Resultats Reals'!$C$32,2,IF(OR(M5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M5)&gt;0),1,0))+IF(N5='Resultats Reals'!$C$35,2,IF(OR(N5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N5)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV5">
         <f>IF(O5='Resultats Reals'!$C$3,2,IF(OR(O5='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O5)&gt;0),1,0))+IF(P5='Resultats Reals'!$C$6,2,IF(OR(P5='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P5)&gt;0),1,0))+IF(Q5='Resultats Reals'!$C$9,2,IF(OR(Q5='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q5)&gt;0),1,0))+IF(R5='Resultats Reals'!$C$12,2,IF(OR(R5='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R5)&gt;0),1,0))+IF(S5='Resultats Reals'!$C$15,2,IF(OR(S5='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S5)&gt;0),1,0))+IF(T5='Resultats Reals'!$C$18,2,IF(OR(T5='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T5)&gt;0),1,0))+IF(U5='Resultats Reals'!$C$21,2,IF(OR(U5='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U5)&gt;0),1,0))+IF(V5='Resultats Reals'!$C$24,2,IF(OR(V5='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V5)&gt;0),1,0))+IF(W5='Resultats Reals'!$C$27,2,IF(OR(W5='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W5)&gt;0),1,0))+IF(X5='Resultats Reals'!$C$30,2,IF(OR(X5='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X5)&gt;0),1,0))+IF(Y5='Resultats Reals'!$C$33,2,IF(OR(Y5='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y5)&gt;0),1,0))+IF(Z5='Resultats Reals'!$C$36,2,IF(OR(Z5='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z5)&gt;0),1,0))</f>
@@ -8130,7 +8133,7 @@
       </c>
       <c r="BW5">
         <f>IF(AA5='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0,2,0.5),IF(OR(AA5='Resultats Reals'!$C$2,AA5='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA5)&gt;0),1,0))+IF(AB5='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0,2,0.5),IF(OR(AB5='Resultats Reals'!$C$5,AB5='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB5)&gt;0),1,0))+IF(AC5='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0,2,0.5),IF(OR(AC5='Resultats Reals'!$C$8,AC5='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC5)&gt;0),1,0))+IF(AD5='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0,2,0.5),IF(OR(AD5='Resultats Reals'!$C$11,AD5='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD5)&gt;0),1,0))+IF(AE5='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0,2,0.5),IF(OR(AE5='Resultats Reals'!$C$14,AE5='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE5)&gt;0),1,0))+IF(AF5='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0,2,0.5),IF(OR(AF5='Resultats Reals'!$C$17,AF5='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF5)&gt;0),1,0))+IF(AG5='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0,2,0.5),IF(OR(AG5='Resultats Reals'!$C$20,AG5='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG5)&gt;0),1,0))+IF(AH5='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0,2,0.5),IF(OR(AH5='Resultats Reals'!$C$23,AH5='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH5)&gt;0),1,0))+IF(AI5='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0,2,0.5),IF(OR(AI5='Resultats Reals'!$C$26,AI5='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI5)&gt;0),1,0))+IF(AJ5='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0,2,0.5),IF(OR(AJ5='Resultats Reals'!$C$29,AJ5='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ5)&gt;0),1,0))+IF(AK5='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0,2,0.5),IF(OR(AK5='Resultats Reals'!$C$32,AK5='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK5)&gt;0),1,0))+IF(AL5='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0,2,0.5),IF(OR(AL5='Resultats Reals'!$C$35,AL5='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL5)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA5)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB5)&gt;0,1,0)</f>
@@ -8166,10 +8169,10 @@
       </c>
       <c r="CF5" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="6" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>137</v>
       </c>
@@ -8385,7 +8388,7 @@
       </c>
       <c r="BU6">
         <f>IF(C6='Resultats Reals'!$C$2,2,IF(OR(C6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C6)&gt;0),1,0))+IF(D6='Resultats Reals'!$C$5,2,IF(OR(D6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D6)&gt;0),1,0))+IF(E6='Resultats Reals'!$C$8,2,IF(OR(E6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E6)&gt;0),1,0))+IF(F6='Resultats Reals'!$C$11,2,IF(OR(F6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F6)&gt;0),1,0))+IF(G6='Resultats Reals'!$C$14,2,IF(OR(G6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G6)&gt;0),1,0))+IF(H6='Resultats Reals'!$C$17,2,IF(OR(H6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H6)&gt;0),1,0))+IF(I6='Resultats Reals'!$C$20,2,IF(OR(I6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I6)&gt;0),1,0))+IF(J6='Resultats Reals'!$C$23,2,IF(OR(J6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J6)&gt;0),1,0))+IF(K6='Resultats Reals'!$C$26,2,IF(OR(K6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K6)&gt;0),1,0))+IF(L6='Resultats Reals'!$C$29,2,IF(OR(L6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L6)&gt;0),1,0))+IF(M6='Resultats Reals'!$C$32,2,IF(OR(M6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M6)&gt;0),1,0))+IF(N6='Resultats Reals'!$C$35,2,IF(OR(N6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N6)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV6">
         <f>IF(O6='Resultats Reals'!$C$3,2,IF(OR(O6='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O6)&gt;0),1,0))+IF(P6='Resultats Reals'!$C$6,2,IF(OR(P6='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P6)&gt;0),1,0))+IF(Q6='Resultats Reals'!$C$9,2,IF(OR(Q6='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q6)&gt;0),1,0))+IF(R6='Resultats Reals'!$C$12,2,IF(OR(R6='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R6)&gt;0),1,0))+IF(S6='Resultats Reals'!$C$15,2,IF(OR(S6='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S6)&gt;0),1,0))+IF(T6='Resultats Reals'!$C$18,2,IF(OR(T6='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T6)&gt;0),1,0))+IF(U6='Resultats Reals'!$C$21,2,IF(OR(U6='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U6)&gt;0),1,0))+IF(V6='Resultats Reals'!$C$24,2,IF(OR(V6='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V6)&gt;0),1,0))+IF(W6='Resultats Reals'!$C$27,2,IF(OR(W6='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W6)&gt;0),1,0))+IF(X6='Resultats Reals'!$C$30,2,IF(OR(X6='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X6)&gt;0),1,0))+IF(Y6='Resultats Reals'!$C$33,2,IF(OR(Y6='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y6)&gt;0),1,0))+IF(Z6='Resultats Reals'!$C$36,2,IF(OR(Z6='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z6)&gt;0),1,0))</f>
@@ -8393,7 +8396,7 @@
       </c>
       <c r="BW6">
         <f>IF(AA6='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0,2,0.5),IF(OR(AA6='Resultats Reals'!$C$2,AA6='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA6)&gt;0),1,0))+IF(AB6='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0,2,0.5),IF(OR(AB6='Resultats Reals'!$C$5,AB6='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB6)&gt;0),1,0))+IF(AC6='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0,2,0.5),IF(OR(AC6='Resultats Reals'!$C$8,AC6='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC6)&gt;0),1,0))+IF(AD6='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0,2,0.5),IF(OR(AD6='Resultats Reals'!$C$11,AD6='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD6)&gt;0),1,0))+IF(AE6='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0,2,0.5),IF(OR(AE6='Resultats Reals'!$C$14,AE6='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE6)&gt;0),1,0))+IF(AF6='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0,2,0.5),IF(OR(AF6='Resultats Reals'!$C$17,AF6='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF6)&gt;0),1,0))+IF(AG6='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0,2,0.5),IF(OR(AG6='Resultats Reals'!$C$20,AG6='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG6)&gt;0),1,0))+IF(AH6='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0,2,0.5),IF(OR(AH6='Resultats Reals'!$C$23,AH6='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH6)&gt;0),1,0))+IF(AI6='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0,2,0.5),IF(OR(AI6='Resultats Reals'!$C$26,AI6='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI6)&gt;0),1,0))+IF(AJ6='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0,2,0.5),IF(OR(AJ6='Resultats Reals'!$C$29,AJ6='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ6)&gt;0),1,0))+IF(AK6='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0,2,0.5),IF(OR(AK6='Resultats Reals'!$C$32,AK6='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK6)&gt;0),1,0))+IF(AL6='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0,2,0.5),IF(OR(AL6='Resultats Reals'!$C$35,AL6='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL6)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX6">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA6)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB6)&gt;0,1,0)</f>
@@ -8429,10 +8432,10 @@
       </c>
       <c r="CF6" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>43.5</v>
       </c>
     </row>
-    <row r="7" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -8656,7 +8659,7 @@
       </c>
       <c r="BW7">
         <f>IF(AA7='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0,2,0.5),IF(OR(AA7='Resultats Reals'!$C$2,AA7='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA7)&gt;0),1,0))+IF(AB7='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0,2,0.5),IF(OR(AB7='Resultats Reals'!$C$5,AB7='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB7)&gt;0),1,0))+IF(AC7='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0,2,0.5),IF(OR(AC7='Resultats Reals'!$C$8,AC7='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC7)&gt;0),1,0))+IF(AD7='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0,2,0.5),IF(OR(AD7='Resultats Reals'!$C$11,AD7='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD7)&gt;0),1,0))+IF(AE7='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0,2,0.5),IF(OR(AE7='Resultats Reals'!$C$14,AE7='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE7)&gt;0),1,0))+IF(AF7='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0,2,0.5),IF(OR(AF7='Resultats Reals'!$C$17,AF7='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF7)&gt;0),1,0))+IF(AG7='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0,2,0.5),IF(OR(AG7='Resultats Reals'!$C$20,AG7='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG7)&gt;0),1,0))+IF(AH7='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0,2,0.5),IF(OR(AH7='Resultats Reals'!$C$23,AH7='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH7)&gt;0),1,0))+IF(AI7='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0,2,0.5),IF(OR(AI7='Resultats Reals'!$C$26,AI7='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI7)&gt;0),1,0))+IF(AJ7='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0,2,0.5),IF(OR(AJ7='Resultats Reals'!$C$29,AJ7='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ7)&gt;0),1,0))+IF(AK7='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0,2,0.5),IF(OR(AK7='Resultats Reals'!$C$32,AK7='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK7)&gt;0),1,0))+IF(AL7='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0,2,0.5),IF(OR(AL7='Resultats Reals'!$C$35,AL7='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL7)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX7">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA7)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB7)&gt;0,1,0)</f>
@@ -8692,10 +8695,10 @@
       </c>
       <c r="CF7" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="8" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>140</v>
       </c>
@@ -8911,7 +8914,7 @@
       </c>
       <c r="BU8">
         <f>IF(C8='Resultats Reals'!$C$2,2,IF(OR(C8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C8)&gt;0),1,0))+IF(D8='Resultats Reals'!$C$5,2,IF(OR(D8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D8)&gt;0),1,0))+IF(E8='Resultats Reals'!$C$8,2,IF(OR(E8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E8)&gt;0),1,0))+IF(F8='Resultats Reals'!$C$11,2,IF(OR(F8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F8)&gt;0),1,0))+IF(G8='Resultats Reals'!$C$14,2,IF(OR(G8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G8)&gt;0),1,0))+IF(H8='Resultats Reals'!$C$17,2,IF(OR(H8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H8)&gt;0),1,0))+IF(I8='Resultats Reals'!$C$20,2,IF(OR(I8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I8)&gt;0),1,0))+IF(J8='Resultats Reals'!$C$23,2,IF(OR(J8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J8)&gt;0),1,0))+IF(K8='Resultats Reals'!$C$26,2,IF(OR(K8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K8)&gt;0),1,0))+IF(L8='Resultats Reals'!$C$29,2,IF(OR(L8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L8)&gt;0),1,0))+IF(M8='Resultats Reals'!$C$32,2,IF(OR(M8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M8)&gt;0),1,0))+IF(N8='Resultats Reals'!$C$35,2,IF(OR(N8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N8)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BV8">
         <f>IF(O8='Resultats Reals'!$C$3,2,IF(OR(O8='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O8)&gt;0),1,0))+IF(P8='Resultats Reals'!$C$6,2,IF(OR(P8='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P8)&gt;0),1,0))+IF(Q8='Resultats Reals'!$C$9,2,IF(OR(Q8='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q8)&gt;0),1,0))+IF(R8='Resultats Reals'!$C$12,2,IF(OR(R8='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R8)&gt;0),1,0))+IF(S8='Resultats Reals'!$C$15,2,IF(OR(S8='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S8)&gt;0),1,0))+IF(T8='Resultats Reals'!$C$18,2,IF(OR(T8='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T8)&gt;0),1,0))+IF(U8='Resultats Reals'!$C$21,2,IF(OR(U8='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U8)&gt;0),1,0))+IF(V8='Resultats Reals'!$C$24,2,IF(OR(V8='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V8)&gt;0),1,0))+IF(W8='Resultats Reals'!$C$27,2,IF(OR(W8='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W8)&gt;0),1,0))+IF(X8='Resultats Reals'!$C$30,2,IF(OR(X8='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X8)&gt;0),1,0))+IF(Y8='Resultats Reals'!$C$33,2,IF(OR(Y8='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y8)&gt;0),1,0))+IF(Z8='Resultats Reals'!$C$36,2,IF(OR(Z8='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z8)&gt;0),1,0))</f>
@@ -8919,7 +8922,7 @@
       </c>
       <c r="BW8">
         <f>IF(AA8='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0,2,0.5),IF(OR(AA8='Resultats Reals'!$C$2,AA8='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA8)&gt;0),1,0))+IF(AB8='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0,2,0.5),IF(OR(AB8='Resultats Reals'!$C$5,AB8='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB8)&gt;0),1,0))+IF(AC8='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0,2,0.5),IF(OR(AC8='Resultats Reals'!$C$8,AC8='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC8)&gt;0),1,0))+IF(AD8='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0,2,0.5),IF(OR(AD8='Resultats Reals'!$C$11,AD8='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD8)&gt;0),1,0))+IF(AE8='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0,2,0.5),IF(OR(AE8='Resultats Reals'!$C$14,AE8='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE8)&gt;0),1,0))+IF(AF8='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0,2,0.5),IF(OR(AF8='Resultats Reals'!$C$17,AF8='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF8)&gt;0),1,0))+IF(AG8='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0,2,0.5),IF(OR(AG8='Resultats Reals'!$C$20,AG8='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG8)&gt;0),1,0))+IF(AH8='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0,2,0.5),IF(OR(AH8='Resultats Reals'!$C$23,AH8='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH8)&gt;0),1,0))+IF(AI8='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0,2,0.5),IF(OR(AI8='Resultats Reals'!$C$26,AI8='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI8)&gt;0),1,0))+IF(AJ8='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0,2,0.5),IF(OR(AJ8='Resultats Reals'!$C$29,AJ8='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ8)&gt;0),1,0))+IF(AK8='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0,2,0.5),IF(OR(AK8='Resultats Reals'!$C$32,AK8='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK8)&gt;0),1,0))+IF(AL8='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0,2,0.5),IF(OR(AL8='Resultats Reals'!$C$35,AL8='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL8)&gt;0),1,0))</f>
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BX8">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA8)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB8)&gt;0,1,0)</f>
@@ -8955,10 +8958,10 @@
       </c>
       <c r="CF8" s="7">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30.5</v>
       </c>
     </row>
-    <row r="9" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -9185,7 +9188,7 @@
       </c>
       <c r="BW9">
         <f>IF(AA9='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0,2,0.5),IF(OR(AA9='Resultats Reals'!$C$2,AA9='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA9)&gt;0),1,0))+IF(AB9='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0,2,0.5),IF(OR(AB9='Resultats Reals'!$C$5,AB9='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB9)&gt;0),1,0))+IF(AC9='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0,2,0.5),IF(OR(AC9='Resultats Reals'!$C$8,AC9='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC9)&gt;0),1,0))+IF(AD9='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0,2,0.5),IF(OR(AD9='Resultats Reals'!$C$11,AD9='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD9)&gt;0),1,0))+IF(AE9='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0,2,0.5),IF(OR(AE9='Resultats Reals'!$C$14,AE9='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE9)&gt;0),1,0))+IF(AF9='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0,2,0.5),IF(OR(AF9='Resultats Reals'!$C$17,AF9='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF9)&gt;0),1,0))+IF(AG9='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0,2,0.5),IF(OR(AG9='Resultats Reals'!$C$20,AG9='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG9)&gt;0),1,0))+IF(AH9='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0,2,0.5),IF(OR(AH9='Resultats Reals'!$C$23,AH9='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH9)&gt;0),1,0))+IF(AI9='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0,2,0.5),IF(OR(AI9='Resultats Reals'!$C$26,AI9='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI9)&gt;0),1,0))+IF(AJ9='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0,2,0.5),IF(OR(AJ9='Resultats Reals'!$C$29,AJ9='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ9)&gt;0),1,0))+IF(AK9='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0,2,0.5),IF(OR(AK9='Resultats Reals'!$C$32,AK9='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK9)&gt;0),1,0))+IF(AL9='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0,2,0.5),IF(OR(AL9='Resultats Reals'!$C$35,AL9='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL9)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX9">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA9)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB9)&gt;0,1,0)</f>
@@ -9221,10 +9224,10 @@
       </c>
       <c r="CF9" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>150</v>
       </c>
@@ -9440,15 +9443,15 @@
       </c>
       <c r="BU10">
         <f>IF(C10='Resultats Reals'!$C$2,2,IF(OR(C10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C10)&gt;0),1,0))+IF(D10='Resultats Reals'!$C$5,2,IF(OR(D10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D10)&gt;0),1,0))+IF(E10='Resultats Reals'!$C$8,2,IF(OR(E10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E10)&gt;0),1,0))+IF(F10='Resultats Reals'!$C$11,2,IF(OR(F10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F10)&gt;0),1,0))+IF(G10='Resultats Reals'!$C$14,2,IF(OR(G10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G10)&gt;0),1,0))+IF(H10='Resultats Reals'!$C$17,2,IF(OR(H10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H10)&gt;0),1,0))+IF(I10='Resultats Reals'!$C$20,2,IF(OR(I10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I10)&gt;0),1,0))+IF(J10='Resultats Reals'!$C$23,2,IF(OR(J10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J10)&gt;0),1,0))+IF(K10='Resultats Reals'!$C$26,2,IF(OR(K10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K10)&gt;0),1,0))+IF(L10='Resultats Reals'!$C$29,2,IF(OR(L10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L10)&gt;0),1,0))+IF(M10='Resultats Reals'!$C$32,2,IF(OR(M10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M10)&gt;0),1,0))+IF(N10='Resultats Reals'!$C$35,2,IF(OR(N10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N10)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV10">
         <f>IF(O10='Resultats Reals'!$C$3,2,IF(OR(O10='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O10)&gt;0),1,0))+IF(P10='Resultats Reals'!$C$6,2,IF(OR(P10='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P10)&gt;0),1,0))+IF(Q10='Resultats Reals'!$C$9,2,IF(OR(Q10='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q10)&gt;0),1,0))+IF(R10='Resultats Reals'!$C$12,2,IF(OR(R10='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R10)&gt;0),1,0))+IF(S10='Resultats Reals'!$C$15,2,IF(OR(S10='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S10)&gt;0),1,0))+IF(T10='Resultats Reals'!$C$18,2,IF(OR(T10='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T10)&gt;0),1,0))+IF(U10='Resultats Reals'!$C$21,2,IF(OR(U10='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U10)&gt;0),1,0))+IF(V10='Resultats Reals'!$C$24,2,IF(OR(V10='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V10)&gt;0),1,0))+IF(W10='Resultats Reals'!$C$27,2,IF(OR(W10='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W10)&gt;0),1,0))+IF(X10='Resultats Reals'!$C$30,2,IF(OR(X10='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X10)&gt;0),1,0))+IF(Y10='Resultats Reals'!$C$33,2,IF(OR(Y10='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y10)&gt;0),1,0))+IF(Z10='Resultats Reals'!$C$36,2,IF(OR(Z10='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z10)&gt;0),1,0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BW10">
         <f>IF(AA10='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0,2,0.5),IF(OR(AA10='Resultats Reals'!$C$2,AA10='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA10)&gt;0),1,0))+IF(AB10='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0,2,0.5),IF(OR(AB10='Resultats Reals'!$C$5,AB10='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB10)&gt;0),1,0))+IF(AC10='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0,2,0.5),IF(OR(AC10='Resultats Reals'!$C$8,AC10='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC10)&gt;0),1,0))+IF(AD10='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0,2,0.5),IF(OR(AD10='Resultats Reals'!$C$11,AD10='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD10)&gt;0),1,0))+IF(AE10='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0,2,0.5),IF(OR(AE10='Resultats Reals'!$C$14,AE10='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE10)&gt;0),1,0))+IF(AF10='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0,2,0.5),IF(OR(AF10='Resultats Reals'!$C$17,AF10='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF10)&gt;0),1,0))+IF(AG10='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0,2,0.5),IF(OR(AG10='Resultats Reals'!$C$20,AG10='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG10)&gt;0),1,0))+IF(AH10='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0,2,0.5),IF(OR(AH10='Resultats Reals'!$C$23,AH10='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH10)&gt;0),1,0))+IF(AI10='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0,2,0.5),IF(OR(AI10='Resultats Reals'!$C$26,AI10='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI10)&gt;0),1,0))+IF(AJ10='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0,2,0.5),IF(OR(AJ10='Resultats Reals'!$C$29,AJ10='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ10)&gt;0),1,0))+IF(AK10='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0,2,0.5),IF(OR(AK10='Resultats Reals'!$C$32,AK10='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK10)&gt;0),1,0))+IF(AL10='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0,2,0.5),IF(OR(AL10='Resultats Reals'!$C$35,AL10='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL10)&gt;0),1,0))</f>
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX10">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA10)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB10)&gt;0,1,0)</f>
@@ -9484,10 +9487,10 @@
       </c>
       <c r="CF10" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="11" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -9703,7 +9706,7 @@
       </c>
       <c r="BU11">
         <f>IF(C11='Resultats Reals'!$C$2,2,IF(OR(C11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C11)&gt;0),1,0))+IF(D11='Resultats Reals'!$C$5,2,IF(OR(D11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D11)&gt;0),1,0))+IF(E11='Resultats Reals'!$C$8,2,IF(OR(E11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E11)&gt;0),1,0))+IF(F11='Resultats Reals'!$C$11,2,IF(OR(F11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F11)&gt;0),1,0))+IF(G11='Resultats Reals'!$C$14,2,IF(OR(G11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G11)&gt;0),1,0))+IF(H11='Resultats Reals'!$C$17,2,IF(OR(H11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H11)&gt;0),1,0))+IF(I11='Resultats Reals'!$C$20,2,IF(OR(I11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I11)&gt;0),1,0))+IF(J11='Resultats Reals'!$C$23,2,IF(OR(J11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J11)&gt;0),1,0))+IF(K11='Resultats Reals'!$C$26,2,IF(OR(K11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K11)&gt;0),1,0))+IF(L11='Resultats Reals'!$C$29,2,IF(OR(L11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L11)&gt;0),1,0))+IF(M11='Resultats Reals'!$C$32,2,IF(OR(M11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M11)&gt;0),1,0))+IF(N11='Resultats Reals'!$C$35,2,IF(OR(N11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N11)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV11">
         <f>IF(O11='Resultats Reals'!$C$3,2,IF(OR(O11='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O11)&gt;0),1,0))+IF(P11='Resultats Reals'!$C$6,2,IF(OR(P11='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P11)&gt;0),1,0))+IF(Q11='Resultats Reals'!$C$9,2,IF(OR(Q11='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q11)&gt;0),1,0))+IF(R11='Resultats Reals'!$C$12,2,IF(OR(R11='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R11)&gt;0),1,0))+IF(S11='Resultats Reals'!$C$15,2,IF(OR(S11='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S11)&gt;0),1,0))+IF(T11='Resultats Reals'!$C$18,2,IF(OR(T11='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T11)&gt;0),1,0))+IF(U11='Resultats Reals'!$C$21,2,IF(OR(U11='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U11)&gt;0),1,0))+IF(V11='Resultats Reals'!$C$24,2,IF(OR(V11='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V11)&gt;0),1,0))+IF(W11='Resultats Reals'!$C$27,2,IF(OR(W11='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W11)&gt;0),1,0))+IF(X11='Resultats Reals'!$C$30,2,IF(OR(X11='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X11)&gt;0),1,0))+IF(Y11='Resultats Reals'!$C$33,2,IF(OR(Y11='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y11)&gt;0),1,0))+IF(Z11='Resultats Reals'!$C$36,2,IF(OR(Z11='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z11)&gt;0),1,0))</f>
@@ -9711,7 +9714,7 @@
       </c>
       <c r="BW11">
         <f>IF(AA11='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0,2,0.5),IF(OR(AA11='Resultats Reals'!$C$2,AA11='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA11)&gt;0),1,0))+IF(AB11='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0,2,0.5),IF(OR(AB11='Resultats Reals'!$C$5,AB11='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB11)&gt;0),1,0))+IF(AC11='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0,2,0.5),IF(OR(AC11='Resultats Reals'!$C$8,AC11='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC11)&gt;0),1,0))+IF(AD11='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0,2,0.5),IF(OR(AD11='Resultats Reals'!$C$11,AD11='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD11)&gt;0),1,0))+IF(AE11='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0,2,0.5),IF(OR(AE11='Resultats Reals'!$C$14,AE11='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE11)&gt;0),1,0))+IF(AF11='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0,2,0.5),IF(OR(AF11='Resultats Reals'!$C$17,AF11='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF11)&gt;0),1,0))+IF(AG11='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0,2,0.5),IF(OR(AG11='Resultats Reals'!$C$20,AG11='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG11)&gt;0),1,0))+IF(AH11='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0,2,0.5),IF(OR(AH11='Resultats Reals'!$C$23,AH11='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH11)&gt;0),1,0))+IF(AI11='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0,2,0.5),IF(OR(AI11='Resultats Reals'!$C$26,AI11='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI11)&gt;0),1,0))+IF(AJ11='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0,2,0.5),IF(OR(AJ11='Resultats Reals'!$C$29,AJ11='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ11)&gt;0),1,0))+IF(AK11='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0,2,0.5),IF(OR(AK11='Resultats Reals'!$C$32,AK11='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK11)&gt;0),1,0))+IF(AL11='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0,2,0.5),IF(OR(AL11='Resultats Reals'!$C$35,AL11='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL11)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX11">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA11)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB11)&gt;0,1,0)</f>
@@ -9747,10 +9750,10 @@
       </c>
       <c r="CF11" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -9966,7 +9969,7 @@
       </c>
       <c r="BU12">
         <f>IF(C12='Resultats Reals'!$C$2,2,IF(OR(C12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C12)&gt;0),1,0))+IF(D12='Resultats Reals'!$C$5,2,IF(OR(D12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D12)&gt;0),1,0))+IF(E12='Resultats Reals'!$C$8,2,IF(OR(E12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E12)&gt;0),1,0))+IF(F12='Resultats Reals'!$C$11,2,IF(OR(F12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F12)&gt;0),1,0))+IF(G12='Resultats Reals'!$C$14,2,IF(OR(G12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G12)&gt;0),1,0))+IF(H12='Resultats Reals'!$C$17,2,IF(OR(H12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H12)&gt;0),1,0))+IF(I12='Resultats Reals'!$C$20,2,IF(OR(I12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I12)&gt;0),1,0))+IF(J12='Resultats Reals'!$C$23,2,IF(OR(J12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J12)&gt;0),1,0))+IF(K12='Resultats Reals'!$C$26,2,IF(OR(K12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K12)&gt;0),1,0))+IF(L12='Resultats Reals'!$C$29,2,IF(OR(L12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L12)&gt;0),1,0))+IF(M12='Resultats Reals'!$C$32,2,IF(OR(M12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M12)&gt;0),1,0))+IF(N12='Resultats Reals'!$C$35,2,IF(OR(N12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N12)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV12">
         <f>IF(O12='Resultats Reals'!$C$3,2,IF(OR(O12='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O12)&gt;0),1,0))+IF(P12='Resultats Reals'!$C$6,2,IF(OR(P12='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P12)&gt;0),1,0))+IF(Q12='Resultats Reals'!$C$9,2,IF(OR(Q12='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q12)&gt;0),1,0))+IF(R12='Resultats Reals'!$C$12,2,IF(OR(R12='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R12)&gt;0),1,0))+IF(S12='Resultats Reals'!$C$15,2,IF(OR(S12='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S12)&gt;0),1,0))+IF(T12='Resultats Reals'!$C$18,2,IF(OR(T12='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T12)&gt;0),1,0))+IF(U12='Resultats Reals'!$C$21,2,IF(OR(U12='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U12)&gt;0),1,0))+IF(V12='Resultats Reals'!$C$24,2,IF(OR(V12='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V12)&gt;0),1,0))+IF(W12='Resultats Reals'!$C$27,2,IF(OR(W12='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W12)&gt;0),1,0))+IF(X12='Resultats Reals'!$C$30,2,IF(OR(X12='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X12)&gt;0),1,0))+IF(Y12='Resultats Reals'!$C$33,2,IF(OR(Y12='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y12)&gt;0),1,0))+IF(Z12='Resultats Reals'!$C$36,2,IF(OR(Z12='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z12)&gt;0),1,0))</f>
@@ -9974,7 +9977,7 @@
       </c>
       <c r="BW12">
         <f>IF(AA12='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0,2,0.5),IF(OR(AA12='Resultats Reals'!$C$2,AA12='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA12)&gt;0),1,0))+IF(AB12='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0,2,0.5),IF(OR(AB12='Resultats Reals'!$C$5,AB12='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB12)&gt;0),1,0))+IF(AC12='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0,2,0.5),IF(OR(AC12='Resultats Reals'!$C$8,AC12='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC12)&gt;0),1,0))+IF(AD12='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0,2,0.5),IF(OR(AD12='Resultats Reals'!$C$11,AD12='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD12)&gt;0),1,0))+IF(AE12='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0,2,0.5),IF(OR(AE12='Resultats Reals'!$C$14,AE12='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE12)&gt;0),1,0))+IF(AF12='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0,2,0.5),IF(OR(AF12='Resultats Reals'!$C$17,AF12='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF12)&gt;0),1,0))+IF(AG12='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0,2,0.5),IF(OR(AG12='Resultats Reals'!$C$20,AG12='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG12)&gt;0),1,0))+IF(AH12='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0,2,0.5),IF(OR(AH12='Resultats Reals'!$C$23,AH12='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH12)&gt;0),1,0))+IF(AI12='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0,2,0.5),IF(OR(AI12='Resultats Reals'!$C$26,AI12='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI12)&gt;0),1,0))+IF(AJ12='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0,2,0.5),IF(OR(AJ12='Resultats Reals'!$C$29,AJ12='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ12)&gt;0),1,0))+IF(AK12='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0,2,0.5),IF(OR(AK12='Resultats Reals'!$C$32,AK12='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK12)&gt;0),1,0))+IF(AL12='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0,2,0.5),IF(OR(AL12='Resultats Reals'!$C$35,AL12='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL12)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX12">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA12)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB12)&gt;0,1,0)</f>
@@ -10010,10 +10013,10 @@
       </c>
       <c r="CF12" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="13" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -10229,7 +10232,7 @@
       </c>
       <c r="BU13">
         <f>IF(C13='Resultats Reals'!$C$2,2,IF(OR(C13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C13)&gt;0),1,0))+IF(D13='Resultats Reals'!$C$5,2,IF(OR(D13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D13)&gt;0),1,0))+IF(E13='Resultats Reals'!$C$8,2,IF(OR(E13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E13)&gt;0),1,0))+IF(F13='Resultats Reals'!$C$11,2,IF(OR(F13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F13)&gt;0),1,0))+IF(G13='Resultats Reals'!$C$14,2,IF(OR(G13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G13)&gt;0),1,0))+IF(H13='Resultats Reals'!$C$17,2,IF(OR(H13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H13)&gt;0),1,0))+IF(I13='Resultats Reals'!$C$20,2,IF(OR(I13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I13)&gt;0),1,0))+IF(J13='Resultats Reals'!$C$23,2,IF(OR(J13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J13)&gt;0),1,0))+IF(K13='Resultats Reals'!$C$26,2,IF(OR(K13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K13)&gt;0),1,0))+IF(L13='Resultats Reals'!$C$29,2,IF(OR(L13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L13)&gt;0),1,0))+IF(M13='Resultats Reals'!$C$32,2,IF(OR(M13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M13)&gt;0),1,0))+IF(N13='Resultats Reals'!$C$35,2,IF(OR(N13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N13)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BV13">
         <f>IF(O13='Resultats Reals'!$C$3,2,IF(OR(O13='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O13)&gt;0),1,0))+IF(P13='Resultats Reals'!$C$6,2,IF(OR(P13='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P13)&gt;0),1,0))+IF(Q13='Resultats Reals'!$C$9,2,IF(OR(Q13='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q13)&gt;0),1,0))+IF(R13='Resultats Reals'!$C$12,2,IF(OR(R13='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R13)&gt;0),1,0))+IF(S13='Resultats Reals'!$C$15,2,IF(OR(S13='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S13)&gt;0),1,0))+IF(T13='Resultats Reals'!$C$18,2,IF(OR(T13='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T13)&gt;0),1,0))+IF(U13='Resultats Reals'!$C$21,2,IF(OR(U13='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U13)&gt;0),1,0))+IF(V13='Resultats Reals'!$C$24,2,IF(OR(V13='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V13)&gt;0),1,0))+IF(W13='Resultats Reals'!$C$27,2,IF(OR(W13='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W13)&gt;0),1,0))+IF(X13='Resultats Reals'!$C$30,2,IF(OR(X13='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X13)&gt;0),1,0))+IF(Y13='Resultats Reals'!$C$33,2,IF(OR(Y13='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y13)&gt;0),1,0))+IF(Z13='Resultats Reals'!$C$36,2,IF(OR(Z13='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z13)&gt;0),1,0))</f>
@@ -10237,7 +10240,7 @@
       </c>
       <c r="BW13">
         <f>IF(AA13='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0,2,0.5),IF(OR(AA13='Resultats Reals'!$C$2,AA13='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA13)&gt;0),1,0))+IF(AB13='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0,2,0.5),IF(OR(AB13='Resultats Reals'!$C$5,AB13='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB13)&gt;0),1,0))+IF(AC13='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0,2,0.5),IF(OR(AC13='Resultats Reals'!$C$8,AC13='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC13)&gt;0),1,0))+IF(AD13='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0,2,0.5),IF(OR(AD13='Resultats Reals'!$C$11,AD13='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD13)&gt;0),1,0))+IF(AE13='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0,2,0.5),IF(OR(AE13='Resultats Reals'!$C$14,AE13='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE13)&gt;0),1,0))+IF(AF13='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0,2,0.5),IF(OR(AF13='Resultats Reals'!$C$17,AF13='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF13)&gt;0),1,0))+IF(AG13='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0,2,0.5),IF(OR(AG13='Resultats Reals'!$C$20,AG13='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG13)&gt;0),1,0))+IF(AH13='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0,2,0.5),IF(OR(AH13='Resultats Reals'!$C$23,AH13='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH13)&gt;0),1,0))+IF(AI13='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0,2,0.5),IF(OR(AI13='Resultats Reals'!$C$26,AI13='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI13)&gt;0),1,0))+IF(AJ13='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0,2,0.5),IF(OR(AJ13='Resultats Reals'!$C$29,AJ13='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ13)&gt;0),1,0))+IF(AK13='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0,2,0.5),IF(OR(AK13='Resultats Reals'!$C$32,AK13='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK13)&gt;0),1,0))+IF(AL13='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0,2,0.5),IF(OR(AL13='Resultats Reals'!$C$35,AL13='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL13)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA13)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB13)&gt;0,1,0)</f>
@@ -10273,10 +10276,10 @@
       </c>
       <c r="CF13" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="14" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>156</v>
       </c>
@@ -10492,7 +10495,7 @@
       </c>
       <c r="BU14">
         <f>IF(C14='Resultats Reals'!$C$2,2,IF(OR(C14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C14)&gt;0),1,0))+IF(D14='Resultats Reals'!$C$5,2,IF(OR(D14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D14)&gt;0),1,0))+IF(E14='Resultats Reals'!$C$8,2,IF(OR(E14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E14)&gt;0),1,0))+IF(F14='Resultats Reals'!$C$11,2,IF(OR(F14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F14)&gt;0),1,0))+IF(G14='Resultats Reals'!$C$14,2,IF(OR(G14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G14)&gt;0),1,0))+IF(H14='Resultats Reals'!$C$17,2,IF(OR(H14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H14)&gt;0),1,0))+IF(I14='Resultats Reals'!$C$20,2,IF(OR(I14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I14)&gt;0),1,0))+IF(J14='Resultats Reals'!$C$23,2,IF(OR(J14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J14)&gt;0),1,0))+IF(K14='Resultats Reals'!$C$26,2,IF(OR(K14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K14)&gt;0),1,0))+IF(L14='Resultats Reals'!$C$29,2,IF(OR(L14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L14)&gt;0),1,0))+IF(M14='Resultats Reals'!$C$32,2,IF(OR(M14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M14)&gt;0),1,0))+IF(N14='Resultats Reals'!$C$35,2,IF(OR(N14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N14)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV14">
         <f>IF(O14='Resultats Reals'!$C$3,2,IF(OR(O14='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O14)&gt;0),1,0))+IF(P14='Resultats Reals'!$C$6,2,IF(OR(P14='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P14)&gt;0),1,0))+IF(Q14='Resultats Reals'!$C$9,2,IF(OR(Q14='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q14)&gt;0),1,0))+IF(R14='Resultats Reals'!$C$12,2,IF(OR(R14='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R14)&gt;0),1,0))+IF(S14='Resultats Reals'!$C$15,2,IF(OR(S14='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S14)&gt;0),1,0))+IF(T14='Resultats Reals'!$C$18,2,IF(OR(T14='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T14)&gt;0),1,0))+IF(U14='Resultats Reals'!$C$21,2,IF(OR(U14='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U14)&gt;0),1,0))+IF(V14='Resultats Reals'!$C$24,2,IF(OR(V14='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V14)&gt;0),1,0))+IF(W14='Resultats Reals'!$C$27,2,IF(OR(W14='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W14)&gt;0),1,0))+IF(X14='Resultats Reals'!$C$30,2,IF(OR(X14='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X14)&gt;0),1,0))+IF(Y14='Resultats Reals'!$C$33,2,IF(OR(Y14='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y14)&gt;0),1,0))+IF(Z14='Resultats Reals'!$C$36,2,IF(OR(Z14='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z14)&gt;0),1,0))</f>
@@ -10500,7 +10503,7 @@
       </c>
       <c r="BW14">
         <f>IF(AA14='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0,2,0.5),IF(OR(AA14='Resultats Reals'!$C$2,AA14='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA14)&gt;0),1,0))+IF(AB14='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0,2,0.5),IF(OR(AB14='Resultats Reals'!$C$5,AB14='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB14)&gt;0),1,0))+IF(AC14='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0,2,0.5),IF(OR(AC14='Resultats Reals'!$C$8,AC14='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC14)&gt;0),1,0))+IF(AD14='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0,2,0.5),IF(OR(AD14='Resultats Reals'!$C$11,AD14='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD14)&gt;0),1,0))+IF(AE14='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0,2,0.5),IF(OR(AE14='Resultats Reals'!$C$14,AE14='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE14)&gt;0),1,0))+IF(AF14='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0,2,0.5),IF(OR(AF14='Resultats Reals'!$C$17,AF14='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF14)&gt;0),1,0))+IF(AG14='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0,2,0.5),IF(OR(AG14='Resultats Reals'!$C$20,AG14='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG14)&gt;0),1,0))+IF(AH14='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0,2,0.5),IF(OR(AH14='Resultats Reals'!$C$23,AH14='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH14)&gt;0),1,0))+IF(AI14='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0,2,0.5),IF(OR(AI14='Resultats Reals'!$C$26,AI14='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI14)&gt;0),1,0))+IF(AJ14='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0,2,0.5),IF(OR(AJ14='Resultats Reals'!$C$29,AJ14='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ14)&gt;0),1,0))+IF(AK14='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0,2,0.5),IF(OR(AK14='Resultats Reals'!$C$32,AK14='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK14)&gt;0),1,0))+IF(AL14='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0,2,0.5),IF(OR(AL14='Resultats Reals'!$C$35,AL14='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL14)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BX14">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA14)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB14)&gt;0,1,0)</f>
@@ -10536,10 +10539,10 @@
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>157</v>
       </c>
@@ -10755,15 +10758,15 @@
       </c>
       <c r="BU15">
         <f>IF(C15='Resultats Reals'!$C$2,2,IF(OR(C15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C15)&gt;0),1,0))+IF(D15='Resultats Reals'!$C$5,2,IF(OR(D15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D15)&gt;0),1,0))+IF(E15='Resultats Reals'!$C$8,2,IF(OR(E15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E15)&gt;0),1,0))+IF(F15='Resultats Reals'!$C$11,2,IF(OR(F15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F15)&gt;0),1,0))+IF(G15='Resultats Reals'!$C$14,2,IF(OR(G15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G15)&gt;0),1,0))+IF(H15='Resultats Reals'!$C$17,2,IF(OR(H15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H15)&gt;0),1,0))+IF(I15='Resultats Reals'!$C$20,2,IF(OR(I15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I15)&gt;0),1,0))+IF(J15='Resultats Reals'!$C$23,2,IF(OR(J15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J15)&gt;0),1,0))+IF(K15='Resultats Reals'!$C$26,2,IF(OR(K15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K15)&gt;0),1,0))+IF(L15='Resultats Reals'!$C$29,2,IF(OR(L15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L15)&gt;0),1,0))+IF(M15='Resultats Reals'!$C$32,2,IF(OR(M15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M15)&gt;0),1,0))+IF(N15='Resultats Reals'!$C$35,2,IF(OR(N15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N15)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV15">
         <f>IF(O15='Resultats Reals'!$C$3,2,IF(OR(O15='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O15)&gt;0),1,0))+IF(P15='Resultats Reals'!$C$6,2,IF(OR(P15='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P15)&gt;0),1,0))+IF(Q15='Resultats Reals'!$C$9,2,IF(OR(Q15='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q15)&gt;0),1,0))+IF(R15='Resultats Reals'!$C$12,2,IF(OR(R15='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R15)&gt;0),1,0))+IF(S15='Resultats Reals'!$C$15,2,IF(OR(S15='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S15)&gt;0),1,0))+IF(T15='Resultats Reals'!$C$18,2,IF(OR(T15='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T15)&gt;0),1,0))+IF(U15='Resultats Reals'!$C$21,2,IF(OR(U15='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U15)&gt;0),1,0))+IF(V15='Resultats Reals'!$C$24,2,IF(OR(V15='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V15)&gt;0),1,0))+IF(W15='Resultats Reals'!$C$27,2,IF(OR(W15='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W15)&gt;0),1,0))+IF(X15='Resultats Reals'!$C$30,2,IF(OR(X15='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X15)&gt;0),1,0))+IF(Y15='Resultats Reals'!$C$33,2,IF(OR(Y15='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y15)&gt;0),1,0))+IF(Z15='Resultats Reals'!$C$36,2,IF(OR(Z15='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z15)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BW15">
         <f>IF(AA15='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0,2,0.5),IF(OR(AA15='Resultats Reals'!$C$2,AA15='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA15)&gt;0),1,0))+IF(AB15='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0,2,0.5),IF(OR(AB15='Resultats Reals'!$C$5,AB15='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB15)&gt;0),1,0))+IF(AC15='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0,2,0.5),IF(OR(AC15='Resultats Reals'!$C$8,AC15='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC15)&gt;0),1,0))+IF(AD15='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0,2,0.5),IF(OR(AD15='Resultats Reals'!$C$11,AD15='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD15)&gt;0),1,0))+IF(AE15='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0,2,0.5),IF(OR(AE15='Resultats Reals'!$C$14,AE15='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE15)&gt;0),1,0))+IF(AF15='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0,2,0.5),IF(OR(AF15='Resultats Reals'!$C$17,AF15='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF15)&gt;0),1,0))+IF(AG15='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0,2,0.5),IF(OR(AG15='Resultats Reals'!$C$20,AG15='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG15)&gt;0),1,0))+IF(AH15='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0,2,0.5),IF(OR(AH15='Resultats Reals'!$C$23,AH15='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH15)&gt;0),1,0))+IF(AI15='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0,2,0.5),IF(OR(AI15='Resultats Reals'!$C$26,AI15='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI15)&gt;0),1,0))+IF(AJ15='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0,2,0.5),IF(OR(AJ15='Resultats Reals'!$C$29,AJ15='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ15)&gt;0),1,0))+IF(AK15='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0,2,0.5),IF(OR(AK15='Resultats Reals'!$C$32,AK15='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK15)&gt;0),1,0))+IF(AL15='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0,2,0.5),IF(OR(AL15='Resultats Reals'!$C$35,AL15='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL15)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="BX15">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA15)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB15)&gt;0,1,0)</f>
@@ -10799,10 +10802,10 @@
       </c>
       <c r="CF15" s="7">
         <f t="shared" si="0"/>
-        <v>43.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="16" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -11018,7 +11021,7 @@
       </c>
       <c r="BU16">
         <f>IF(C16='Resultats Reals'!$C$2,2,IF(OR(C16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C16)&gt;0),1,0))+IF(D16='Resultats Reals'!$C$5,2,IF(OR(D16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D16)&gt;0),1,0))+IF(E16='Resultats Reals'!$C$8,2,IF(OR(E16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E16)&gt;0),1,0))+IF(F16='Resultats Reals'!$C$11,2,IF(OR(F16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F16)&gt;0),1,0))+IF(G16='Resultats Reals'!$C$14,2,IF(OR(G16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G16)&gt;0),1,0))+IF(H16='Resultats Reals'!$C$17,2,IF(OR(H16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H16)&gt;0),1,0))+IF(I16='Resultats Reals'!$C$20,2,IF(OR(I16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I16)&gt;0),1,0))+IF(J16='Resultats Reals'!$C$23,2,IF(OR(J16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J16)&gt;0),1,0))+IF(K16='Resultats Reals'!$C$26,2,IF(OR(K16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K16)&gt;0),1,0))+IF(L16='Resultats Reals'!$C$29,2,IF(OR(L16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L16)&gt;0),1,0))+IF(M16='Resultats Reals'!$C$32,2,IF(OR(M16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M16)&gt;0),1,0))+IF(N16='Resultats Reals'!$C$35,2,IF(OR(N16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N16)&gt;0),1,0))</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BV16">
         <f>IF(O16='Resultats Reals'!$C$3,2,IF(OR(O16='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O16)&gt;0),1,0))+IF(P16='Resultats Reals'!$C$6,2,IF(OR(P16='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P16)&gt;0),1,0))+IF(Q16='Resultats Reals'!$C$9,2,IF(OR(Q16='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q16)&gt;0),1,0))+IF(R16='Resultats Reals'!$C$12,2,IF(OR(R16='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R16)&gt;0),1,0))+IF(S16='Resultats Reals'!$C$15,2,IF(OR(S16='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S16)&gt;0),1,0))+IF(T16='Resultats Reals'!$C$18,2,IF(OR(T16='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T16)&gt;0),1,0))+IF(U16='Resultats Reals'!$C$21,2,IF(OR(U16='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U16)&gt;0),1,0))+IF(V16='Resultats Reals'!$C$24,2,IF(OR(V16='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V16)&gt;0),1,0))+IF(W16='Resultats Reals'!$C$27,2,IF(OR(W16='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W16)&gt;0),1,0))+IF(X16='Resultats Reals'!$C$30,2,IF(OR(X16='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X16)&gt;0),1,0))+IF(Y16='Resultats Reals'!$C$33,2,IF(OR(Y16='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y16)&gt;0),1,0))+IF(Z16='Resultats Reals'!$C$36,2,IF(OR(Z16='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z16)&gt;0),1,0))</f>
@@ -11026,7 +11029,7 @@
       </c>
       <c r="BW16">
         <f>IF(AA16='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0,2,0.5),IF(OR(AA16='Resultats Reals'!$C$2,AA16='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA16)&gt;0),1,0))+IF(AB16='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0,2,0.5),IF(OR(AB16='Resultats Reals'!$C$5,AB16='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB16)&gt;0),1,0))+IF(AC16='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0,2,0.5),IF(OR(AC16='Resultats Reals'!$C$8,AC16='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC16)&gt;0),1,0))+IF(AD16='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0,2,0.5),IF(OR(AD16='Resultats Reals'!$C$11,AD16='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD16)&gt;0),1,0))+IF(AE16='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0,2,0.5),IF(OR(AE16='Resultats Reals'!$C$14,AE16='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE16)&gt;0),1,0))+IF(AF16='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0,2,0.5),IF(OR(AF16='Resultats Reals'!$C$17,AF16='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF16)&gt;0),1,0))+IF(AG16='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0,2,0.5),IF(OR(AG16='Resultats Reals'!$C$20,AG16='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG16)&gt;0),1,0))+IF(AH16='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0,2,0.5),IF(OR(AH16='Resultats Reals'!$C$23,AH16='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH16)&gt;0),1,0))+IF(AI16='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0,2,0.5),IF(OR(AI16='Resultats Reals'!$C$26,AI16='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI16)&gt;0),1,0))+IF(AJ16='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0,2,0.5),IF(OR(AJ16='Resultats Reals'!$C$29,AJ16='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ16)&gt;0),1,0))+IF(AK16='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0,2,0.5),IF(OR(AK16='Resultats Reals'!$C$32,AK16='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK16)&gt;0),1,0))+IF(AL16='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0,2,0.5),IF(OR(AL16='Resultats Reals'!$C$35,AL16='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL16)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="BX16">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA16)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB16)&gt;0,1,0)</f>
@@ -11062,10 +11065,10 @@
       </c>
       <c r="CF16" s="7">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>41.5</v>
       </c>
     </row>
-    <row r="17" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>160</v>
       </c>
@@ -11281,7 +11284,7 @@
       </c>
       <c r="BU17">
         <f>IF(C17='Resultats Reals'!$C$2,2,IF(OR(C17='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C17)&gt;0),1,0))+IF(D17='Resultats Reals'!$C$5,2,IF(OR(D17='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D17)&gt;0),1,0))+IF(E17='Resultats Reals'!$C$8,2,IF(OR(E17='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E17)&gt;0),1,0))+IF(F17='Resultats Reals'!$C$11,2,IF(OR(F17='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F17)&gt;0),1,0))+IF(G17='Resultats Reals'!$C$14,2,IF(OR(G17='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G17)&gt;0),1,0))+IF(H17='Resultats Reals'!$C$17,2,IF(OR(H17='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H17)&gt;0),1,0))+IF(I17='Resultats Reals'!$C$20,2,IF(OR(I17='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I17)&gt;0),1,0))+IF(J17='Resultats Reals'!$C$23,2,IF(OR(J17='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J17)&gt;0),1,0))+IF(K17='Resultats Reals'!$C$26,2,IF(OR(K17='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K17)&gt;0),1,0))+IF(L17='Resultats Reals'!$C$29,2,IF(OR(L17='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L17)&gt;0),1,0))+IF(M17='Resultats Reals'!$C$32,2,IF(OR(M17='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M17)&gt;0),1,0))+IF(N17='Resultats Reals'!$C$35,2,IF(OR(N17='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N17)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BV17">
         <f>IF(O17='Resultats Reals'!$C$3,2,IF(OR(O17='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O17)&gt;0),1,0))+IF(P17='Resultats Reals'!$C$6,2,IF(OR(P17='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P17)&gt;0),1,0))+IF(Q17='Resultats Reals'!$C$9,2,IF(OR(Q17='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q17)&gt;0),1,0))+IF(R17='Resultats Reals'!$C$12,2,IF(OR(R17='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R17)&gt;0),1,0))+IF(S17='Resultats Reals'!$C$15,2,IF(OR(S17='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S17)&gt;0),1,0))+IF(T17='Resultats Reals'!$C$18,2,IF(OR(T17='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T17)&gt;0),1,0))+IF(U17='Resultats Reals'!$C$21,2,IF(OR(U17='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U17)&gt;0),1,0))+IF(V17='Resultats Reals'!$C$24,2,IF(OR(V17='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V17)&gt;0),1,0))+IF(W17='Resultats Reals'!$C$27,2,IF(OR(W17='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W17)&gt;0),1,0))+IF(X17='Resultats Reals'!$C$30,2,IF(OR(X17='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X17)&gt;0),1,0))+IF(Y17='Resultats Reals'!$C$33,2,IF(OR(Y17='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y17)&gt;0),1,0))+IF(Z17='Resultats Reals'!$C$36,2,IF(OR(Z17='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z17)&gt;0),1,0))</f>
@@ -11325,10 +11328,10 @@
       </c>
       <c r="CF17" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>36.5</v>
       </c>
     </row>
-    <row r="18" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -11547,7 +11550,7 @@
       </c>
       <c r="BU18">
         <f>IF(C18='Resultats Reals'!$C$2,2,IF(OR(C18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C18)&gt;0),1,0))+IF(D18='Resultats Reals'!$C$5,2,IF(OR(D18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D18)&gt;0),1,0))+IF(E18='Resultats Reals'!$C$8,2,IF(OR(E18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E18)&gt;0),1,0))+IF(F18='Resultats Reals'!$C$11,2,IF(OR(F18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F18)&gt;0),1,0))+IF(G18='Resultats Reals'!$C$14,2,IF(OR(G18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G18)&gt;0),1,0))+IF(H18='Resultats Reals'!$C$17,2,IF(OR(H18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H18)&gt;0),1,0))+IF(I18='Resultats Reals'!$C$20,2,IF(OR(I18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I18)&gt;0),1,0))+IF(J18='Resultats Reals'!$C$23,2,IF(OR(J18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J18)&gt;0),1,0))+IF(K18='Resultats Reals'!$C$26,2,IF(OR(K18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K18)&gt;0),1,0))+IF(L18='Resultats Reals'!$C$29,2,IF(OR(L18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L18)&gt;0),1,0))+IF(M18='Resultats Reals'!$C$32,2,IF(OR(M18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M18)&gt;0),1,0))+IF(N18='Resultats Reals'!$C$35,2,IF(OR(N18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N18)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV18">
         <f>IF(O18='Resultats Reals'!$C$3,2,IF(OR(O18='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O18)&gt;0),1,0))+IF(P18='Resultats Reals'!$C$6,2,IF(OR(P18='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P18)&gt;0),1,0))+IF(Q18='Resultats Reals'!$C$9,2,IF(OR(Q18='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q18)&gt;0),1,0))+IF(R18='Resultats Reals'!$C$12,2,IF(OR(R18='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R18)&gt;0),1,0))+IF(S18='Resultats Reals'!$C$15,2,IF(OR(S18='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S18)&gt;0),1,0))+IF(T18='Resultats Reals'!$C$18,2,IF(OR(T18='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T18)&gt;0),1,0))+IF(U18='Resultats Reals'!$C$21,2,IF(OR(U18='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U18)&gt;0),1,0))+IF(V18='Resultats Reals'!$C$24,2,IF(OR(V18='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V18)&gt;0),1,0))+IF(W18='Resultats Reals'!$C$27,2,IF(OR(W18='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W18)&gt;0),1,0))+IF(X18='Resultats Reals'!$C$30,2,IF(OR(X18='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X18)&gt;0),1,0))+IF(Y18='Resultats Reals'!$C$33,2,IF(OR(Y18='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y18)&gt;0),1,0))+IF(Z18='Resultats Reals'!$C$36,2,IF(OR(Z18='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z18)&gt;0),1,0))</f>
@@ -11555,7 +11558,7 @@
       </c>
       <c r="BW18">
         <f>IF(AA18='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0,2,0.5),IF(OR(AA18='Resultats Reals'!$C$2,AA18='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA18)&gt;0),1,0))+IF(AB18='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0,2,0.5),IF(OR(AB18='Resultats Reals'!$C$5,AB18='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB18)&gt;0),1,0))+IF(AC18='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0,2,0.5),IF(OR(AC18='Resultats Reals'!$C$8,AC18='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC18)&gt;0),1,0))+IF(AD18='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0,2,0.5),IF(OR(AD18='Resultats Reals'!$C$11,AD18='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD18)&gt;0),1,0))+IF(AE18='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0,2,0.5),IF(OR(AE18='Resultats Reals'!$C$14,AE18='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE18)&gt;0),1,0))+IF(AF18='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0,2,0.5),IF(OR(AF18='Resultats Reals'!$C$17,AF18='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF18)&gt;0),1,0))+IF(AG18='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0,2,0.5),IF(OR(AG18='Resultats Reals'!$C$20,AG18='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG18)&gt;0),1,0))+IF(AH18='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0,2,0.5),IF(OR(AH18='Resultats Reals'!$C$23,AH18='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH18)&gt;0),1,0))+IF(AI18='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0,2,0.5),IF(OR(AI18='Resultats Reals'!$C$26,AI18='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI18)&gt;0),1,0))+IF(AJ18='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0,2,0.5),IF(OR(AJ18='Resultats Reals'!$C$29,AJ18='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ18)&gt;0),1,0))+IF(AK18='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0,2,0.5),IF(OR(AK18='Resultats Reals'!$C$32,AK18='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK18)&gt;0),1,0))+IF(AL18='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0,2,0.5),IF(OR(AL18='Resultats Reals'!$C$35,AL18='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL18)&gt;0),1,0))</f>
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="BX18">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA18)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB18)&gt;0,1,0)</f>
@@ -11591,10 +11594,10 @@
       </c>
       <c r="CF18" s="7">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="19" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>166</v>
       </c>
@@ -11810,15 +11813,15 @@
       </c>
       <c r="BU19">
         <f>IF(C19='Resultats Reals'!$C$2,2,IF(OR(C19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C19)&gt;0),1,0))+IF(D19='Resultats Reals'!$C$5,2,IF(OR(D19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D19)&gt;0),1,0))+IF(E19='Resultats Reals'!$C$8,2,IF(OR(E19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E19)&gt;0),1,0))+IF(F19='Resultats Reals'!$C$11,2,IF(OR(F19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F19)&gt;0),1,0))+IF(G19='Resultats Reals'!$C$14,2,IF(OR(G19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G19)&gt;0),1,0))+IF(H19='Resultats Reals'!$C$17,2,IF(OR(H19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H19)&gt;0),1,0))+IF(I19='Resultats Reals'!$C$20,2,IF(OR(I19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I19)&gt;0),1,0))+IF(J19='Resultats Reals'!$C$23,2,IF(OR(J19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J19)&gt;0),1,0))+IF(K19='Resultats Reals'!$C$26,2,IF(OR(K19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K19)&gt;0),1,0))+IF(L19='Resultats Reals'!$C$29,2,IF(OR(L19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L19)&gt;0),1,0))+IF(M19='Resultats Reals'!$C$32,2,IF(OR(M19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M19)&gt;0),1,0))+IF(N19='Resultats Reals'!$C$35,2,IF(OR(N19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N19)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV19">
         <f>IF(O19='Resultats Reals'!$C$3,2,IF(OR(O19='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O19)&gt;0),1,0))+IF(P19='Resultats Reals'!$C$6,2,IF(OR(P19='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P19)&gt;0),1,0))+IF(Q19='Resultats Reals'!$C$9,2,IF(OR(Q19='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q19)&gt;0),1,0))+IF(R19='Resultats Reals'!$C$12,2,IF(OR(R19='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R19)&gt;0),1,0))+IF(S19='Resultats Reals'!$C$15,2,IF(OR(S19='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S19)&gt;0),1,0))+IF(T19='Resultats Reals'!$C$18,2,IF(OR(T19='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T19)&gt;0),1,0))+IF(U19='Resultats Reals'!$C$21,2,IF(OR(U19='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U19)&gt;0),1,0))+IF(V19='Resultats Reals'!$C$24,2,IF(OR(V19='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V19)&gt;0),1,0))+IF(W19='Resultats Reals'!$C$27,2,IF(OR(W19='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W19)&gt;0),1,0))+IF(X19='Resultats Reals'!$C$30,2,IF(OR(X19='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X19)&gt;0),1,0))+IF(Y19='Resultats Reals'!$C$33,2,IF(OR(Y19='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y19)&gt;0),1,0))+IF(Z19='Resultats Reals'!$C$36,2,IF(OR(Z19='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z19)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BW19">
         <f>IF(AA19='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0,2,0.5),IF(OR(AA19='Resultats Reals'!$C$2,AA19='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA19)&gt;0),1,0))+IF(AB19='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0,2,0.5),IF(OR(AB19='Resultats Reals'!$C$5,AB19='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB19)&gt;0),1,0))+IF(AC19='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0,2,0.5),IF(OR(AC19='Resultats Reals'!$C$8,AC19='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC19)&gt;0),1,0))+IF(AD19='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0,2,0.5),IF(OR(AD19='Resultats Reals'!$C$11,AD19='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD19)&gt;0),1,0))+IF(AE19='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0,2,0.5),IF(OR(AE19='Resultats Reals'!$C$14,AE19='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE19)&gt;0),1,0))+IF(AF19='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0,2,0.5),IF(OR(AF19='Resultats Reals'!$C$17,AF19='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF19)&gt;0),1,0))+IF(AG19='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0,2,0.5),IF(OR(AG19='Resultats Reals'!$C$20,AG19='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG19)&gt;0),1,0))+IF(AH19='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0,2,0.5),IF(OR(AH19='Resultats Reals'!$C$23,AH19='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH19)&gt;0),1,0))+IF(AI19='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0,2,0.5),IF(OR(AI19='Resultats Reals'!$C$26,AI19='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI19)&gt;0),1,0))+IF(AJ19='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0,2,0.5),IF(OR(AJ19='Resultats Reals'!$C$29,AJ19='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ19)&gt;0),1,0))+IF(AK19='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0,2,0.5),IF(OR(AK19='Resultats Reals'!$C$32,AK19='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK19)&gt;0),1,0))+IF(AL19='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0,2,0.5),IF(OR(AL19='Resultats Reals'!$C$35,AL19='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL19)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX19">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA19)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB19)&gt;0,1,0)</f>
@@ -11846,7 +11849,7 @@
       </c>
       <c r="CD19">
         <f>IFERROR(VLOOKUP(BT19,'Resultats Reals'!$N$2:$O$100,2,FALSE),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CE19">
         <f>IF(BR19='Resultats Reals'!$L$2,5,0)</f>
@@ -11854,10 +11857,10 @@
       </c>
       <c r="CF19" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>168</v>
       </c>
@@ -12073,7 +12076,7 @@
       </c>
       <c r="BU20">
         <f>IF(C20='Resultats Reals'!$C$2,2,IF(OR(C20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C20)&gt;0),1,0))+IF(D20='Resultats Reals'!$C$5,2,IF(OR(D20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D20)&gt;0),1,0))+IF(E20='Resultats Reals'!$C$8,2,IF(OR(E20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E20)&gt;0),1,0))+IF(F20='Resultats Reals'!$C$11,2,IF(OR(F20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F20)&gt;0),1,0))+IF(G20='Resultats Reals'!$C$14,2,IF(OR(G20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G20)&gt;0),1,0))+IF(H20='Resultats Reals'!$C$17,2,IF(OR(H20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H20)&gt;0),1,0))+IF(I20='Resultats Reals'!$C$20,2,IF(OR(I20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I20)&gt;0),1,0))+IF(J20='Resultats Reals'!$C$23,2,IF(OR(J20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J20)&gt;0),1,0))+IF(K20='Resultats Reals'!$C$26,2,IF(OR(K20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K20)&gt;0),1,0))+IF(L20='Resultats Reals'!$C$29,2,IF(OR(L20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L20)&gt;0),1,0))+IF(M20='Resultats Reals'!$C$32,2,IF(OR(M20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M20)&gt;0),1,0))+IF(N20='Resultats Reals'!$C$35,2,IF(OR(N20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N20)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV20">
         <f>IF(O20='Resultats Reals'!$C$3,2,IF(OR(O20='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O20)&gt;0),1,0))+IF(P20='Resultats Reals'!$C$6,2,IF(OR(P20='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P20)&gt;0),1,0))+IF(Q20='Resultats Reals'!$C$9,2,IF(OR(Q20='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q20)&gt;0),1,0))+IF(R20='Resultats Reals'!$C$12,2,IF(OR(R20='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R20)&gt;0),1,0))+IF(S20='Resultats Reals'!$C$15,2,IF(OR(S20='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S20)&gt;0),1,0))+IF(T20='Resultats Reals'!$C$18,2,IF(OR(T20='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T20)&gt;0),1,0))+IF(U20='Resultats Reals'!$C$21,2,IF(OR(U20='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U20)&gt;0),1,0))+IF(V20='Resultats Reals'!$C$24,2,IF(OR(V20='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V20)&gt;0),1,0))+IF(W20='Resultats Reals'!$C$27,2,IF(OR(W20='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W20)&gt;0),1,0))+IF(X20='Resultats Reals'!$C$30,2,IF(OR(X20='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X20)&gt;0),1,0))+IF(Y20='Resultats Reals'!$C$33,2,IF(OR(Y20='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y20)&gt;0),1,0))+IF(Z20='Resultats Reals'!$C$36,2,IF(OR(Z20='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z20)&gt;0),1,0))</f>
@@ -12081,7 +12084,7 @@
       </c>
       <c r="BW20">
         <f>IF(AA20='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0,2,0.5),IF(OR(AA20='Resultats Reals'!$C$2,AA20='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA20)&gt;0),1,0))+IF(AB20='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0,2,0.5),IF(OR(AB20='Resultats Reals'!$C$5,AB20='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB20)&gt;0),1,0))+IF(AC20='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0,2,0.5),IF(OR(AC20='Resultats Reals'!$C$8,AC20='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC20)&gt;0),1,0))+IF(AD20='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0,2,0.5),IF(OR(AD20='Resultats Reals'!$C$11,AD20='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD20)&gt;0),1,0))+IF(AE20='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0,2,0.5),IF(OR(AE20='Resultats Reals'!$C$14,AE20='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE20)&gt;0),1,0))+IF(AF20='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0,2,0.5),IF(OR(AF20='Resultats Reals'!$C$17,AF20='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF20)&gt;0),1,0))+IF(AG20='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0,2,0.5),IF(OR(AG20='Resultats Reals'!$C$20,AG20='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG20)&gt;0),1,0))+IF(AH20='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0,2,0.5),IF(OR(AH20='Resultats Reals'!$C$23,AH20='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH20)&gt;0),1,0))+IF(AI20='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0,2,0.5),IF(OR(AI20='Resultats Reals'!$C$26,AI20='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI20)&gt;0),1,0))+IF(AJ20='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0,2,0.5),IF(OR(AJ20='Resultats Reals'!$C$29,AJ20='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ20)&gt;0),1,0))+IF(AK20='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0,2,0.5),IF(OR(AK20='Resultats Reals'!$C$32,AK20='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK20)&gt;0),1,0))+IF(AL20='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0,2,0.5),IF(OR(AL20='Resultats Reals'!$C$35,AL20='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL20)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX20">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA20)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB20)&gt;0,1,0)</f>
@@ -12117,10 +12120,10 @@
       </c>
       <c r="CF20" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -12336,7 +12339,7 @@
       </c>
       <c r="BU21">
         <f>IF(C21='Resultats Reals'!$C$2,2,IF(OR(C21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C21)&gt;0),1,0))+IF(D21='Resultats Reals'!$C$5,2,IF(OR(D21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D21)&gt;0),1,0))+IF(E21='Resultats Reals'!$C$8,2,IF(OR(E21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E21)&gt;0),1,0))+IF(F21='Resultats Reals'!$C$11,2,IF(OR(F21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F21)&gt;0),1,0))+IF(G21='Resultats Reals'!$C$14,2,IF(OR(G21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G21)&gt;0),1,0))+IF(H21='Resultats Reals'!$C$17,2,IF(OR(H21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H21)&gt;0),1,0))+IF(I21='Resultats Reals'!$C$20,2,IF(OR(I21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I21)&gt;0),1,0))+IF(J21='Resultats Reals'!$C$23,2,IF(OR(J21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J21)&gt;0),1,0))+IF(K21='Resultats Reals'!$C$26,2,IF(OR(K21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K21)&gt;0),1,0))+IF(L21='Resultats Reals'!$C$29,2,IF(OR(L21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L21)&gt;0),1,0))+IF(M21='Resultats Reals'!$C$32,2,IF(OR(M21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M21)&gt;0),1,0))+IF(N21='Resultats Reals'!$C$35,2,IF(OR(N21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N21)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV21">
         <f>IF(O21='Resultats Reals'!$C$3,2,IF(OR(O21='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O21)&gt;0),1,0))+IF(P21='Resultats Reals'!$C$6,2,IF(OR(P21='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P21)&gt;0),1,0))+IF(Q21='Resultats Reals'!$C$9,2,IF(OR(Q21='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q21)&gt;0),1,0))+IF(R21='Resultats Reals'!$C$12,2,IF(OR(R21='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R21)&gt;0),1,0))+IF(S21='Resultats Reals'!$C$15,2,IF(OR(S21='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S21)&gt;0),1,0))+IF(T21='Resultats Reals'!$C$18,2,IF(OR(T21='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T21)&gt;0),1,0))+IF(U21='Resultats Reals'!$C$21,2,IF(OR(U21='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U21)&gt;0),1,0))+IF(V21='Resultats Reals'!$C$24,2,IF(OR(V21='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V21)&gt;0),1,0))+IF(W21='Resultats Reals'!$C$27,2,IF(OR(W21='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W21)&gt;0),1,0))+IF(X21='Resultats Reals'!$C$30,2,IF(OR(X21='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X21)&gt;0),1,0))+IF(Y21='Resultats Reals'!$C$33,2,IF(OR(Y21='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y21)&gt;0),1,0))+IF(Z21='Resultats Reals'!$C$36,2,IF(OR(Z21='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z21)&gt;0),1,0))</f>
@@ -12344,7 +12347,7 @@
       </c>
       <c r="BW21">
         <f>IF(AA21='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0,2,0.5),IF(OR(AA21='Resultats Reals'!$C$2,AA21='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA21)&gt;0),1,0))+IF(AB21='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0,2,0.5),IF(OR(AB21='Resultats Reals'!$C$5,AB21='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB21)&gt;0),1,0))+IF(AC21='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0,2,0.5),IF(OR(AC21='Resultats Reals'!$C$8,AC21='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC21)&gt;0),1,0))+IF(AD21='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0,2,0.5),IF(OR(AD21='Resultats Reals'!$C$11,AD21='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD21)&gt;0),1,0))+IF(AE21='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0,2,0.5),IF(OR(AE21='Resultats Reals'!$C$14,AE21='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE21)&gt;0),1,0))+IF(AF21='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0,2,0.5),IF(OR(AF21='Resultats Reals'!$C$17,AF21='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF21)&gt;0),1,0))+IF(AG21='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0,2,0.5),IF(OR(AG21='Resultats Reals'!$C$20,AG21='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG21)&gt;0),1,0))+IF(AH21='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0,2,0.5),IF(OR(AH21='Resultats Reals'!$C$23,AH21='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH21)&gt;0),1,0))+IF(AI21='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0,2,0.5),IF(OR(AI21='Resultats Reals'!$C$26,AI21='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI21)&gt;0),1,0))+IF(AJ21='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0,2,0.5),IF(OR(AJ21='Resultats Reals'!$C$29,AJ21='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ21)&gt;0),1,0))+IF(AK21='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0,2,0.5),IF(OR(AK21='Resultats Reals'!$C$32,AK21='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK21)&gt;0),1,0))+IF(AL21='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0,2,0.5),IF(OR(AL21='Resultats Reals'!$C$35,AL21='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL21)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX21">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA21)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB21)&gt;0,1,0)</f>
@@ -12380,10 +12383,10 @@
       </c>
       <c r="CF21" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="22" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -12599,11 +12602,11 @@
       </c>
       <c r="BU22">
         <f>IF(C22='Resultats Reals'!$C$2,2,IF(OR(C22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C22)&gt;0),1,0))+IF(D22='Resultats Reals'!$C$5,2,IF(OR(D22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D22)&gt;0),1,0))+IF(E22='Resultats Reals'!$C$8,2,IF(OR(E22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E22)&gt;0),1,0))+IF(F22='Resultats Reals'!$C$11,2,IF(OR(F22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F22)&gt;0),1,0))+IF(G22='Resultats Reals'!$C$14,2,IF(OR(G22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G22)&gt;0),1,0))+IF(H22='Resultats Reals'!$C$17,2,IF(OR(H22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H22)&gt;0),1,0))+IF(I22='Resultats Reals'!$C$20,2,IF(OR(I22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I22)&gt;0),1,0))+IF(J22='Resultats Reals'!$C$23,2,IF(OR(J22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J22)&gt;0),1,0))+IF(K22='Resultats Reals'!$C$26,2,IF(OR(K22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K22)&gt;0),1,0))+IF(L22='Resultats Reals'!$C$29,2,IF(OR(L22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L22)&gt;0),1,0))+IF(M22='Resultats Reals'!$C$32,2,IF(OR(M22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M22)&gt;0),1,0))+IF(N22='Resultats Reals'!$C$35,2,IF(OR(N22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N22)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BV22">
         <f>IF(O22='Resultats Reals'!$C$3,2,IF(OR(O22='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O22)&gt;0),1,0))+IF(P22='Resultats Reals'!$C$6,2,IF(OR(P22='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P22)&gt;0),1,0))+IF(Q22='Resultats Reals'!$C$9,2,IF(OR(Q22='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q22)&gt;0),1,0))+IF(R22='Resultats Reals'!$C$12,2,IF(OR(R22='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R22)&gt;0),1,0))+IF(S22='Resultats Reals'!$C$15,2,IF(OR(S22='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S22)&gt;0),1,0))+IF(T22='Resultats Reals'!$C$18,2,IF(OR(T22='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T22)&gt;0),1,0))+IF(U22='Resultats Reals'!$C$21,2,IF(OR(U22='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U22)&gt;0),1,0))+IF(V22='Resultats Reals'!$C$24,2,IF(OR(V22='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V22)&gt;0),1,0))+IF(W22='Resultats Reals'!$C$27,2,IF(OR(W22='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W22)&gt;0),1,0))+IF(X22='Resultats Reals'!$C$30,2,IF(OR(X22='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X22)&gt;0),1,0))+IF(Y22='Resultats Reals'!$C$33,2,IF(OR(Y22='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y22)&gt;0),1,0))+IF(Z22='Resultats Reals'!$C$36,2,IF(OR(Z22='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z22)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW22">
         <f>IF(AA22='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0,2,0.5),IF(OR(AA22='Resultats Reals'!$C$2,AA22='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA22)&gt;0),1,0))+IF(AB22='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0,2,0.5),IF(OR(AB22='Resultats Reals'!$C$5,AB22='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB22)&gt;0),1,0))+IF(AC22='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0,2,0.5),IF(OR(AC22='Resultats Reals'!$C$8,AC22='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC22)&gt;0),1,0))+IF(AD22='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0,2,0.5),IF(OR(AD22='Resultats Reals'!$C$11,AD22='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD22)&gt;0),1,0))+IF(AE22='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0,2,0.5),IF(OR(AE22='Resultats Reals'!$C$14,AE22='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE22)&gt;0),1,0))+IF(AF22='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0,2,0.5),IF(OR(AF22='Resultats Reals'!$C$17,AF22='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF22)&gt;0),1,0))+IF(AG22='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0,2,0.5),IF(OR(AG22='Resultats Reals'!$C$20,AG22='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG22)&gt;0),1,0))+IF(AH22='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0,2,0.5),IF(OR(AH22='Resultats Reals'!$C$23,AH22='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH22)&gt;0),1,0))+IF(AI22='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0,2,0.5),IF(OR(AI22='Resultats Reals'!$C$26,AI22='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI22)&gt;0),1,0))+IF(AJ22='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0,2,0.5),IF(OR(AJ22='Resultats Reals'!$C$29,AJ22='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ22)&gt;0),1,0))+IF(AK22='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0,2,0.5),IF(OR(AK22='Resultats Reals'!$C$32,AK22='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK22)&gt;0),1,0))+IF(AL22='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0,2,0.5),IF(OR(AL22='Resultats Reals'!$C$35,AL22='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL22)&gt;0),1,0))</f>
@@ -12643,10 +12646,10 @@
       </c>
       <c r="CF22" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="23" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>172</v>
       </c>
@@ -12862,11 +12865,11 @@
       </c>
       <c r="BU23">
         <f>IF(C23='Resultats Reals'!$C$2,2,IF(OR(C23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C23)&gt;0),1,0))+IF(D23='Resultats Reals'!$C$5,2,IF(OR(D23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D23)&gt;0),1,0))+IF(E23='Resultats Reals'!$C$8,2,IF(OR(E23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E23)&gt;0),1,0))+IF(F23='Resultats Reals'!$C$11,2,IF(OR(F23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F23)&gt;0),1,0))+IF(G23='Resultats Reals'!$C$14,2,IF(OR(G23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G23)&gt;0),1,0))+IF(H23='Resultats Reals'!$C$17,2,IF(OR(H23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H23)&gt;0),1,0))+IF(I23='Resultats Reals'!$C$20,2,IF(OR(I23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I23)&gt;0),1,0))+IF(J23='Resultats Reals'!$C$23,2,IF(OR(J23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J23)&gt;0),1,0))+IF(K23='Resultats Reals'!$C$26,2,IF(OR(K23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K23)&gt;0),1,0))+IF(L23='Resultats Reals'!$C$29,2,IF(OR(L23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L23)&gt;0),1,0))+IF(M23='Resultats Reals'!$C$32,2,IF(OR(M23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M23)&gt;0),1,0))+IF(N23='Resultats Reals'!$C$35,2,IF(OR(N23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N23)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BV23">
         <f>IF(O23='Resultats Reals'!$C$3,2,IF(OR(O23='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O23)&gt;0),1,0))+IF(P23='Resultats Reals'!$C$6,2,IF(OR(P23='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P23)&gt;0),1,0))+IF(Q23='Resultats Reals'!$C$9,2,IF(OR(Q23='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q23)&gt;0),1,0))+IF(R23='Resultats Reals'!$C$12,2,IF(OR(R23='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R23)&gt;0),1,0))+IF(S23='Resultats Reals'!$C$15,2,IF(OR(S23='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S23)&gt;0),1,0))+IF(T23='Resultats Reals'!$C$18,2,IF(OR(T23='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T23)&gt;0),1,0))+IF(U23='Resultats Reals'!$C$21,2,IF(OR(U23='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U23)&gt;0),1,0))+IF(V23='Resultats Reals'!$C$24,2,IF(OR(V23='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V23)&gt;0),1,0))+IF(W23='Resultats Reals'!$C$27,2,IF(OR(W23='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W23)&gt;0),1,0))+IF(X23='Resultats Reals'!$C$30,2,IF(OR(X23='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X23)&gt;0),1,0))+IF(Y23='Resultats Reals'!$C$33,2,IF(OR(Y23='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y23)&gt;0),1,0))+IF(Z23='Resultats Reals'!$C$36,2,IF(OR(Z23='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z23)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW23">
         <f>IF(AA23='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0,2,0.5),IF(OR(AA23='Resultats Reals'!$C$2,AA23='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA23)&gt;0),1,0))+IF(AB23='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0,2,0.5),IF(OR(AB23='Resultats Reals'!$C$5,AB23='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB23)&gt;0),1,0))+IF(AC23='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0,2,0.5),IF(OR(AC23='Resultats Reals'!$C$8,AC23='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC23)&gt;0),1,0))+IF(AD23='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0,2,0.5),IF(OR(AD23='Resultats Reals'!$C$11,AD23='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD23)&gt;0),1,0))+IF(AE23='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0,2,0.5),IF(OR(AE23='Resultats Reals'!$C$14,AE23='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE23)&gt;0),1,0))+IF(AF23='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0,2,0.5),IF(OR(AF23='Resultats Reals'!$C$17,AF23='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF23)&gt;0),1,0))+IF(AG23='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0,2,0.5),IF(OR(AG23='Resultats Reals'!$C$20,AG23='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG23)&gt;0),1,0))+IF(AH23='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0,2,0.5),IF(OR(AH23='Resultats Reals'!$C$23,AH23='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH23)&gt;0),1,0))+IF(AI23='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0,2,0.5),IF(OR(AI23='Resultats Reals'!$C$26,AI23='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI23)&gt;0),1,0))+IF(AJ23='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0,2,0.5),IF(OR(AJ23='Resultats Reals'!$C$29,AJ23='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ23)&gt;0),1,0))+IF(AK23='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0,2,0.5),IF(OR(AK23='Resultats Reals'!$C$32,AK23='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK23)&gt;0),1,0))+IF(AL23='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0,2,0.5),IF(OR(AL23='Resultats Reals'!$C$35,AL23='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL23)&gt;0),1,0))</f>
@@ -12906,10 +12909,10 @@
       </c>
       <c r="CF23" s="7">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>35.5</v>
       </c>
     </row>
-    <row r="24" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>174</v>
       </c>
@@ -13125,7 +13128,7 @@
       </c>
       <c r="BU24">
         <f>IF(C24='Resultats Reals'!$C$2,2,IF(OR(C24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C24)&gt;0),1,0))+IF(D24='Resultats Reals'!$C$5,2,IF(OR(D24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D24)&gt;0),1,0))+IF(E24='Resultats Reals'!$C$8,2,IF(OR(E24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E24)&gt;0),1,0))+IF(F24='Resultats Reals'!$C$11,2,IF(OR(F24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F24)&gt;0),1,0))+IF(G24='Resultats Reals'!$C$14,2,IF(OR(G24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G24)&gt;0),1,0))+IF(H24='Resultats Reals'!$C$17,2,IF(OR(H24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H24)&gt;0),1,0))+IF(I24='Resultats Reals'!$C$20,2,IF(OR(I24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I24)&gt;0),1,0))+IF(J24='Resultats Reals'!$C$23,2,IF(OR(J24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J24)&gt;0),1,0))+IF(K24='Resultats Reals'!$C$26,2,IF(OR(K24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K24)&gt;0),1,0))+IF(L24='Resultats Reals'!$C$29,2,IF(OR(L24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L24)&gt;0),1,0))+IF(M24='Resultats Reals'!$C$32,2,IF(OR(M24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M24)&gt;0),1,0))+IF(N24='Resultats Reals'!$C$35,2,IF(OR(N24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N24)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV24">
         <f>IF(O24='Resultats Reals'!$C$3,2,IF(OR(O24='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O24)&gt;0),1,0))+IF(P24='Resultats Reals'!$C$6,2,IF(OR(P24='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P24)&gt;0),1,0))+IF(Q24='Resultats Reals'!$C$9,2,IF(OR(Q24='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q24)&gt;0),1,0))+IF(R24='Resultats Reals'!$C$12,2,IF(OR(R24='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R24)&gt;0),1,0))+IF(S24='Resultats Reals'!$C$15,2,IF(OR(S24='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S24)&gt;0),1,0))+IF(T24='Resultats Reals'!$C$18,2,IF(OR(T24='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T24)&gt;0),1,0))+IF(U24='Resultats Reals'!$C$21,2,IF(OR(U24='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U24)&gt;0),1,0))+IF(V24='Resultats Reals'!$C$24,2,IF(OR(V24='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V24)&gt;0),1,0))+IF(W24='Resultats Reals'!$C$27,2,IF(OR(W24='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W24)&gt;0),1,0))+IF(X24='Resultats Reals'!$C$30,2,IF(OR(X24='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X24)&gt;0),1,0))+IF(Y24='Resultats Reals'!$C$33,2,IF(OR(Y24='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y24)&gt;0),1,0))+IF(Z24='Resultats Reals'!$C$36,2,IF(OR(Z24='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z24)&gt;0),1,0))</f>
@@ -13133,7 +13136,7 @@
       </c>
       <c r="BW24">
         <f>IF(AA24='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0,2,0.5),IF(OR(AA24='Resultats Reals'!$C$2,AA24='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA24)&gt;0),1,0))+IF(AB24='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0,2,0.5),IF(OR(AB24='Resultats Reals'!$C$5,AB24='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB24)&gt;0),1,0))+IF(AC24='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0,2,0.5),IF(OR(AC24='Resultats Reals'!$C$8,AC24='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC24)&gt;0),1,0))+IF(AD24='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0,2,0.5),IF(OR(AD24='Resultats Reals'!$C$11,AD24='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD24)&gt;0),1,0))+IF(AE24='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0,2,0.5),IF(OR(AE24='Resultats Reals'!$C$14,AE24='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE24)&gt;0),1,0))+IF(AF24='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0,2,0.5),IF(OR(AF24='Resultats Reals'!$C$17,AF24='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF24)&gt;0),1,0))+IF(AG24='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0,2,0.5),IF(OR(AG24='Resultats Reals'!$C$20,AG24='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG24)&gt;0),1,0))+IF(AH24='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0,2,0.5),IF(OR(AH24='Resultats Reals'!$C$23,AH24='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH24)&gt;0),1,0))+IF(AI24='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0,2,0.5),IF(OR(AI24='Resultats Reals'!$C$26,AI24='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI24)&gt;0),1,0))+IF(AJ24='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0,2,0.5),IF(OR(AJ24='Resultats Reals'!$C$29,AJ24='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ24)&gt;0),1,0))+IF(AK24='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0,2,0.5),IF(OR(AK24='Resultats Reals'!$C$32,AK24='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK24)&gt;0),1,0))+IF(AL24='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0,2,0.5),IF(OR(AL24='Resultats Reals'!$C$35,AL24='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL24)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="BX24">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA24)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB24)&gt;0,1,0)</f>
@@ -13169,10 +13172,10 @@
       </c>
       <c r="CF24" s="7">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="25" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>175</v>
       </c>
@@ -13388,11 +13391,11 @@
       </c>
       <c r="BU25">
         <f>IF(C25='Resultats Reals'!$C$2,2,IF(OR(C25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C25)&gt;0),1,0))+IF(D25='Resultats Reals'!$C$5,2,IF(OR(D25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D25)&gt;0),1,0))+IF(E25='Resultats Reals'!$C$8,2,IF(OR(E25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E25)&gt;0),1,0))+IF(F25='Resultats Reals'!$C$11,2,IF(OR(F25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F25)&gt;0),1,0))+IF(G25='Resultats Reals'!$C$14,2,IF(OR(G25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G25)&gt;0),1,0))+IF(H25='Resultats Reals'!$C$17,2,IF(OR(H25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H25)&gt;0),1,0))+IF(I25='Resultats Reals'!$C$20,2,IF(OR(I25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I25)&gt;0),1,0))+IF(J25='Resultats Reals'!$C$23,2,IF(OR(J25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J25)&gt;0),1,0))+IF(K25='Resultats Reals'!$C$26,2,IF(OR(K25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K25)&gt;0),1,0))+IF(L25='Resultats Reals'!$C$29,2,IF(OR(L25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L25)&gt;0),1,0))+IF(M25='Resultats Reals'!$C$32,2,IF(OR(M25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M25)&gt;0),1,0))+IF(N25='Resultats Reals'!$C$35,2,IF(OR(N25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N25)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BV25">
         <f>IF(O25='Resultats Reals'!$C$3,2,IF(OR(O25='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O25)&gt;0),1,0))+IF(P25='Resultats Reals'!$C$6,2,IF(OR(P25='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P25)&gt;0),1,0))+IF(Q25='Resultats Reals'!$C$9,2,IF(OR(Q25='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q25)&gt;0),1,0))+IF(R25='Resultats Reals'!$C$12,2,IF(OR(R25='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R25)&gt;0),1,0))+IF(S25='Resultats Reals'!$C$15,2,IF(OR(S25='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S25)&gt;0),1,0))+IF(T25='Resultats Reals'!$C$18,2,IF(OR(T25='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T25)&gt;0),1,0))+IF(U25='Resultats Reals'!$C$21,2,IF(OR(U25='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U25)&gt;0),1,0))+IF(V25='Resultats Reals'!$C$24,2,IF(OR(V25='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V25)&gt;0),1,0))+IF(W25='Resultats Reals'!$C$27,2,IF(OR(W25='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W25)&gt;0),1,0))+IF(X25='Resultats Reals'!$C$30,2,IF(OR(X25='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X25)&gt;0),1,0))+IF(Y25='Resultats Reals'!$C$33,2,IF(OR(Y25='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y25)&gt;0),1,0))+IF(Z25='Resultats Reals'!$C$36,2,IF(OR(Z25='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z25)&gt;0),1,0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BW25">
         <f>IF(AA25='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0,2,0.5),IF(OR(AA25='Resultats Reals'!$C$2,AA25='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA25)&gt;0),1,0))+IF(AB25='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0,2,0.5),IF(OR(AB25='Resultats Reals'!$C$5,AB25='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB25)&gt;0),1,0))+IF(AC25='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0,2,0.5),IF(OR(AC25='Resultats Reals'!$C$8,AC25='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC25)&gt;0),1,0))+IF(AD25='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0,2,0.5),IF(OR(AD25='Resultats Reals'!$C$11,AD25='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD25)&gt;0),1,0))+IF(AE25='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0,2,0.5),IF(OR(AE25='Resultats Reals'!$C$14,AE25='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE25)&gt;0),1,0))+IF(AF25='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0,2,0.5),IF(OR(AF25='Resultats Reals'!$C$17,AF25='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF25)&gt;0),1,0))+IF(AG25='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0,2,0.5),IF(OR(AG25='Resultats Reals'!$C$20,AG25='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG25)&gt;0),1,0))+IF(AH25='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0,2,0.5),IF(OR(AH25='Resultats Reals'!$C$23,AH25='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH25)&gt;0),1,0))+IF(AI25='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0,2,0.5),IF(OR(AI25='Resultats Reals'!$C$26,AI25='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI25)&gt;0),1,0))+IF(AJ25='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0,2,0.5),IF(OR(AJ25='Resultats Reals'!$C$29,AJ25='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ25)&gt;0),1,0))+IF(AK25='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0,2,0.5),IF(OR(AK25='Resultats Reals'!$C$32,AK25='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK25)&gt;0),1,0))+IF(AL25='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0,2,0.5),IF(OR(AL25='Resultats Reals'!$C$35,AL25='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL25)&gt;0),1,0))</f>
@@ -13432,10 +13435,10 @@
       </c>
       <c r="CF25" s="7">
         <f t="shared" si="0"/>
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
     </row>
-    <row r="26" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>176</v>
       </c>
@@ -13654,7 +13657,7 @@
       </c>
       <c r="BU26">
         <f>IF(C26='Resultats Reals'!$C$2,2,IF(OR(C26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C26)&gt;0),1,0))+IF(D26='Resultats Reals'!$C$5,2,IF(OR(D26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D26)&gt;0),1,0))+IF(E26='Resultats Reals'!$C$8,2,IF(OR(E26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E26)&gt;0),1,0))+IF(F26='Resultats Reals'!$C$11,2,IF(OR(F26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F26)&gt;0),1,0))+IF(G26='Resultats Reals'!$C$14,2,IF(OR(G26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G26)&gt;0),1,0))+IF(H26='Resultats Reals'!$C$17,2,IF(OR(H26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H26)&gt;0),1,0))+IF(I26='Resultats Reals'!$C$20,2,IF(OR(I26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I26)&gt;0),1,0))+IF(J26='Resultats Reals'!$C$23,2,IF(OR(J26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J26)&gt;0),1,0))+IF(K26='Resultats Reals'!$C$26,2,IF(OR(K26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K26)&gt;0),1,0))+IF(L26='Resultats Reals'!$C$29,2,IF(OR(L26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L26)&gt;0),1,0))+IF(M26='Resultats Reals'!$C$32,2,IF(OR(M26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M26)&gt;0),1,0))+IF(N26='Resultats Reals'!$C$35,2,IF(OR(N26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N26)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BV26">
         <f>IF(O26='Resultats Reals'!$C$3,2,IF(OR(O26='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O26)&gt;0),1,0))+IF(P26='Resultats Reals'!$C$6,2,IF(OR(P26='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P26)&gt;0),1,0))+IF(Q26='Resultats Reals'!$C$9,2,IF(OR(Q26='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q26)&gt;0),1,0))+IF(R26='Resultats Reals'!$C$12,2,IF(OR(R26='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R26)&gt;0),1,0))+IF(S26='Resultats Reals'!$C$15,2,IF(OR(S26='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S26)&gt;0),1,0))+IF(T26='Resultats Reals'!$C$18,2,IF(OR(T26='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T26)&gt;0),1,0))+IF(U26='Resultats Reals'!$C$21,2,IF(OR(U26='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U26)&gt;0),1,0))+IF(V26='Resultats Reals'!$C$24,2,IF(OR(V26='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V26)&gt;0),1,0))+IF(W26='Resultats Reals'!$C$27,2,IF(OR(W26='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W26)&gt;0),1,0))+IF(X26='Resultats Reals'!$C$30,2,IF(OR(X26='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X26)&gt;0),1,0))+IF(Y26='Resultats Reals'!$C$33,2,IF(OR(Y26='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y26)&gt;0),1,0))+IF(Z26='Resultats Reals'!$C$36,2,IF(OR(Z26='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z26)&gt;0),1,0))</f>
@@ -13662,7 +13665,7 @@
       </c>
       <c r="BW26">
         <f>IF(AA26='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0,2,0.5),IF(OR(AA26='Resultats Reals'!$C$2,AA26='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA26)&gt;0),1,0))+IF(AB26='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0,2,0.5),IF(OR(AB26='Resultats Reals'!$C$5,AB26='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB26)&gt;0),1,0))+IF(AC26='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0,2,0.5),IF(OR(AC26='Resultats Reals'!$C$8,AC26='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC26)&gt;0),1,0))+IF(AD26='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0,2,0.5),IF(OR(AD26='Resultats Reals'!$C$11,AD26='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD26)&gt;0),1,0))+IF(AE26='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0,2,0.5),IF(OR(AE26='Resultats Reals'!$C$14,AE26='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE26)&gt;0),1,0))+IF(AF26='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0,2,0.5),IF(OR(AF26='Resultats Reals'!$C$17,AF26='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF26)&gt;0),1,0))+IF(AG26='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0,2,0.5),IF(OR(AG26='Resultats Reals'!$C$20,AG26='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG26)&gt;0),1,0))+IF(AH26='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0,2,0.5),IF(OR(AH26='Resultats Reals'!$C$23,AH26='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH26)&gt;0),1,0))+IF(AI26='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0,2,0.5),IF(OR(AI26='Resultats Reals'!$C$26,AI26='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI26)&gt;0),1,0))+IF(AJ26='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0,2,0.5),IF(OR(AJ26='Resultats Reals'!$C$29,AJ26='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ26)&gt;0),1,0))+IF(AK26='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0,2,0.5),IF(OR(AK26='Resultats Reals'!$C$32,AK26='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK26)&gt;0),1,0))+IF(AL26='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0,2,0.5),IF(OR(AL26='Resultats Reals'!$C$35,AL26='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL26)&gt;0),1,0))</f>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BX26">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA26)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB26)&gt;0,1,0)</f>
@@ -13698,10 +13701,10 @@
       </c>
       <c r="CF26" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>178</v>
       </c>
@@ -13917,7 +13920,7 @@
       </c>
       <c r="BU27">
         <f>IF(C27='Resultats Reals'!$C$2,2,IF(OR(C27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C27)&gt;0),1,0))+IF(D27='Resultats Reals'!$C$5,2,IF(OR(D27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D27)&gt;0),1,0))+IF(E27='Resultats Reals'!$C$8,2,IF(OR(E27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E27)&gt;0),1,0))+IF(F27='Resultats Reals'!$C$11,2,IF(OR(F27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F27)&gt;0),1,0))+IF(G27='Resultats Reals'!$C$14,2,IF(OR(G27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G27)&gt;0),1,0))+IF(H27='Resultats Reals'!$C$17,2,IF(OR(H27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H27)&gt;0),1,0))+IF(I27='Resultats Reals'!$C$20,2,IF(OR(I27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I27)&gt;0),1,0))+IF(J27='Resultats Reals'!$C$23,2,IF(OR(J27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J27)&gt;0),1,0))+IF(K27='Resultats Reals'!$C$26,2,IF(OR(K27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K27)&gt;0),1,0))+IF(L27='Resultats Reals'!$C$29,2,IF(OR(L27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L27)&gt;0),1,0))+IF(M27='Resultats Reals'!$C$32,2,IF(OR(M27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M27)&gt;0),1,0))+IF(N27='Resultats Reals'!$C$35,2,IF(OR(N27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N27)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV27">
         <f>IF(O27='Resultats Reals'!$C$3,2,IF(OR(O27='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O27)&gt;0),1,0))+IF(P27='Resultats Reals'!$C$6,2,IF(OR(P27='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P27)&gt;0),1,0))+IF(Q27='Resultats Reals'!$C$9,2,IF(OR(Q27='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q27)&gt;0),1,0))+IF(R27='Resultats Reals'!$C$12,2,IF(OR(R27='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R27)&gt;0),1,0))+IF(S27='Resultats Reals'!$C$15,2,IF(OR(S27='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S27)&gt;0),1,0))+IF(T27='Resultats Reals'!$C$18,2,IF(OR(T27='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T27)&gt;0),1,0))+IF(U27='Resultats Reals'!$C$21,2,IF(OR(U27='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U27)&gt;0),1,0))+IF(V27='Resultats Reals'!$C$24,2,IF(OR(V27='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V27)&gt;0),1,0))+IF(W27='Resultats Reals'!$C$27,2,IF(OR(W27='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W27)&gt;0),1,0))+IF(X27='Resultats Reals'!$C$30,2,IF(OR(X27='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X27)&gt;0),1,0))+IF(Y27='Resultats Reals'!$C$33,2,IF(OR(Y27='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y27)&gt;0),1,0))+IF(Z27='Resultats Reals'!$C$36,2,IF(OR(Z27='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z27)&gt;0),1,0))</f>
@@ -13925,7 +13928,7 @@
       </c>
       <c r="BW27">
         <f>IF(AA27='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0,2,0.5),IF(OR(AA27='Resultats Reals'!$C$2,AA27='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA27)&gt;0),1,0))+IF(AB27='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0,2,0.5),IF(OR(AB27='Resultats Reals'!$C$5,AB27='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB27)&gt;0),1,0))+IF(AC27='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0,2,0.5),IF(OR(AC27='Resultats Reals'!$C$8,AC27='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC27)&gt;0),1,0))+IF(AD27='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0,2,0.5),IF(OR(AD27='Resultats Reals'!$C$11,AD27='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD27)&gt;0),1,0))+IF(AE27='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0,2,0.5),IF(OR(AE27='Resultats Reals'!$C$14,AE27='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE27)&gt;0),1,0))+IF(AF27='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0,2,0.5),IF(OR(AF27='Resultats Reals'!$C$17,AF27='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF27)&gt;0),1,0))+IF(AG27='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0,2,0.5),IF(OR(AG27='Resultats Reals'!$C$20,AG27='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG27)&gt;0),1,0))+IF(AH27='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0,2,0.5),IF(OR(AH27='Resultats Reals'!$C$23,AH27='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH27)&gt;0),1,0))+IF(AI27='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0,2,0.5),IF(OR(AI27='Resultats Reals'!$C$26,AI27='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI27)&gt;0),1,0))+IF(AJ27='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0,2,0.5),IF(OR(AJ27='Resultats Reals'!$C$29,AJ27='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ27)&gt;0),1,0))+IF(AK27='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0,2,0.5),IF(OR(AK27='Resultats Reals'!$C$32,AK27='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK27)&gt;0),1,0))+IF(AL27='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0,2,0.5),IF(OR(AL27='Resultats Reals'!$C$35,AL27='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL27)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX27">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA27)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB27)&gt;0,1,0)</f>
@@ -13961,10 +13964,10 @@
       </c>
       <c r="CF27" s="7">
         <f t="shared" si="0"/>
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="28" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>179</v>
       </c>
@@ -14188,7 +14191,7 @@
       </c>
       <c r="BW28">
         <f>IF(AA28='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0,2,0.5),IF(OR(AA28='Resultats Reals'!$C$2,AA28='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA28)&gt;0),1,0))+IF(AB28='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0,2,0.5),IF(OR(AB28='Resultats Reals'!$C$5,AB28='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB28)&gt;0),1,0))+IF(AC28='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0,2,0.5),IF(OR(AC28='Resultats Reals'!$C$8,AC28='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC28)&gt;0),1,0))+IF(AD28='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0,2,0.5),IF(OR(AD28='Resultats Reals'!$C$11,AD28='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD28)&gt;0),1,0))+IF(AE28='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0,2,0.5),IF(OR(AE28='Resultats Reals'!$C$14,AE28='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE28)&gt;0),1,0))+IF(AF28='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0,2,0.5),IF(OR(AF28='Resultats Reals'!$C$17,AF28='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF28)&gt;0),1,0))+IF(AG28='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0,2,0.5),IF(OR(AG28='Resultats Reals'!$C$20,AG28='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG28)&gt;0),1,0))+IF(AH28='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0,2,0.5),IF(OR(AH28='Resultats Reals'!$C$23,AH28='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH28)&gt;0),1,0))+IF(AI28='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0,2,0.5),IF(OR(AI28='Resultats Reals'!$C$26,AI28='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI28)&gt;0),1,0))+IF(AJ28='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0,2,0.5),IF(OR(AJ28='Resultats Reals'!$C$29,AJ28='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ28)&gt;0),1,0))+IF(AK28='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0,2,0.5),IF(OR(AK28='Resultats Reals'!$C$32,AK28='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK28)&gt;0),1,0))+IF(AL28='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0,2,0.5),IF(OR(AL28='Resultats Reals'!$C$35,AL28='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL28)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="BX28">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA28)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB28)&gt;0,1,0)</f>
@@ -14224,10 +14227,10 @@
       </c>
       <c r="CF28" s="7">
         <f t="shared" si="0"/>
-        <v>42.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="29" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>181</v>
       </c>
@@ -14446,15 +14449,15 @@
       </c>
       <c r="BU29">
         <f>IF(C29='Resultats Reals'!$C$2,2,IF(OR(C29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C29)&gt;0),1,0))+IF(D29='Resultats Reals'!$C$5,2,IF(OR(D29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D29)&gt;0),1,0))+IF(E29='Resultats Reals'!$C$8,2,IF(OR(E29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E29)&gt;0),1,0))+IF(F29='Resultats Reals'!$C$11,2,IF(OR(F29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F29)&gt;0),1,0))+IF(G29='Resultats Reals'!$C$14,2,IF(OR(G29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G29)&gt;0),1,0))+IF(H29='Resultats Reals'!$C$17,2,IF(OR(H29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H29)&gt;0),1,0))+IF(I29='Resultats Reals'!$C$20,2,IF(OR(I29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I29)&gt;0),1,0))+IF(J29='Resultats Reals'!$C$23,2,IF(OR(J29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J29)&gt;0),1,0))+IF(K29='Resultats Reals'!$C$26,2,IF(OR(K29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K29)&gt;0),1,0))+IF(L29='Resultats Reals'!$C$29,2,IF(OR(L29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L29)&gt;0),1,0))+IF(M29='Resultats Reals'!$C$32,2,IF(OR(M29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M29)&gt;0),1,0))+IF(N29='Resultats Reals'!$C$35,2,IF(OR(N29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N29)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV29">
         <f>IF(O29='Resultats Reals'!$C$3,2,IF(OR(O29='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O29)&gt;0),1,0))+IF(P29='Resultats Reals'!$C$6,2,IF(OR(P29='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P29)&gt;0),1,0))+IF(Q29='Resultats Reals'!$C$9,2,IF(OR(Q29='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q29)&gt;0),1,0))+IF(R29='Resultats Reals'!$C$12,2,IF(OR(R29='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R29)&gt;0),1,0))+IF(S29='Resultats Reals'!$C$15,2,IF(OR(S29='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S29)&gt;0),1,0))+IF(T29='Resultats Reals'!$C$18,2,IF(OR(T29='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T29)&gt;0),1,0))+IF(U29='Resultats Reals'!$C$21,2,IF(OR(U29='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U29)&gt;0),1,0))+IF(V29='Resultats Reals'!$C$24,2,IF(OR(V29='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V29)&gt;0),1,0))+IF(W29='Resultats Reals'!$C$27,2,IF(OR(W29='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W29)&gt;0),1,0))+IF(X29='Resultats Reals'!$C$30,2,IF(OR(X29='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X29)&gt;0),1,0))+IF(Y29='Resultats Reals'!$C$33,2,IF(OR(Y29='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y29)&gt;0),1,0))+IF(Z29='Resultats Reals'!$C$36,2,IF(OR(Z29='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z29)&gt;0),1,0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BW29">
         <f>IF(AA29='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0,2,0.5),IF(OR(AA29='Resultats Reals'!$C$2,AA29='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA29)&gt;0),1,0))+IF(AB29='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0,2,0.5),IF(OR(AB29='Resultats Reals'!$C$5,AB29='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB29)&gt;0),1,0))+IF(AC29='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0,2,0.5),IF(OR(AC29='Resultats Reals'!$C$8,AC29='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC29)&gt;0),1,0))+IF(AD29='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0,2,0.5),IF(OR(AD29='Resultats Reals'!$C$11,AD29='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD29)&gt;0),1,0))+IF(AE29='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0,2,0.5),IF(OR(AE29='Resultats Reals'!$C$14,AE29='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE29)&gt;0),1,0))+IF(AF29='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0,2,0.5),IF(OR(AF29='Resultats Reals'!$C$17,AF29='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF29)&gt;0),1,0))+IF(AG29='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0,2,0.5),IF(OR(AG29='Resultats Reals'!$C$20,AG29='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG29)&gt;0),1,0))+IF(AH29='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0,2,0.5),IF(OR(AH29='Resultats Reals'!$C$23,AH29='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH29)&gt;0),1,0))+IF(AI29='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0,2,0.5),IF(OR(AI29='Resultats Reals'!$C$26,AI29='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI29)&gt;0),1,0))+IF(AJ29='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0,2,0.5),IF(OR(AJ29='Resultats Reals'!$C$29,AJ29='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ29)&gt;0),1,0))+IF(AK29='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0,2,0.5),IF(OR(AK29='Resultats Reals'!$C$32,AK29='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK29)&gt;0),1,0))+IF(AL29='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0,2,0.5),IF(OR(AL29='Resultats Reals'!$C$35,AL29='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL29)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX29">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA29)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB29)&gt;0,1,0)</f>
@@ -14490,10 +14493,10 @@
       </c>
       <c r="CF29" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
     </row>
-    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -14709,7 +14712,7 @@
       </c>
       <c r="BU30">
         <f>IF(C30='Resultats Reals'!$C$2,2,IF(OR(C30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C30)&gt;0),1,0))+IF(D30='Resultats Reals'!$C$5,2,IF(OR(D30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D30)&gt;0),1,0))+IF(E30='Resultats Reals'!$C$8,2,IF(OR(E30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E30)&gt;0),1,0))+IF(F30='Resultats Reals'!$C$11,2,IF(OR(F30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F30)&gt;0),1,0))+IF(G30='Resultats Reals'!$C$14,2,IF(OR(G30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G30)&gt;0),1,0))+IF(H30='Resultats Reals'!$C$17,2,IF(OR(H30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H30)&gt;0),1,0))+IF(I30='Resultats Reals'!$C$20,2,IF(OR(I30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I30)&gt;0),1,0))+IF(J30='Resultats Reals'!$C$23,2,IF(OR(J30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J30)&gt;0),1,0))+IF(K30='Resultats Reals'!$C$26,2,IF(OR(K30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K30)&gt;0),1,0))+IF(L30='Resultats Reals'!$C$29,2,IF(OR(L30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L30)&gt;0),1,0))+IF(M30='Resultats Reals'!$C$32,2,IF(OR(M30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M30)&gt;0),1,0))+IF(N30='Resultats Reals'!$C$35,2,IF(OR(N30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N30)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV30">
         <f>IF(O30='Resultats Reals'!$C$3,2,IF(OR(O30='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O30)&gt;0),1,0))+IF(P30='Resultats Reals'!$C$6,2,IF(OR(P30='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P30)&gt;0),1,0))+IF(Q30='Resultats Reals'!$C$9,2,IF(OR(Q30='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q30)&gt;0),1,0))+IF(R30='Resultats Reals'!$C$12,2,IF(OR(R30='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R30)&gt;0),1,0))+IF(S30='Resultats Reals'!$C$15,2,IF(OR(S30='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S30)&gt;0),1,0))+IF(T30='Resultats Reals'!$C$18,2,IF(OR(T30='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T30)&gt;0),1,0))+IF(U30='Resultats Reals'!$C$21,2,IF(OR(U30='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U30)&gt;0),1,0))+IF(V30='Resultats Reals'!$C$24,2,IF(OR(V30='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V30)&gt;0),1,0))+IF(W30='Resultats Reals'!$C$27,2,IF(OR(W30='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W30)&gt;0),1,0))+IF(X30='Resultats Reals'!$C$30,2,IF(OR(X30='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X30)&gt;0),1,0))+IF(Y30='Resultats Reals'!$C$33,2,IF(OR(Y30='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y30)&gt;0),1,0))+IF(Z30='Resultats Reals'!$C$36,2,IF(OR(Z30='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z30)&gt;0),1,0))</f>
@@ -14717,7 +14720,7 @@
       </c>
       <c r="BW30">
         <f>IF(AA30='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0,2,0.5),IF(OR(AA30='Resultats Reals'!$C$2,AA30='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA30)&gt;0),1,0))+IF(AB30='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0,2,0.5),IF(OR(AB30='Resultats Reals'!$C$5,AB30='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB30)&gt;0),1,0))+IF(AC30='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0,2,0.5),IF(OR(AC30='Resultats Reals'!$C$8,AC30='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC30)&gt;0),1,0))+IF(AD30='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0,2,0.5),IF(OR(AD30='Resultats Reals'!$C$11,AD30='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD30)&gt;0),1,0))+IF(AE30='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0,2,0.5),IF(OR(AE30='Resultats Reals'!$C$14,AE30='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE30)&gt;0),1,0))+IF(AF30='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0,2,0.5),IF(OR(AF30='Resultats Reals'!$C$17,AF30='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF30)&gt;0),1,0))+IF(AG30='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0,2,0.5),IF(OR(AG30='Resultats Reals'!$C$20,AG30='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG30)&gt;0),1,0))+IF(AH30='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0,2,0.5),IF(OR(AH30='Resultats Reals'!$C$23,AH30='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH30)&gt;0),1,0))+IF(AI30='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0,2,0.5),IF(OR(AI30='Resultats Reals'!$C$26,AI30='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI30)&gt;0),1,0))+IF(AJ30='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0,2,0.5),IF(OR(AJ30='Resultats Reals'!$C$29,AJ30='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ30)&gt;0),1,0))+IF(AK30='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0,2,0.5),IF(OR(AK30='Resultats Reals'!$C$32,AK30='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK30)&gt;0),1,0))+IF(AL30='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0,2,0.5),IF(OR(AL30='Resultats Reals'!$C$35,AL30='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL30)&gt;0),1,0))</f>
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX30">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA30)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB30)&gt;0,1,0)</f>
@@ -14753,10 +14756,10 @@
       </c>
       <c r="CF30" s="7">
         <f t="shared" si="0"/>
-        <v>38.5</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>184</v>
       </c>
@@ -14972,7 +14975,7 @@
       </c>
       <c r="BU31">
         <f>IF(C31='Resultats Reals'!$C$2,2,IF(OR(C31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C31)&gt;0),1,0))+IF(D31='Resultats Reals'!$C$5,2,IF(OR(D31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D31)&gt;0),1,0))+IF(E31='Resultats Reals'!$C$8,2,IF(OR(E31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E31)&gt;0),1,0))+IF(F31='Resultats Reals'!$C$11,2,IF(OR(F31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F31)&gt;0),1,0))+IF(G31='Resultats Reals'!$C$14,2,IF(OR(G31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G31)&gt;0),1,0))+IF(H31='Resultats Reals'!$C$17,2,IF(OR(H31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H31)&gt;0),1,0))+IF(I31='Resultats Reals'!$C$20,2,IF(OR(I31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I31)&gt;0),1,0))+IF(J31='Resultats Reals'!$C$23,2,IF(OR(J31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J31)&gt;0),1,0))+IF(K31='Resultats Reals'!$C$26,2,IF(OR(K31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K31)&gt;0),1,0))+IF(L31='Resultats Reals'!$C$29,2,IF(OR(L31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L31)&gt;0),1,0))+IF(M31='Resultats Reals'!$C$32,2,IF(OR(M31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M31)&gt;0),1,0))+IF(N31='Resultats Reals'!$C$35,2,IF(OR(N31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N31)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV31">
         <f>IF(O31='Resultats Reals'!$C$3,2,IF(OR(O31='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O31)&gt;0),1,0))+IF(P31='Resultats Reals'!$C$6,2,IF(OR(P31='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P31)&gt;0),1,0))+IF(Q31='Resultats Reals'!$C$9,2,IF(OR(Q31='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q31)&gt;0),1,0))+IF(R31='Resultats Reals'!$C$12,2,IF(OR(R31='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R31)&gt;0),1,0))+IF(S31='Resultats Reals'!$C$15,2,IF(OR(S31='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S31)&gt;0),1,0))+IF(T31='Resultats Reals'!$C$18,2,IF(OR(T31='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T31)&gt;0),1,0))+IF(U31='Resultats Reals'!$C$21,2,IF(OR(U31='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U31)&gt;0),1,0))+IF(V31='Resultats Reals'!$C$24,2,IF(OR(V31='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V31)&gt;0),1,0))+IF(W31='Resultats Reals'!$C$27,2,IF(OR(W31='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W31)&gt;0),1,0))+IF(X31='Resultats Reals'!$C$30,2,IF(OR(X31='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X31)&gt;0),1,0))+IF(Y31='Resultats Reals'!$C$33,2,IF(OR(Y31='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y31)&gt;0),1,0))+IF(Z31='Resultats Reals'!$C$36,2,IF(OR(Z31='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z31)&gt;0),1,0))</f>
@@ -14980,7 +14983,7 @@
       </c>
       <c r="BW31">
         <f>IF(AA31='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0,2,0.5),IF(OR(AA31='Resultats Reals'!$C$2,AA31='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA31)&gt;0),1,0))+IF(AB31='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0,2,0.5),IF(OR(AB31='Resultats Reals'!$C$5,AB31='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB31)&gt;0),1,0))+IF(AC31='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0,2,0.5),IF(OR(AC31='Resultats Reals'!$C$8,AC31='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC31)&gt;0),1,0))+IF(AD31='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0,2,0.5),IF(OR(AD31='Resultats Reals'!$C$11,AD31='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD31)&gt;0),1,0))+IF(AE31='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0,2,0.5),IF(OR(AE31='Resultats Reals'!$C$14,AE31='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE31)&gt;0),1,0))+IF(AF31='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0,2,0.5),IF(OR(AF31='Resultats Reals'!$C$17,AF31='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF31)&gt;0),1,0))+IF(AG31='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0,2,0.5),IF(OR(AG31='Resultats Reals'!$C$20,AG31='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG31)&gt;0),1,0))+IF(AH31='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0,2,0.5),IF(OR(AH31='Resultats Reals'!$C$23,AH31='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH31)&gt;0),1,0))+IF(AI31='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0,2,0.5),IF(OR(AI31='Resultats Reals'!$C$26,AI31='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI31)&gt;0),1,0))+IF(AJ31='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0,2,0.5),IF(OR(AJ31='Resultats Reals'!$C$29,AJ31='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ31)&gt;0),1,0))+IF(AK31='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0,2,0.5),IF(OR(AK31='Resultats Reals'!$C$32,AK31='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK31)&gt;0),1,0))+IF(AL31='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0,2,0.5),IF(OR(AL31='Resultats Reals'!$C$35,AL31='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL31)&gt;0),1,0))</f>
-        <v>12.5</v>
+        <v>9.5</v>
       </c>
       <c r="BX31">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA31)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB31)&gt;0,1,0)</f>
@@ -15016,10 +15019,10 @@
       </c>
       <c r="CF31" s="7">
         <f t="shared" si="0"/>
-        <v>41.5</v>
+        <v>37.5</v>
       </c>
     </row>
-    <row r="32" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>185</v>
       </c>
@@ -15238,7 +15241,7 @@
       </c>
       <c r="BU32">
         <f>IF(C32='Resultats Reals'!$C$2,2,IF(OR(C32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C32)&gt;0),1,0))+IF(D32='Resultats Reals'!$C$5,2,IF(OR(D32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D32)&gt;0),1,0))+IF(E32='Resultats Reals'!$C$8,2,IF(OR(E32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E32)&gt;0),1,0))+IF(F32='Resultats Reals'!$C$11,2,IF(OR(F32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F32)&gt;0),1,0))+IF(G32='Resultats Reals'!$C$14,2,IF(OR(G32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G32)&gt;0),1,0))+IF(H32='Resultats Reals'!$C$17,2,IF(OR(H32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H32)&gt;0),1,0))+IF(I32='Resultats Reals'!$C$20,2,IF(OR(I32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I32)&gt;0),1,0))+IF(J32='Resultats Reals'!$C$23,2,IF(OR(J32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J32)&gt;0),1,0))+IF(K32='Resultats Reals'!$C$26,2,IF(OR(K32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K32)&gt;0),1,0))+IF(L32='Resultats Reals'!$C$29,2,IF(OR(L32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L32)&gt;0),1,0))+IF(M32='Resultats Reals'!$C$32,2,IF(OR(M32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M32)&gt;0),1,0))+IF(N32='Resultats Reals'!$C$35,2,IF(OR(N32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N32)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV32">
         <f>IF(O32='Resultats Reals'!$C$3,2,IF(OR(O32='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O32)&gt;0),1,0))+IF(P32='Resultats Reals'!$C$6,2,IF(OR(P32='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P32)&gt;0),1,0))+IF(Q32='Resultats Reals'!$C$9,2,IF(OR(Q32='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q32)&gt;0),1,0))+IF(R32='Resultats Reals'!$C$12,2,IF(OR(R32='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R32)&gt;0),1,0))+IF(S32='Resultats Reals'!$C$15,2,IF(OR(S32='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S32)&gt;0),1,0))+IF(T32='Resultats Reals'!$C$18,2,IF(OR(T32='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T32)&gt;0),1,0))+IF(U32='Resultats Reals'!$C$21,2,IF(OR(U32='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U32)&gt;0),1,0))+IF(V32='Resultats Reals'!$C$24,2,IF(OR(V32='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V32)&gt;0),1,0))+IF(W32='Resultats Reals'!$C$27,2,IF(OR(W32='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W32)&gt;0),1,0))+IF(X32='Resultats Reals'!$C$30,2,IF(OR(X32='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X32)&gt;0),1,0))+IF(Y32='Resultats Reals'!$C$33,2,IF(OR(Y32='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y32)&gt;0),1,0))+IF(Z32='Resultats Reals'!$C$36,2,IF(OR(Z32='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z32)&gt;0),1,0))</f>
@@ -15246,7 +15249,7 @@
       </c>
       <c r="BW32">
         <f>IF(AA32='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0,2,0.5),IF(OR(AA32='Resultats Reals'!$C$2,AA32='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA32)&gt;0),1,0))+IF(AB32='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0,2,0.5),IF(OR(AB32='Resultats Reals'!$C$5,AB32='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB32)&gt;0),1,0))+IF(AC32='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0,2,0.5),IF(OR(AC32='Resultats Reals'!$C$8,AC32='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC32)&gt;0),1,0))+IF(AD32='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0,2,0.5),IF(OR(AD32='Resultats Reals'!$C$11,AD32='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD32)&gt;0),1,0))+IF(AE32='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0,2,0.5),IF(OR(AE32='Resultats Reals'!$C$14,AE32='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE32)&gt;0),1,0))+IF(AF32='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0,2,0.5),IF(OR(AF32='Resultats Reals'!$C$17,AF32='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF32)&gt;0),1,0))+IF(AG32='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0,2,0.5),IF(OR(AG32='Resultats Reals'!$C$20,AG32='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG32)&gt;0),1,0))+IF(AH32='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0,2,0.5),IF(OR(AH32='Resultats Reals'!$C$23,AH32='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH32)&gt;0),1,0))+IF(AI32='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0,2,0.5),IF(OR(AI32='Resultats Reals'!$C$26,AI32='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI32)&gt;0),1,0))+IF(AJ32='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0,2,0.5),IF(OR(AJ32='Resultats Reals'!$C$29,AJ32='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ32)&gt;0),1,0))+IF(AK32='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0,2,0.5),IF(OR(AK32='Resultats Reals'!$C$32,AK32='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK32)&gt;0),1,0))+IF(AL32='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0,2,0.5),IF(OR(AL32='Resultats Reals'!$C$35,AL32='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL32)&gt;0),1,0))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BX32">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA32)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB32)&gt;0,1,0)</f>
@@ -15282,10 +15285,10 @@
       </c>
       <c r="CF32" s="7">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>187</v>
       </c>
@@ -15504,7 +15507,7 @@
       </c>
       <c r="BU33">
         <f>IF(C33='Resultats Reals'!$C$2,2,IF(OR(C33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C33)&gt;0),1,0))+IF(D33='Resultats Reals'!$C$5,2,IF(OR(D33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D33)&gt;0),1,0))+IF(E33='Resultats Reals'!$C$8,2,IF(OR(E33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E33)&gt;0),1,0))+IF(F33='Resultats Reals'!$C$11,2,IF(OR(F33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F33)&gt;0),1,0))+IF(G33='Resultats Reals'!$C$14,2,IF(OR(G33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G33)&gt;0),1,0))+IF(H33='Resultats Reals'!$C$17,2,IF(OR(H33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H33)&gt;0),1,0))+IF(I33='Resultats Reals'!$C$20,2,IF(OR(I33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I33)&gt;0),1,0))+IF(J33='Resultats Reals'!$C$23,2,IF(OR(J33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J33)&gt;0),1,0))+IF(K33='Resultats Reals'!$C$26,2,IF(OR(K33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K33)&gt;0),1,0))+IF(L33='Resultats Reals'!$C$29,2,IF(OR(L33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L33)&gt;0),1,0))+IF(M33='Resultats Reals'!$C$32,2,IF(OR(M33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M33)&gt;0),1,0))+IF(N33='Resultats Reals'!$C$35,2,IF(OR(N33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N33)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV33">
         <f>IF(O33='Resultats Reals'!$C$3,2,IF(OR(O33='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O33)&gt;0),1,0))+IF(P33='Resultats Reals'!$C$6,2,IF(OR(P33='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P33)&gt;0),1,0))+IF(Q33='Resultats Reals'!$C$9,2,IF(OR(Q33='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q33)&gt;0),1,0))+IF(R33='Resultats Reals'!$C$12,2,IF(OR(R33='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R33)&gt;0),1,0))+IF(S33='Resultats Reals'!$C$15,2,IF(OR(S33='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S33)&gt;0),1,0))+IF(T33='Resultats Reals'!$C$18,2,IF(OR(T33='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T33)&gt;0),1,0))+IF(U33='Resultats Reals'!$C$21,2,IF(OR(U33='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U33)&gt;0),1,0))+IF(V33='Resultats Reals'!$C$24,2,IF(OR(V33='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V33)&gt;0),1,0))+IF(W33='Resultats Reals'!$C$27,2,IF(OR(W33='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W33)&gt;0),1,0))+IF(X33='Resultats Reals'!$C$30,2,IF(OR(X33='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X33)&gt;0),1,0))+IF(Y33='Resultats Reals'!$C$33,2,IF(OR(Y33='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y33)&gt;0),1,0))+IF(Z33='Resultats Reals'!$C$36,2,IF(OR(Z33='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z33)&gt;0),1,0))</f>
@@ -15512,7 +15515,7 @@
       </c>
       <c r="BW33">
         <f>IF(AA33='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0,2,0.5),IF(OR(AA33='Resultats Reals'!$C$2,AA33='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA33)&gt;0),1,0))+IF(AB33='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0,2,0.5),IF(OR(AB33='Resultats Reals'!$C$5,AB33='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB33)&gt;0),1,0))+IF(AC33='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0,2,0.5),IF(OR(AC33='Resultats Reals'!$C$8,AC33='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC33)&gt;0),1,0))+IF(AD33='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0,2,0.5),IF(OR(AD33='Resultats Reals'!$C$11,AD33='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD33)&gt;0),1,0))+IF(AE33='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0,2,0.5),IF(OR(AE33='Resultats Reals'!$C$14,AE33='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE33)&gt;0),1,0))+IF(AF33='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0,2,0.5),IF(OR(AF33='Resultats Reals'!$C$17,AF33='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF33)&gt;0),1,0))+IF(AG33='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0,2,0.5),IF(OR(AG33='Resultats Reals'!$C$20,AG33='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG33)&gt;0),1,0))+IF(AH33='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0,2,0.5),IF(OR(AH33='Resultats Reals'!$C$23,AH33='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH33)&gt;0),1,0))+IF(AI33='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0,2,0.5),IF(OR(AI33='Resultats Reals'!$C$26,AI33='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI33)&gt;0),1,0))+IF(AJ33='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0,2,0.5),IF(OR(AJ33='Resultats Reals'!$C$29,AJ33='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ33)&gt;0),1,0))+IF(AK33='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0,2,0.5),IF(OR(AK33='Resultats Reals'!$C$32,AK33='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK33)&gt;0),1,0))+IF(AL33='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0,2,0.5),IF(OR(AL33='Resultats Reals'!$C$35,AL33='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL33)&gt;0),1,0))</f>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX33">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA33)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB33)&gt;0,1,0)</f>
@@ -15548,10 +15551,10 @@
       </c>
       <c r="CF33" s="7">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
     </row>
-    <row r="34" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>189</v>
       </c>
@@ -15770,7 +15773,7 @@
       </c>
       <c r="BU34">
         <f>IF(C34='Resultats Reals'!$C$2,2,IF(OR(C34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C34)&gt;0),1,0))+IF(D34='Resultats Reals'!$C$5,2,IF(OR(D34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D34)&gt;0),1,0))+IF(E34='Resultats Reals'!$C$8,2,IF(OR(E34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E34)&gt;0),1,0))+IF(F34='Resultats Reals'!$C$11,2,IF(OR(F34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F34)&gt;0),1,0))+IF(G34='Resultats Reals'!$C$14,2,IF(OR(G34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G34)&gt;0),1,0))+IF(H34='Resultats Reals'!$C$17,2,IF(OR(H34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H34)&gt;0),1,0))+IF(I34='Resultats Reals'!$C$20,2,IF(OR(I34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I34)&gt;0),1,0))+IF(J34='Resultats Reals'!$C$23,2,IF(OR(J34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J34)&gt;0),1,0))+IF(K34='Resultats Reals'!$C$26,2,IF(OR(K34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K34)&gt;0),1,0))+IF(L34='Resultats Reals'!$C$29,2,IF(OR(L34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L34)&gt;0),1,0))+IF(M34='Resultats Reals'!$C$32,2,IF(OR(M34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M34)&gt;0),1,0))+IF(N34='Resultats Reals'!$C$35,2,IF(OR(N34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N34)&gt;0),1,0))</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BV34">
         <f>IF(O34='Resultats Reals'!$C$3,2,IF(OR(O34='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O34)&gt;0),1,0))+IF(P34='Resultats Reals'!$C$6,2,IF(OR(P34='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P34)&gt;0),1,0))+IF(Q34='Resultats Reals'!$C$9,2,IF(OR(Q34='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q34)&gt;0),1,0))+IF(R34='Resultats Reals'!$C$12,2,IF(OR(R34='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R34)&gt;0),1,0))+IF(S34='Resultats Reals'!$C$15,2,IF(OR(S34='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S34)&gt;0),1,0))+IF(T34='Resultats Reals'!$C$18,2,IF(OR(T34='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T34)&gt;0),1,0))+IF(U34='Resultats Reals'!$C$21,2,IF(OR(U34='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U34)&gt;0),1,0))+IF(V34='Resultats Reals'!$C$24,2,IF(OR(V34='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V34)&gt;0),1,0))+IF(W34='Resultats Reals'!$C$27,2,IF(OR(W34='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W34)&gt;0),1,0))+IF(X34='Resultats Reals'!$C$30,2,IF(OR(X34='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X34)&gt;0),1,0))+IF(Y34='Resultats Reals'!$C$33,2,IF(OR(Y34='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y34)&gt;0),1,0))+IF(Z34='Resultats Reals'!$C$36,2,IF(OR(Z34='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z34)&gt;0),1,0))</f>
@@ -15778,7 +15781,7 @@
       </c>
       <c r="BW34">
         <f>IF(AA34='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0,2,0.5),IF(OR(AA34='Resultats Reals'!$C$2,AA34='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA34)&gt;0),1,0))+IF(AB34='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0,2,0.5),IF(OR(AB34='Resultats Reals'!$C$5,AB34='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB34)&gt;0),1,0))+IF(AC34='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0,2,0.5),IF(OR(AC34='Resultats Reals'!$C$8,AC34='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC34)&gt;0),1,0))+IF(AD34='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0,2,0.5),IF(OR(AD34='Resultats Reals'!$C$11,AD34='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD34)&gt;0),1,0))+IF(AE34='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0,2,0.5),IF(OR(AE34='Resultats Reals'!$C$14,AE34='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE34)&gt;0),1,0))+IF(AF34='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0,2,0.5),IF(OR(AF34='Resultats Reals'!$C$17,AF34='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF34)&gt;0),1,0))+IF(AG34='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0,2,0.5),IF(OR(AG34='Resultats Reals'!$C$20,AG34='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG34)&gt;0),1,0))+IF(AH34='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0,2,0.5),IF(OR(AH34='Resultats Reals'!$C$23,AH34='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH34)&gt;0),1,0))+IF(AI34='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0,2,0.5),IF(OR(AI34='Resultats Reals'!$C$26,AI34='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI34)&gt;0),1,0))+IF(AJ34='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0,2,0.5),IF(OR(AJ34='Resultats Reals'!$C$29,AJ34='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ34)&gt;0),1,0))+IF(AK34='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0,2,0.5),IF(OR(AK34='Resultats Reals'!$C$32,AK34='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK34)&gt;0),1,0))+IF(AL34='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0,2,0.5),IF(OR(AL34='Resultats Reals'!$C$35,AL34='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL34)&gt;0),1,0))</f>
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="BX34">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA34)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB34)&gt;0,1,0)</f>
@@ -15814,10 +15817,10 @@
       </c>
       <c r="CF34" s="7">
         <f t="shared" si="0"/>
-        <v>44.5</v>
+        <v>40.5</v>
       </c>
     </row>
-    <row r="35" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>191</v>
       </c>
@@ -16033,15 +16036,15 @@
       </c>
       <c r="BU35">
         <f>IF(C35='Resultats Reals'!$C$2,2,IF(OR(C35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C35)&gt;0),1,0))+IF(D35='Resultats Reals'!$C$5,2,IF(OR(D35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D35)&gt;0),1,0))+IF(E35='Resultats Reals'!$C$8,2,IF(OR(E35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E35)&gt;0),1,0))+IF(F35='Resultats Reals'!$C$11,2,IF(OR(F35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F35)&gt;0),1,0))+IF(G35='Resultats Reals'!$C$14,2,IF(OR(G35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G35)&gt;0),1,0))+IF(H35='Resultats Reals'!$C$17,2,IF(OR(H35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H35)&gt;0),1,0))+IF(I35='Resultats Reals'!$C$20,2,IF(OR(I35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I35)&gt;0),1,0))+IF(J35='Resultats Reals'!$C$23,2,IF(OR(J35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J35)&gt;0),1,0))+IF(K35='Resultats Reals'!$C$26,2,IF(OR(K35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K35)&gt;0),1,0))+IF(L35='Resultats Reals'!$C$29,2,IF(OR(L35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L35)&gt;0),1,0))+IF(M35='Resultats Reals'!$C$32,2,IF(OR(M35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M35)&gt;0),1,0))+IF(N35='Resultats Reals'!$C$35,2,IF(OR(N35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N35)&gt;0),1,0))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV35">
         <f>IF(O35='Resultats Reals'!$C$3,2,IF(OR(O35='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O35)&gt;0),1,0))+IF(P35='Resultats Reals'!$C$6,2,IF(OR(P35='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P35)&gt;0),1,0))+IF(Q35='Resultats Reals'!$C$9,2,IF(OR(Q35='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q35)&gt;0),1,0))+IF(R35='Resultats Reals'!$C$12,2,IF(OR(R35='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R35)&gt;0),1,0))+IF(S35='Resultats Reals'!$C$15,2,IF(OR(S35='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S35)&gt;0),1,0))+IF(T35='Resultats Reals'!$C$18,2,IF(OR(T35='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T35)&gt;0),1,0))+IF(U35='Resultats Reals'!$C$21,2,IF(OR(U35='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U35)&gt;0),1,0))+IF(V35='Resultats Reals'!$C$24,2,IF(OR(V35='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V35)&gt;0),1,0))+IF(W35='Resultats Reals'!$C$27,2,IF(OR(W35='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W35)&gt;0),1,0))+IF(X35='Resultats Reals'!$C$30,2,IF(OR(X35='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X35)&gt;0),1,0))+IF(Y35='Resultats Reals'!$C$33,2,IF(OR(Y35='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y35)&gt;0),1,0))+IF(Z35='Resultats Reals'!$C$36,2,IF(OR(Z35='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z35)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BW35">
         <f>IF(AA35='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0,2,0.5),IF(OR(AA35='Resultats Reals'!$C$2,AA35='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA35)&gt;0),1,0))+IF(AB35='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0,2,0.5),IF(OR(AB35='Resultats Reals'!$C$5,AB35='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB35)&gt;0),1,0))+IF(AC35='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0,2,0.5),IF(OR(AC35='Resultats Reals'!$C$8,AC35='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC35)&gt;0),1,0))+IF(AD35='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0,2,0.5),IF(OR(AD35='Resultats Reals'!$C$11,AD35='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD35)&gt;0),1,0))+IF(AE35='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0,2,0.5),IF(OR(AE35='Resultats Reals'!$C$14,AE35='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE35)&gt;0),1,0))+IF(AF35='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0,2,0.5),IF(OR(AF35='Resultats Reals'!$C$17,AF35='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF35)&gt;0),1,0))+IF(AG35='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0,2,0.5),IF(OR(AG35='Resultats Reals'!$C$20,AG35='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG35)&gt;0),1,0))+IF(AH35='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0,2,0.5),IF(OR(AH35='Resultats Reals'!$C$23,AH35='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH35)&gt;0),1,0))+IF(AI35='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0,2,0.5),IF(OR(AI35='Resultats Reals'!$C$26,AI35='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI35)&gt;0),1,0))+IF(AJ35='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0,2,0.5),IF(OR(AJ35='Resultats Reals'!$C$29,AJ35='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ35)&gt;0),1,0))+IF(AK35='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0,2,0.5),IF(OR(AK35='Resultats Reals'!$C$32,AK35='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK35)&gt;0),1,0))+IF(AL35='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0,2,0.5),IF(OR(AL35='Resultats Reals'!$C$35,AL35='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL35)&gt;0),1,0))</f>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BX35">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA35)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB35)&gt;0,1,0)</f>
@@ -16077,10 +16080,10 @@
       </c>
       <c r="CF35" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>192</v>
       </c>
@@ -16304,7 +16307,7 @@
       </c>
       <c r="BW36">
         <f>IF(AA36='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0,2,0.5),IF(OR(AA36='Resultats Reals'!$C$2,AA36='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA36)&gt;0),1,0))+IF(AB36='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0,2,0.5),IF(OR(AB36='Resultats Reals'!$C$5,AB36='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB36)&gt;0),1,0))+IF(AC36='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0,2,0.5),IF(OR(AC36='Resultats Reals'!$C$8,AC36='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC36)&gt;0),1,0))+IF(AD36='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0,2,0.5),IF(OR(AD36='Resultats Reals'!$C$11,AD36='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD36)&gt;0),1,0))+IF(AE36='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0,2,0.5),IF(OR(AE36='Resultats Reals'!$C$14,AE36='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE36)&gt;0),1,0))+IF(AF36='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0,2,0.5),IF(OR(AF36='Resultats Reals'!$C$17,AF36='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF36)&gt;0),1,0))+IF(AG36='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0,2,0.5),IF(OR(AG36='Resultats Reals'!$C$20,AG36='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG36)&gt;0),1,0))+IF(AH36='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0,2,0.5),IF(OR(AH36='Resultats Reals'!$C$23,AH36='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH36)&gt;0),1,0))+IF(AI36='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0,2,0.5),IF(OR(AI36='Resultats Reals'!$C$26,AI36='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI36)&gt;0),1,0))+IF(AJ36='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0,2,0.5),IF(OR(AJ36='Resultats Reals'!$C$29,AJ36='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ36)&gt;0),1,0))+IF(AK36='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0,2,0.5),IF(OR(AK36='Resultats Reals'!$C$32,AK36='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK36)&gt;0),1,0))+IF(AL36='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0,2,0.5),IF(OR(AL36='Resultats Reals'!$C$35,AL36='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL36)&gt;0),1,0))</f>
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BX36">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA36)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB36)&gt;0,1,0)</f>
@@ -16340,10 +16343,10 @@
       </c>
       <c r="CF36" s="7">
         <f t="shared" si="0"/>
-        <v>45.5</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -16559,7 +16562,7 @@
       </c>
       <c r="BU37">
         <f>IF(C37='Resultats Reals'!$C$2,2,IF(OR(C37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C37)&gt;0),1,0))+IF(D37='Resultats Reals'!$C$5,2,IF(OR(D37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D37)&gt;0),1,0))+IF(E37='Resultats Reals'!$C$8,2,IF(OR(E37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E37)&gt;0),1,0))+IF(F37='Resultats Reals'!$C$11,2,IF(OR(F37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F37)&gt;0),1,0))+IF(G37='Resultats Reals'!$C$14,2,IF(OR(G37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G37)&gt;0),1,0))+IF(H37='Resultats Reals'!$C$17,2,IF(OR(H37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H37)&gt;0),1,0))+IF(I37='Resultats Reals'!$C$20,2,IF(OR(I37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I37)&gt;0),1,0))+IF(J37='Resultats Reals'!$C$23,2,IF(OR(J37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J37)&gt;0),1,0))+IF(K37='Resultats Reals'!$C$26,2,IF(OR(K37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K37)&gt;0),1,0))+IF(L37='Resultats Reals'!$C$29,2,IF(OR(L37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L37)&gt;0),1,0))+IF(M37='Resultats Reals'!$C$32,2,IF(OR(M37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M37)&gt;0),1,0))+IF(N37='Resultats Reals'!$C$35,2,IF(OR(N37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N37)&gt;0),1,0))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BV37">
         <f>IF(O37='Resultats Reals'!$C$3,2,IF(OR(O37='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O37)&gt;0),1,0))+IF(P37='Resultats Reals'!$C$6,2,IF(OR(P37='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P37)&gt;0),1,0))+IF(Q37='Resultats Reals'!$C$9,2,IF(OR(Q37='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q37)&gt;0),1,0))+IF(R37='Resultats Reals'!$C$12,2,IF(OR(R37='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R37)&gt;0),1,0))+IF(S37='Resultats Reals'!$C$15,2,IF(OR(S37='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S37)&gt;0),1,0))+IF(T37='Resultats Reals'!$C$18,2,IF(OR(T37='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T37)&gt;0),1,0))+IF(U37='Resultats Reals'!$C$21,2,IF(OR(U37='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U37)&gt;0),1,0))+IF(V37='Resultats Reals'!$C$24,2,IF(OR(V37='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V37)&gt;0),1,0))+IF(W37='Resultats Reals'!$C$27,2,IF(OR(W37='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W37)&gt;0),1,0))+IF(X37='Resultats Reals'!$C$30,2,IF(OR(X37='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X37)&gt;0),1,0))+IF(Y37='Resultats Reals'!$C$33,2,IF(OR(Y37='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y37)&gt;0),1,0))+IF(Z37='Resultats Reals'!$C$36,2,IF(OR(Z37='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z37)&gt;0),1,0))</f>
@@ -16567,7 +16570,7 @@
       </c>
       <c r="BW37">
         <f>IF(AA37='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0,2,0.5),IF(OR(AA37='Resultats Reals'!$C$2,AA37='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA37)&gt;0),1,0))+IF(AB37='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0,2,0.5),IF(OR(AB37='Resultats Reals'!$C$5,AB37='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB37)&gt;0),1,0))+IF(AC37='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0,2,0.5),IF(OR(AC37='Resultats Reals'!$C$8,AC37='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC37)&gt;0),1,0))+IF(AD37='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0,2,0.5),IF(OR(AD37='Resultats Reals'!$C$11,AD37='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD37)&gt;0),1,0))+IF(AE37='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0,2,0.5),IF(OR(AE37='Resultats Reals'!$C$14,AE37='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE37)&gt;0),1,0))+IF(AF37='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0,2,0.5),IF(OR(AF37='Resultats Reals'!$C$17,AF37='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF37)&gt;0),1,0))+IF(AG37='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0,2,0.5),IF(OR(AG37='Resultats Reals'!$C$20,AG37='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG37)&gt;0),1,0))+IF(AH37='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0,2,0.5),IF(OR(AH37='Resultats Reals'!$C$23,AH37='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH37)&gt;0),1,0))+IF(AI37='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0,2,0.5),IF(OR(AI37='Resultats Reals'!$C$26,AI37='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI37)&gt;0),1,0))+IF(AJ37='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0,2,0.5),IF(OR(AJ37='Resultats Reals'!$C$29,AJ37='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ37)&gt;0),1,0))+IF(AK37='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0,2,0.5),IF(OR(AK37='Resultats Reals'!$C$32,AK37='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK37)&gt;0),1,0))+IF(AL37='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0,2,0.5),IF(OR(AL37='Resultats Reals'!$C$35,AL37='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL37)&gt;0),1,0))</f>
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX37">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA37)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB37)&gt;0,1,0)</f>
@@ -16603,10 +16606,10 @@
       </c>
       <c r="CF37" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>44.5</v>
       </c>
     </row>
-    <row r="38" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -16825,7 +16828,7 @@
       </c>
       <c r="BU38">
         <f>IF(C38='Resultats Reals'!$C$2,2,IF(OR(C38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C38)&gt;0),1,0))+IF(D38='Resultats Reals'!$C$5,2,IF(OR(D38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,D38)&gt;0),1,0))+IF(E38='Resultats Reals'!$C$8,2,IF(OR(E38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,E38)&gt;0),1,0))+IF(F38='Resultats Reals'!$C$11,2,IF(OR(F38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,F38)&gt;0),1,0))+IF(G38='Resultats Reals'!$C$14,2,IF(OR(G38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,G38)&gt;0),1,0))+IF(H38='Resultats Reals'!$C$17,2,IF(OR(H38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,H38)&gt;0),1,0))+IF(I38='Resultats Reals'!$C$20,2,IF(OR(I38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,I38)&gt;0),1,0))+IF(J38='Resultats Reals'!$C$23,2,IF(OR(J38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,J38)&gt;0),1,0))+IF(K38='Resultats Reals'!$C$26,2,IF(OR(K38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,K38)&gt;0),1,0))+IF(L38='Resultats Reals'!$C$29,2,IF(OR(L38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,L38)&gt;0),1,0))+IF(M38='Resultats Reals'!$C$32,2,IF(OR(M38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,M38)&gt;0),1,0))+IF(N38='Resultats Reals'!$C$35,2,IF(OR(N38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,N38)&gt;0),1,0))</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BV38">
         <f>IF(O38='Resultats Reals'!$C$3,2,IF(OR(O38='Resultats Reals'!$C$2,COUNTIF('Resultats Reals'!$E$2:$E$33,O38)&gt;0),1,0))+IF(P38='Resultats Reals'!$C$6,2,IF(OR(P38='Resultats Reals'!$C$5,COUNTIF('Resultats Reals'!$E$2:$E$33,P38)&gt;0),1,0))+IF(Q38='Resultats Reals'!$C$9,2,IF(OR(Q38='Resultats Reals'!$C$8,COUNTIF('Resultats Reals'!$E$2:$E$33,Q38)&gt;0),1,0))+IF(R38='Resultats Reals'!$C$12,2,IF(OR(R38='Resultats Reals'!$C$11,COUNTIF('Resultats Reals'!$E$2:$E$33,R38)&gt;0),1,0))+IF(S38='Resultats Reals'!$C$15,2,IF(OR(S38='Resultats Reals'!$C$14,COUNTIF('Resultats Reals'!$E$2:$E$33,S38)&gt;0),1,0))+IF(T38='Resultats Reals'!$C$18,2,IF(OR(T38='Resultats Reals'!$C$17,COUNTIF('Resultats Reals'!$E$2:$E$33,T38)&gt;0),1,0))+IF(U38='Resultats Reals'!$C$21,2,IF(OR(U38='Resultats Reals'!$C$20,COUNTIF('Resultats Reals'!$E$2:$E$33,U38)&gt;0),1,0))+IF(V38='Resultats Reals'!$C$24,2,IF(OR(V38='Resultats Reals'!$C$23,COUNTIF('Resultats Reals'!$E$2:$E$33,V38)&gt;0),1,0))+IF(W38='Resultats Reals'!$C$27,2,IF(OR(W38='Resultats Reals'!$C$26,COUNTIF('Resultats Reals'!$E$2:$E$33,W38)&gt;0),1,0))+IF(X38='Resultats Reals'!$C$30,2,IF(OR(X38='Resultats Reals'!$C$29,COUNTIF('Resultats Reals'!$E$2:$E$33,X38)&gt;0),1,0))+IF(Y38='Resultats Reals'!$C$33,2,IF(OR(Y38='Resultats Reals'!$C$32,COUNTIF('Resultats Reals'!$E$2:$E$33,Y38)&gt;0),1,0))+IF(Z38='Resultats Reals'!$C$36,2,IF(OR(Z38='Resultats Reals'!$C$35,COUNTIF('Resultats Reals'!$E$2:$E$33,Z38)&gt;0),1,0))</f>
@@ -16833,7 +16836,7 @@
       </c>
       <c r="BW38">
         <f>IF(AA38='Resultats Reals'!$C$4,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0,2,0.5),IF(OR(AA38='Resultats Reals'!$C$2,AA38='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,AA38)&gt;0),1,0))+IF(AB38='Resultats Reals'!$C$7,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0,2,0.5),IF(OR(AB38='Resultats Reals'!$C$5,AB38='Resultats Reals'!$C$6,COUNTIF('Resultats Reals'!$E$2:$E$33,AB38)&gt;0),1,0))+IF(AC38='Resultats Reals'!$C$10,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0,2,0.5),IF(OR(AC38='Resultats Reals'!$C$8,AC38='Resultats Reals'!$C$9,COUNTIF('Resultats Reals'!$E$2:$E$33,AC38)&gt;0),1,0))+IF(AD38='Resultats Reals'!$C$13,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0,2,0.5),IF(OR(AD38='Resultats Reals'!$C$11,AD38='Resultats Reals'!$C$12,COUNTIF('Resultats Reals'!$E$2:$E$33,AD38)&gt;0),1,0))+IF(AE38='Resultats Reals'!$C$16,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0,2,0.5),IF(OR(AE38='Resultats Reals'!$C$14,AE38='Resultats Reals'!$C$15,COUNTIF('Resultats Reals'!$E$2:$E$33,AE38)&gt;0),1,0))+IF(AF38='Resultats Reals'!$C$19,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0,2,0.5),IF(OR(AF38='Resultats Reals'!$C$17,AF38='Resultats Reals'!$C$18,COUNTIF('Resultats Reals'!$E$2:$E$33,AF38)&gt;0),1,0))+IF(AG38='Resultats Reals'!$C$22,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0,2,0.5),IF(OR(AG38='Resultats Reals'!$C$20,AG38='Resultats Reals'!$C$21,COUNTIF('Resultats Reals'!$E$2:$E$33,AG38)&gt;0),1,0))+IF(AH38='Resultats Reals'!$C$25,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0,2,0.5),IF(OR(AH38='Resultats Reals'!$C$23,AH38='Resultats Reals'!$C$24,COUNTIF('Resultats Reals'!$E$2:$E$33,AH38)&gt;0),1,0))+IF(AI38='Resultats Reals'!$C$28,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0,2,0.5),IF(OR(AI38='Resultats Reals'!$C$26,AI38='Resultats Reals'!$C$27,COUNTIF('Resultats Reals'!$E$2:$E$33,AI38)&gt;0),1,0))+IF(AJ38='Resultats Reals'!$C$31,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0,2,0.5),IF(OR(AJ38='Resultats Reals'!$C$29,AJ38='Resultats Reals'!$C$30,COUNTIF('Resultats Reals'!$E$2:$E$33,AJ38)&gt;0),1,0))+IF(AK38='Resultats Reals'!$C$34,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0,2,0.5),IF(OR(AK38='Resultats Reals'!$C$32,AK38='Resultats Reals'!$C$33,COUNTIF('Resultats Reals'!$E$2:$E$33,AK38)&gt;0),1,0))+IF(AL38='Resultats Reals'!$C$37,IF(COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0,2,0.5),IF(OR(AL38='Resultats Reals'!$C$35,AL38='Resultats Reals'!$C$36,COUNTIF('Resultats Reals'!$E$2:$E$33,AL38)&gt;0),1,0))</f>
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BX38">
         <f>IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AM38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AN38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AO38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AP38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AQ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AR38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AS38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AT38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AU38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AV38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AW38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AX38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AY38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,AZ38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BA38)&gt;0,1,0)+IF(COUNTIF('Resultats Reals'!$F$2:$F$17,BB38)&gt;0,1,0)</f>
@@ -16869,10 +16872,10 @@
       </c>
       <c r="CF38" s="7">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>42.5</v>
       </c>
     </row>
-    <row r="39" spans="1:84" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:84" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>198</v>
       </c>
@@ -17091,7 +17094,7 @@
       </c>
       <c r="BU39">
         <f>IF(C39='Resultats Reals'!$C$2,2,IF(OR(C39='Resultats Reals'!$C$3,COUNTIF('Resultats Reals'!$E$2:$E$33,C39)&gt;0),1,0))+IF(D39='Res